--- a/translation_dashboard.xlsx
+++ b/translation_dashboard.xlsx
@@ -13879,7 +13879,7 @@
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="24.28125"/>
-    <col customWidth="1" min="2" max="2" width="32.28125"/>
+    <col customWidth="1" min="2" max="2" width="43.28125"/>
     <col customWidth="1" min="3" max="3" width="15.7109375"/>
     <col customWidth="1" min="4" max="4" width="14.00390625"/>
     <col customWidth="1" min="5" max="5" width="15.00390625"/>
@@ -14318,7 +14318,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="1">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -14439,7 +14439,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="1">
       <c r="A24" t="s">
         <v>125</v>
       </c>
@@ -14603,7 +14603,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="1">
       <c r="A31" t="s">
         <v>161</v>
       </c>
@@ -14816,7 +14816,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="1">
       <c r="A40" t="s">
         <v>208</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="1">
       <c r="A42" t="s">
         <v>219</v>
       </c>
@@ -14914,7 +14914,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="1">
       <c r="A44" t="s">
         <v>230</v>
       </c>
@@ -14940,7 +14940,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="1">
       <c r="A45" t="s">
         <v>236</v>
       </c>
@@ -15127,7 +15127,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="1">
       <c r="A53" t="s">
         <v>277</v>
       </c>
@@ -15176,7 +15176,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="1">
       <c r="A55" t="s">
         <v>288</v>
       </c>
@@ -15202,7 +15202,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="1">
       <c r="A56" t="s">
         <v>294</v>
       </c>
@@ -15504,7 +15504,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="1">
       <c r="A69" t="s">
         <v>360</v>
       </c>
@@ -15530,7 +15530,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="1">
       <c r="A70" t="s">
         <v>366</v>
       </c>
@@ -15671,7 +15671,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="1">
       <c r="A76" t="s">
         <v>397</v>
       </c>
@@ -15881,7 +15881,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="1">
       <c r="A85" t="s">
         <v>443</v>
       </c>
@@ -15976,7 +15976,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="1">
       <c r="A89" t="s">
         <v>464</v>
       </c>
@@ -16048,7 +16048,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="1">
       <c r="A92" t="s">
         <v>480</v>
       </c>
@@ -16143,7 +16143,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="1">
       <c r="A96" t="s">
         <v>501</v>
       </c>
@@ -16238,7 +16238,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="1">
       <c r="A100" t="s">
         <v>522</v>
       </c>
@@ -16310,7 +16310,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="1">
       <c r="A103" t="s">
         <v>538</v>
       </c>
@@ -16336,7 +16336,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="1">
       <c r="A104" t="s">
         <v>544</v>
       </c>
@@ -16431,7 +16431,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="1">
       <c r="A108" t="s">
         <v>565</v>
       </c>
@@ -16457,7 +16457,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="1">
       <c r="A109" t="s">
         <v>571</v>
       </c>
@@ -16529,7 +16529,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="1">
       <c r="A112" t="s">
         <v>587</v>
       </c>
@@ -16581,7 +16581,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="1">
       <c r="A114" t="s">
         <v>599</v>
       </c>
@@ -16722,7 +16722,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="1">
       <c r="A120" t="s">
         <v>630</v>
       </c>
@@ -16771,7 +16771,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="1">
       <c r="A122" t="s">
         <v>641</v>
       </c>
@@ -16820,7 +16820,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="1">
       <c r="A124" t="s">
         <v>652</v>
       </c>
@@ -16892,7 +16892,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="1">
       <c r="A127" t="s">
         <v>668</v>
       </c>
@@ -16918,7 +16918,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="1">
       <c r="A128" t="s">
         <v>674</v>
       </c>
@@ -17036,7 +17036,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="1">
       <c r="A133" t="s">
         <v>700</v>
       </c>
@@ -17085,7 +17085,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="1">
       <c r="A135" t="s">
         <v>711</v>
       </c>
@@ -17111,7 +17111,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="1">
       <c r="A136" t="s">
         <v>717</v>
       </c>
@@ -17137,7 +17137,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="1">
       <c r="A137" t="s">
         <v>723</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="1">
       <c r="A140" t="s">
         <v>739</v>
       </c>
@@ -17235,7 +17235,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="1">
       <c r="A141" t="s">
         <v>745</v>
       </c>
@@ -17284,7 +17284,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="1">
       <c r="A143" t="s">
         <v>756</v>
       </c>
@@ -17310,7 +17310,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="1">
       <c r="A144" t="s">
         <v>762</v>
       </c>
@@ -17408,7 +17408,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="1">
       <c r="A148" t="s">
         <v>784</v>
       </c>
@@ -17503,7 +17503,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="1">
       <c r="A152" t="s">
         <v>805</v>
       </c>
@@ -17575,7 +17575,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="1">
       <c r="A155" t="s">
         <v>821</v>
       </c>
@@ -17624,7 +17624,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" hidden="1">
       <c r="A157" t="s">
         <v>832</v>
       </c>
@@ -17650,7 +17650,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="1">
       <c r="A158" t="s">
         <v>838</v>
       </c>
@@ -17676,7 +17676,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="1">
       <c r="A159" t="s">
         <v>844</v>
       </c>
@@ -17912,7 +17912,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="1">
       <c r="A169" t="s">
         <v>896</v>
       </c>
@@ -17938,7 +17938,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="1">
       <c r="A170" t="s">
         <v>902</v>
       </c>
@@ -17987,7 +17987,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="1">
       <c r="A172" t="s">
         <v>913</v>
       </c>
@@ -18128,7 +18128,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="1">
       <c r="A178" t="s">
         <v>944</v>
       </c>
@@ -18177,7 +18177,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="1">
       <c r="A180" t="s">
         <v>955</v>
       </c>
@@ -18226,7 +18226,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" hidden="1">
       <c r="A182" t="s">
         <v>966</v>
       </c>
@@ -18321,7 +18321,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="1">
       <c r="A186" t="s">
         <v>987</v>
       </c>
@@ -18370,7 +18370,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" hidden="1">
       <c r="A188" t="s">
         <v>998</v>
       </c>
@@ -18442,7 +18442,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" hidden="1">
       <c r="A191" t="s">
         <v>1014</v>
       </c>
@@ -18491,7 +18491,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" hidden="1">
       <c r="A193" t="s">
         <v>1025</v>
       </c>
@@ -18563,7 +18563,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" hidden="1">
       <c r="A196" t="s">
         <v>1041</v>
       </c>
@@ -18592,7 +18592,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" hidden="1">
       <c r="A197" t="s">
         <v>1048</v>
       </c>
@@ -18618,7 +18618,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" hidden="1">
       <c r="A198" t="s">
         <v>1054</v>
       </c>
@@ -18713,7 +18713,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" hidden="1">
       <c r="A202" t="s">
         <v>1075</v>
       </c>
@@ -18739,7 +18739,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" hidden="1">
       <c r="A203" t="s">
         <v>1081</v>
       </c>
@@ -18765,7 +18765,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" hidden="1">
       <c r="A204" t="s">
         <v>1087</v>
       </c>
@@ -18791,7 +18791,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" hidden="1">
       <c r="A205" t="s">
         <v>1093</v>
       </c>
@@ -18863,7 +18863,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" hidden="1">
       <c r="A208" t="s">
         <v>1109</v>
       </c>
@@ -18912,7 +18912,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" hidden="1">
       <c r="A210" t="s">
         <v>1120</v>
       </c>
@@ -19007,7 +19007,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" hidden="1">
       <c r="A214" t="s">
         <v>1141</v>
       </c>
@@ -19102,7 +19102,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" hidden="1">
       <c r="A218" t="s">
         <v>1162</v>
       </c>
@@ -19151,7 +19151,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" hidden="1">
       <c r="A220" t="s">
         <v>1173</v>
       </c>
@@ -19177,7 +19177,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" hidden="1">
       <c r="A221" t="s">
         <v>1179</v>
       </c>
@@ -19226,7 +19226,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" hidden="1">
       <c r="A223" t="s">
         <v>1190</v>
       </c>
@@ -19275,7 +19275,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" hidden="1">
       <c r="A225" t="s">
         <v>1201</v>
       </c>
@@ -19416,7 +19416,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" hidden="1">
       <c r="A231" t="s">
         <v>1232</v>
       </c>
@@ -19465,7 +19465,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" hidden="1">
       <c r="A233" t="s">
         <v>1243</v>
       </c>
@@ -19537,7 +19537,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" hidden="1">
       <c r="A236" t="s">
         <v>1259</v>
       </c>
@@ -19701,7 +19701,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" hidden="1">
       <c r="A243" t="s">
         <v>1295</v>
       </c>
@@ -19750,7 +19750,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" hidden="1">
       <c r="A245" t="s">
         <v>1306</v>
       </c>
@@ -19799,7 +19799,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" hidden="1">
       <c r="A247" t="s">
         <v>1317</v>
       </c>
@@ -19825,7 +19825,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" hidden="1">
       <c r="A248" t="s">
         <v>1323</v>
       </c>
@@ -19874,7 +19874,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" hidden="1">
       <c r="A250" t="s">
         <v>1334</v>
       </c>
@@ -19923,7 +19923,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" hidden="1">
       <c r="A252" t="s">
         <v>1345</v>
       </c>
@@ -19972,7 +19972,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" hidden="1">
       <c r="A254" t="s">
         <v>1356</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" hidden="1">
       <c r="A255" t="s">
         <v>1362</v>
       </c>
@@ -20024,7 +20024,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" hidden="1">
       <c r="A256" t="s">
         <v>1368</v>
       </c>
@@ -20073,7 +20073,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" hidden="1">
       <c r="A258" t="s">
         <v>1379</v>
       </c>
@@ -20145,7 +20145,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" hidden="1">
       <c r="A261" t="s">
         <v>1395</v>
       </c>
@@ -20171,7 +20171,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" hidden="1">
       <c r="A262" t="s">
         <v>1401</v>
       </c>
@@ -20197,7 +20197,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" hidden="1">
       <c r="A263" t="s">
         <v>1407</v>
       </c>
@@ -20384,7 +20384,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" hidden="1">
       <c r="A271" t="s">
         <v>1448</v>
       </c>
@@ -20456,7 +20456,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" hidden="1">
       <c r="A274" t="s">
         <v>1464</v>
       </c>
@@ -20482,7 +20482,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" hidden="1">
       <c r="A275" t="s">
         <v>1470</v>
       </c>
@@ -20508,7 +20508,7 @@
         <v>1475</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" hidden="1">
       <c r="A276" t="s">
         <v>1476</v>
       </c>
@@ -20534,7 +20534,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" hidden="1">
       <c r="A277" t="s">
         <v>1482</v>
       </c>
@@ -20583,7 +20583,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" hidden="1">
       <c r="A279" t="s">
         <v>1493</v>
       </c>
@@ -20632,7 +20632,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" hidden="1">
       <c r="A281" t="s">
         <v>1504</v>
       </c>
@@ -20658,7 +20658,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" hidden="1">
       <c r="A282" t="s">
         <v>1510</v>
       </c>
@@ -20684,7 +20684,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" hidden="1">
       <c r="A283" t="s">
         <v>1516</v>
       </c>
@@ -20710,7 +20710,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" hidden="1">
       <c r="A284" t="s">
         <v>1522</v>
       </c>
@@ -20759,7 +20759,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" hidden="1">
       <c r="A286" t="s">
         <v>1533</v>
       </c>
@@ -20808,7 +20808,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" hidden="1">
       <c r="A288" t="s">
         <v>1544</v>
       </c>
@@ -20834,7 +20834,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" hidden="1">
       <c r="A289" t="s">
         <v>1550</v>
       </c>
@@ -20860,7 +20860,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" hidden="1">
       <c r="A290" t="s">
         <v>1556</v>
       </c>
@@ -20909,7 +20909,7 @@
         <v>1566</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" hidden="1">
       <c r="A292" t="s">
         <v>1567</v>
       </c>
@@ -20958,7 +20958,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" hidden="1">
       <c r="A294" t="s">
         <v>1578</v>
       </c>
@@ -20984,7 +20984,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" hidden="1">
       <c r="A295" t="s">
         <v>1584</v>
       </c>
@@ -21033,7 +21033,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" hidden="1">
       <c r="A297" t="s">
         <v>1595</v>
       </c>
@@ -21059,7 +21059,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" hidden="1">
       <c r="A298" t="s">
         <v>1601</v>
       </c>
@@ -21085,7 +21085,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" hidden="1">
       <c r="A299" t="s">
         <v>1607</v>
       </c>
@@ -21160,7 +21160,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" hidden="1">
       <c r="A302" t="s">
         <v>1624</v>
       </c>
@@ -21186,7 +21186,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" hidden="1">
       <c r="A303" t="s">
         <v>1630</v>
       </c>
@@ -21212,7 +21212,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" hidden="1">
       <c r="A304" t="s">
         <v>1636</v>
       </c>
@@ -21238,7 +21238,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" hidden="1">
       <c r="A305" t="s">
         <v>1642</v>
       </c>
@@ -21287,7 +21287,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" hidden="1">
       <c r="A307" t="s">
         <v>1653</v>
       </c>
@@ -21336,7 +21336,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" hidden="1">
       <c r="A309" t="s">
         <v>1664</v>
       </c>
@@ -21362,7 +21362,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" hidden="1">
       <c r="A310" t="s">
         <v>1670</v>
       </c>
@@ -21388,7 +21388,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" hidden="1">
       <c r="A311" t="s">
         <v>1676</v>
       </c>
@@ -21414,7 +21414,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" hidden="1">
       <c r="A312" t="s">
         <v>1682</v>
       </c>
@@ -21440,7 +21440,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" hidden="1">
       <c r="A313" t="s">
         <v>1688</v>
       </c>
@@ -21466,7 +21466,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" hidden="1">
       <c r="A314" t="s">
         <v>1694</v>
       </c>
@@ -21538,7 +21538,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" hidden="1">
       <c r="A317" t="s">
         <v>1710</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" hidden="1">
       <c r="A318" t="s">
         <v>1716</v>
       </c>
@@ -21590,7 +21590,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" hidden="1">
       <c r="A319" t="s">
         <v>1722</v>
       </c>
@@ -21639,7 +21639,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" hidden="1">
       <c r="A321" t="s">
         <v>1733</v>
       </c>
@@ -21665,7 +21665,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" hidden="1">
       <c r="A322" t="s">
         <v>1739</v>
       </c>
@@ -21714,7 +21714,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" hidden="1">
       <c r="A324" t="s">
         <v>1750</v>
       </c>
@@ -21740,7 +21740,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" hidden="1">
       <c r="A325" t="s">
         <v>1756</v>
       </c>
@@ -21861,7 +21861,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" hidden="1">
       <c r="A330" t="s">
         <v>1783</v>
       </c>
@@ -21887,7 +21887,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" hidden="1">
       <c r="A331" t="s">
         <v>1789</v>
       </c>
@@ -21913,7 +21913,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" hidden="1">
       <c r="A332" t="s">
         <v>1795</v>
       </c>
@@ -21939,7 +21939,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" hidden="1">
       <c r="A333" t="s">
         <v>1801</v>
       </c>
@@ -21965,7 +21965,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" hidden="1">
       <c r="A334" t="s">
         <v>1807</v>
       </c>
@@ -22014,7 +22014,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" hidden="1">
       <c r="A336" t="s">
         <v>1818</v>
       </c>
@@ -22040,7 +22040,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" hidden="1">
       <c r="A337" t="s">
         <v>1824</v>
       </c>
@@ -22089,7 +22089,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" hidden="1">
       <c r="A339" t="s">
         <v>1835</v>
       </c>
@@ -22138,7 +22138,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" hidden="1">
       <c r="A341" t="s">
         <v>1846</v>
       </c>
@@ -22164,7 +22164,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" hidden="1">
       <c r="A342" t="s">
         <v>1852</v>
       </c>
@@ -22216,7 +22216,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" hidden="1">
       <c r="A344" t="s">
         <v>1864</v>
       </c>
@@ -22242,7 +22242,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" hidden="1">
       <c r="A345" t="s">
         <v>1870</v>
       </c>
@@ -22268,7 +22268,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" hidden="1">
       <c r="A346" t="s">
         <v>1876</v>
       </c>
@@ -22294,7 +22294,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" hidden="1">
       <c r="A347" t="s">
         <v>1882</v>
       </c>
@@ -22320,7 +22320,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" hidden="1">
       <c r="A348" t="s">
         <v>1888</v>
       </c>
@@ -22346,7 +22346,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" hidden="1">
       <c r="A349" t="s">
         <v>1894</v>
       </c>
@@ -22395,7 +22395,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" hidden="1">
       <c r="A351" t="s">
         <v>1905</v>
       </c>
@@ -22421,7 +22421,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" hidden="1">
       <c r="A352" t="s">
         <v>1911</v>
       </c>
@@ -22447,7 +22447,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" hidden="1">
       <c r="A353" t="s">
         <v>1917</v>
       </c>
@@ -22588,7 +22588,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" hidden="1">
       <c r="A359" t="s">
         <v>1948</v>
       </c>
@@ -22614,7 +22614,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" hidden="1">
       <c r="A360" t="s">
         <v>1954</v>
       </c>
@@ -22663,7 +22663,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" hidden="1">
       <c r="A362" t="s">
         <v>1965</v>
       </c>
@@ -22692,7 +22692,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" hidden="1">
       <c r="A363" t="s">
         <v>1972</v>
       </c>
@@ -22764,7 +22764,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" hidden="1">
       <c r="A366" t="s">
         <v>1988</v>
       </c>
@@ -22790,7 +22790,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" hidden="1">
       <c r="A367" t="s">
         <v>1994</v>
       </c>
@@ -22931,7 +22931,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" hidden="1">
       <c r="A373" t="s">
         <v>2025</v>
       </c>
@@ -23003,7 +23003,7 @@
         <v>2040</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" hidden="1">
       <c r="A376" t="s">
         <v>2041</v>
       </c>
@@ -23029,7 +23029,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="377">
+    <row r="377" hidden="1">
       <c r="A377" t="s">
         <v>2047</v>
       </c>
@@ -23055,7 +23055,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" hidden="1">
       <c r="A378" t="s">
         <v>2053</v>
       </c>
@@ -23081,7 +23081,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" hidden="1">
       <c r="A379" t="s">
         <v>2059</v>
       </c>
@@ -23153,7 +23153,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" hidden="1">
       <c r="A382" t="s">
         <v>2075</v>
       </c>
@@ -23225,7 +23225,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" hidden="1">
       <c r="A385" t="s">
         <v>2091</v>
       </c>
@@ -23251,7 +23251,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="386">
+    <row r="386" hidden="1">
       <c r="A386" t="s">
         <v>2097</v>
       </c>
@@ -23323,7 +23323,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="389">
+    <row r="389" hidden="1">
       <c r="A389" t="s">
         <v>2113</v>
       </c>
@@ -23349,7 +23349,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" hidden="1">
       <c r="A390" t="s">
         <v>2119</v>
       </c>
@@ -23375,7 +23375,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="391">
+    <row r="391" hidden="1">
       <c r="A391" t="s">
         <v>2125</v>
       </c>
@@ -23401,7 +23401,7 @@
         <v>2130</v>
       </c>
     </row>
-    <row r="392">
+    <row r="392" hidden="1">
       <c r="A392" t="s">
         <v>2131</v>
       </c>
@@ -23427,7 +23427,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="393">
+    <row r="393" hidden="1">
       <c r="A393" t="s">
         <v>2137</v>
       </c>
@@ -23453,7 +23453,7 @@
         <v>2142</v>
       </c>
     </row>
-    <row r="394">
+    <row r="394" hidden="1">
       <c r="A394" t="s">
         <v>2143</v>
       </c>
@@ -23479,7 +23479,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="395">
+    <row r="395" hidden="1">
       <c r="A395" t="s">
         <v>2149</v>
       </c>
@@ -23505,7 +23505,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="396">
+    <row r="396" hidden="1">
       <c r="A396" t="s">
         <v>2155</v>
       </c>
@@ -23531,7 +23531,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" hidden="1">
       <c r="A397" t="s">
         <v>2161</v>
       </c>
@@ -23603,7 +23603,7 @@
         <v>2176</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" hidden="1">
       <c r="A400" t="s">
         <v>2177</v>
       </c>
@@ -23629,7 +23629,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="401">
+    <row r="401" hidden="1">
       <c r="A401" t="s">
         <v>2183</v>
       </c>
@@ -23747,7 +23747,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" hidden="1">
       <c r="A406" t="s">
         <v>2209</v>
       </c>
@@ -23773,7 +23773,7 @@
         <v>2214</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" hidden="1">
       <c r="A407" t="s">
         <v>2215</v>
       </c>
@@ -23822,7 +23822,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="409">
+    <row r="409" hidden="1">
       <c r="A409" t="s">
         <v>2226</v>
       </c>
@@ -23917,7 +23917,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" hidden="1">
       <c r="A413" t="s">
         <v>2247</v>
       </c>
@@ -24012,7 +24012,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="417">
+    <row r="417" hidden="1">
       <c r="A417" t="s">
         <v>2268</v>
       </c>
@@ -24038,7 +24038,7 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" hidden="1">
       <c r="A418" t="s">
         <v>2274</v>
       </c>
@@ -24110,7 +24110,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="421">
+    <row r="421" hidden="1">
       <c r="A421" t="s">
         <v>2290</v>
       </c>
@@ -24136,7 +24136,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" hidden="1">
       <c r="A422" t="s">
         <v>2296</v>
       </c>
@@ -24185,7 +24185,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" hidden="1">
       <c r="A424" t="s">
         <v>2307</v>
       </c>
@@ -24234,7 +24234,7 @@
         <v>2317</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" hidden="1">
       <c r="A426" t="s">
         <v>2318</v>
       </c>
@@ -24283,7 +24283,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" hidden="1">
       <c r="A428" t="s">
         <v>2329</v>
       </c>
@@ -24355,7 +24355,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="431">
+    <row r="431" hidden="1">
       <c r="A431" t="s">
         <v>2345</v>
       </c>
@@ -24381,7 +24381,7 @@
         <v>2350</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" hidden="1">
       <c r="A432" t="s">
         <v>2351</v>
       </c>
@@ -24407,7 +24407,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="433">
+    <row r="433" hidden="1">
       <c r="A433" t="s">
         <v>2357</v>
       </c>
@@ -24433,7 +24433,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" hidden="1">
       <c r="A434" t="s">
         <v>2363</v>
       </c>
@@ -24459,7 +24459,7 @@
         <v>2368</v>
       </c>
     </row>
-    <row r="435">
+    <row r="435" hidden="1">
       <c r="A435" t="s">
         <v>2369</v>
       </c>
@@ -24485,7 +24485,7 @@
         <v>2374</v>
       </c>
     </row>
-    <row r="436">
+    <row r="436" hidden="1">
       <c r="A436" t="s">
         <v>2375</v>
       </c>
@@ -24534,7 +24534,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" hidden="1">
       <c r="A438" t="s">
         <v>2386</v>
       </c>
@@ -24560,7 +24560,7 @@
         <v>2391</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" hidden="1">
       <c r="A439" t="s">
         <v>2392</v>
       </c>
@@ -24586,7 +24586,7 @@
         <v>2397</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" hidden="1">
       <c r="A440" t="s">
         <v>2398</v>
       </c>
@@ -24612,7 +24612,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" hidden="1">
       <c r="A441" t="s">
         <v>2404</v>
       </c>
@@ -24638,7 +24638,7 @@
         <v>2409</v>
       </c>
     </row>
-    <row r="442">
+    <row r="442" hidden="1">
       <c r="A442" t="s">
         <v>2410</v>
       </c>
@@ -24664,7 +24664,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="443">
+    <row r="443" hidden="1">
       <c r="A443" t="s">
         <v>2416</v>
       </c>
@@ -24736,7 +24736,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" hidden="1">
       <c r="A446" t="s">
         <v>2432</v>
       </c>
@@ -24785,7 +24785,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="448">
+    <row r="448" hidden="1">
       <c r="A448" t="s">
         <v>2443</v>
       </c>
@@ -24834,7 +24834,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" hidden="1">
       <c r="A450" t="s">
         <v>2454</v>
       </c>
@@ -24860,7 +24860,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" hidden="1">
       <c r="A451" t="s">
         <v>2460</v>
       </c>
@@ -24886,7 +24886,7 @@
         <v>2465</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" hidden="1">
       <c r="A452" t="s">
         <v>2466</v>
       </c>
@@ -24912,7 +24912,7 @@
         <v>2471</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" hidden="1">
       <c r="A453" t="s">
         <v>2472</v>
       </c>
@@ -24961,7 +24961,7 @@
         <v>2482</v>
       </c>
     </row>
-    <row r="455">
+    <row r="455" hidden="1">
       <c r="A455" t="s">
         <v>2483</v>
       </c>
@@ -24987,7 +24987,7 @@
         <v>2488</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" hidden="1">
       <c r="A456" t="s">
         <v>2489</v>
       </c>
@@ -25059,7 +25059,7 @@
         <v>2504</v>
       </c>
     </row>
-    <row r="459">
+    <row r="459" hidden="1">
       <c r="A459" t="s">
         <v>2505</v>
       </c>
@@ -25085,7 +25085,7 @@
         <v>2510</v>
       </c>
     </row>
-    <row r="460">
+    <row r="460" hidden="1">
       <c r="A460" t="s">
         <v>2511</v>
       </c>
@@ -25111,7 +25111,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" hidden="1">
       <c r="A461" t="s">
         <v>2517</v>
       </c>
@@ -25137,7 +25137,7 @@
         <v>2522</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" hidden="1">
       <c r="A462" t="s">
         <v>2523</v>
       </c>
@@ -25163,7 +25163,7 @@
         <v>2528</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" hidden="1">
       <c r="A463" t="s">
         <v>2529</v>
       </c>
@@ -25189,7 +25189,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="464">
+    <row r="464" hidden="1">
       <c r="A464" t="s">
         <v>2535</v>
       </c>
@@ -25284,7 +25284,7 @@
         <v>2555</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" hidden="1">
       <c r="A468" t="s">
         <v>2556</v>
       </c>
@@ -25310,7 +25310,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="469">
+    <row r="469" hidden="1">
       <c r="A469" t="s">
         <v>2562</v>
       </c>
@@ -25336,7 +25336,7 @@
         <v>2567</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" hidden="1">
       <c r="A470" t="s">
         <v>2568</v>
       </c>
@@ -25362,7 +25362,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" hidden="1">
       <c r="A471" t="s">
         <v>2574</v>
       </c>
@@ -25434,7 +25434,7 @@
         <v>2589</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" hidden="1">
       <c r="A474" t="s">
         <v>2590</v>
       </c>
@@ -25483,7 +25483,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" hidden="1">
       <c r="A476" t="s">
         <v>2601</v>
       </c>
@@ -25509,7 +25509,7 @@
         <v>2606</v>
       </c>
     </row>
-    <row r="477">
+    <row r="477" hidden="1">
       <c r="A477" t="s">
         <v>2607</v>
       </c>
@@ -25535,7 +25535,7 @@
         <v>2612</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" hidden="1">
       <c r="A478" t="s">
         <v>2613</v>
       </c>
@@ -25561,7 +25561,7 @@
         <v>2618</v>
       </c>
     </row>
-    <row r="479">
+    <row r="479" hidden="1">
       <c r="A479" t="s">
         <v>2619</v>
       </c>
@@ -25610,7 +25610,7 @@
         <v>2629</v>
       </c>
     </row>
-    <row r="481">
+    <row r="481" hidden="1">
       <c r="A481" t="s">
         <v>2630</v>
       </c>
@@ -25636,7 +25636,7 @@
         <v>2635</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" hidden="1">
       <c r="A482" t="s">
         <v>2636</v>
       </c>
@@ -25685,7 +25685,7 @@
         <v>2646</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" hidden="1">
       <c r="A484" t="s">
         <v>2647</v>
       </c>
@@ -25757,7 +25757,7 @@
         <v>2662</v>
       </c>
     </row>
-    <row r="487">
+    <row r="487" hidden="1">
       <c r="A487" t="s">
         <v>2663</v>
       </c>
@@ -25806,7 +25806,7 @@
         <v>2673</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" hidden="1">
       <c r="A489" t="s">
         <v>2674</v>
       </c>
@@ -25832,7 +25832,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" hidden="1">
       <c r="A490" t="s">
         <v>2680</v>
       </c>
@@ -25858,7 +25858,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="491">
+    <row r="491" hidden="1">
       <c r="A491" t="s">
         <v>2686</v>
       </c>
@@ -25907,7 +25907,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="493">
+    <row r="493" hidden="1">
       <c r="A493" t="s">
         <v>2697</v>
       </c>
@@ -25933,7 +25933,7 @@
         <v>2702</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" hidden="1">
       <c r="A494" t="s">
         <v>2703</v>
       </c>
@@ -26005,7 +26005,7 @@
         <v>2718</v>
       </c>
     </row>
-    <row r="497">
+    <row r="497" hidden="1">
       <c r="A497" t="s">
         <v>2719</v>
       </c>
@@ -26054,7 +26054,7 @@
         <v>2729</v>
       </c>
     </row>
-    <row r="499">
+    <row r="499" hidden="1">
       <c r="A499" t="s">
         <v>2730</v>
       </c>
@@ -26080,7 +26080,7 @@
         <v>2735</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" hidden="1">
       <c r="A500" t="s">
         <v>2736</v>
       </c>
@@ -26106,7 +26106,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" hidden="1">
       <c r="A501" t="s">
         <v>2742</v>
       </c>
@@ -26201,7 +26201,7 @@
         <v>2762</v>
       </c>
     </row>
-    <row r="505">
+    <row r="505" hidden="1">
       <c r="A505" t="s">
         <v>2763</v>
       </c>
@@ -26227,7 +26227,7 @@
         <v>2768</v>
       </c>
     </row>
-    <row r="506">
+    <row r="506" hidden="1">
       <c r="A506" t="s">
         <v>2769</v>
       </c>
@@ -26253,7 +26253,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="507">
+    <row r="507" hidden="1">
       <c r="A507" t="s">
         <v>2775</v>
       </c>
@@ -26351,7 +26351,7 @@
         <v>2796</v>
       </c>
     </row>
-    <row r="511">
+    <row r="511" hidden="1">
       <c r="A511" t="s">
         <v>2797</v>
       </c>
@@ -26400,7 +26400,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" hidden="1">
       <c r="A513" t="s">
         <v>2808</v>
       </c>
@@ -26449,7 +26449,7 @@
         <v>2818</v>
       </c>
     </row>
-    <row r="515">
+    <row r="515" hidden="1">
       <c r="A515" t="s">
         <v>2819</v>
       </c>
@@ -26498,7 +26498,7 @@
         <v>2829</v>
       </c>
     </row>
-    <row r="517">
+    <row r="517" hidden="1">
       <c r="A517" t="s">
         <v>2830</v>
       </c>
@@ -26547,7 +26547,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="519">
+    <row r="519" hidden="1">
       <c r="A519" t="s">
         <v>2841</v>
       </c>
@@ -26642,7 +26642,7 @@
         <v>2861</v>
       </c>
     </row>
-    <row r="523">
+    <row r="523" hidden="1">
       <c r="A523" t="s">
         <v>2862</v>
       </c>
@@ -26668,7 +26668,7 @@
         <v>2867</v>
       </c>
     </row>
-    <row r="524">
+    <row r="524" hidden="1">
       <c r="A524" t="s">
         <v>2868</v>
       </c>
@@ -26694,7 +26694,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="525">
+    <row r="525" hidden="1">
       <c r="A525" t="s">
         <v>2874</v>
       </c>
@@ -26743,7 +26743,7 @@
         <v>2884</v>
       </c>
     </row>
-    <row r="527">
+    <row r="527" hidden="1">
       <c r="A527" t="s">
         <v>2885</v>
       </c>
@@ -26792,7 +26792,7 @@
         <v>2895</v>
       </c>
     </row>
-    <row r="529">
+    <row r="529" hidden="1">
       <c r="A529" t="s">
         <v>2896</v>
       </c>
@@ -26818,7 +26818,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="530">
+    <row r="530" hidden="1">
       <c r="A530" t="s">
         <v>2902</v>
       </c>
@@ -26890,7 +26890,7 @@
         <v>2917</v>
       </c>
     </row>
-    <row r="533">
+    <row r="533" hidden="1">
       <c r="A533" t="s">
         <v>2918</v>
       </c>
@@ -26916,7 +26916,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="534">
+    <row r="534" hidden="1">
       <c r="A534" t="s">
         <v>2924</v>
       </c>
@@ -26942,7 +26942,7 @@
         <v>2929</v>
       </c>
     </row>
-    <row r="535">
+    <row r="535" hidden="1">
       <c r="A535" t="s">
         <v>2930</v>
       </c>
@@ -26968,7 +26968,7 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="536">
+    <row r="536" hidden="1">
       <c r="A536" t="s">
         <v>2936</v>
       </c>
@@ -26994,7 +26994,7 @@
         <v>2941</v>
       </c>
     </row>
-    <row r="537">
+    <row r="537" hidden="1">
       <c r="A537" t="s">
         <v>2942</v>
       </c>
@@ -27020,7 +27020,7 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="538">
+    <row r="538" hidden="1">
       <c r="A538" t="s">
         <v>2948</v>
       </c>
@@ -27069,7 +27069,7 @@
         <v>2958</v>
       </c>
     </row>
-    <row r="540">
+    <row r="540" hidden="1">
       <c r="A540" t="s">
         <v>2959</v>
       </c>
@@ -27118,7 +27118,7 @@
         <v>2969</v>
       </c>
     </row>
-    <row r="542">
+    <row r="542" hidden="1">
       <c r="A542" t="s">
         <v>2970</v>
       </c>
@@ -27144,7 +27144,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="543">
+    <row r="543" hidden="1">
       <c r="A543" t="s">
         <v>2976</v>
       </c>
@@ -27170,7 +27170,7 @@
         <v>2981</v>
       </c>
     </row>
-    <row r="544">
+    <row r="544" hidden="1">
       <c r="A544" t="s">
         <v>2982</v>
       </c>
@@ -27219,7 +27219,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="546">
+    <row r="546" hidden="1">
       <c r="A546" t="s">
         <v>2993</v>
       </c>
@@ -27245,7 +27245,7 @@
         <v>2998</v>
       </c>
     </row>
-    <row r="547">
+    <row r="547" hidden="1">
       <c r="A547" t="s">
         <v>2999</v>
       </c>
@@ -27271,7 +27271,7 @@
         <v>3004</v>
       </c>
     </row>
-    <row r="548">
+    <row r="548" hidden="1">
       <c r="A548" t="s">
         <v>3005</v>
       </c>
@@ -27297,7 +27297,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="549">
+    <row r="549" hidden="1">
       <c r="A549" t="s">
         <v>3011</v>
       </c>
@@ -27346,7 +27346,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="551">
+    <row r="551" hidden="1">
       <c r="A551" t="s">
         <v>3022</v>
       </c>
@@ -27395,7 +27395,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="553">
+    <row r="553" hidden="1">
       <c r="A553" t="s">
         <v>3033</v>
       </c>
@@ -27467,7 +27467,7 @@
         <v>3048</v>
       </c>
     </row>
-    <row r="556">
+    <row r="556" hidden="1">
       <c r="A556" t="s">
         <v>3049</v>
       </c>
@@ -27516,7 +27516,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="558">
+    <row r="558" hidden="1">
       <c r="A558" t="s">
         <v>3060</v>
       </c>
@@ -27542,7 +27542,7 @@
         <v>3065</v>
       </c>
     </row>
-    <row r="559">
+    <row r="559" hidden="1">
       <c r="A559" t="s">
         <v>3066</v>
       </c>
@@ -27591,7 +27591,7 @@
         <v>3076</v>
       </c>
     </row>
-    <row r="561">
+    <row r="561" hidden="1">
       <c r="A561" t="s">
         <v>3077</v>
       </c>
@@ -27617,7 +27617,7 @@
         <v>3082</v>
       </c>
     </row>
-    <row r="562">
+    <row r="562" hidden="1">
       <c r="A562" t="s">
         <v>3083</v>
       </c>
@@ -27643,7 +27643,7 @@
         <v>3088</v>
       </c>
     </row>
-    <row r="563">
+    <row r="563" hidden="1">
       <c r="A563" t="s">
         <v>3089</v>
       </c>
@@ -27692,7 +27692,7 @@
         <v>3099</v>
       </c>
     </row>
-    <row r="565">
+    <row r="565" hidden="1">
       <c r="A565" t="s">
         <v>3100</v>
       </c>
@@ -27718,7 +27718,7 @@
         <v>3105</v>
       </c>
     </row>
-    <row r="566">
+    <row r="566" hidden="1">
       <c r="A566" t="s">
         <v>3106</v>
       </c>
@@ -27770,7 +27770,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="568">
+    <row r="568" hidden="1">
       <c r="A568" t="s">
         <v>3118</v>
       </c>
@@ -27819,7 +27819,7 @@
         <v>3128</v>
       </c>
     </row>
-    <row r="570">
+    <row r="570" hidden="1">
       <c r="A570" t="s">
         <v>3129</v>
       </c>
@@ -27845,7 +27845,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="571">
+    <row r="571" hidden="1">
       <c r="A571" t="s">
         <v>3135</v>
       </c>
@@ -27871,7 +27871,7 @@
         <v>3140</v>
       </c>
     </row>
-    <row r="572">
+    <row r="572" hidden="1">
       <c r="A572" t="s">
         <v>3141</v>
       </c>
@@ -27923,7 +27923,7 @@
         <v>3152</v>
       </c>
     </row>
-    <row r="574">
+    <row r="574" hidden="1">
       <c r="A574" t="s">
         <v>3153</v>
       </c>
@@ -27949,7 +27949,7 @@
         <v>3158</v>
       </c>
     </row>
-    <row r="575">
+    <row r="575" hidden="1">
       <c r="A575" t="s">
         <v>3159</v>
       </c>
@@ -27998,7 +27998,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="577">
+    <row r="577" hidden="1">
       <c r="A577" t="s">
         <v>3170</v>
       </c>
@@ -28024,7 +28024,7 @@
         <v>3175</v>
       </c>
     </row>
-    <row r="578">
+    <row r="578" hidden="1">
       <c r="A578" t="s">
         <v>3176</v>
       </c>
@@ -28050,7 +28050,7 @@
         <v>3181</v>
       </c>
     </row>
-    <row r="579">
+    <row r="579" hidden="1">
       <c r="A579" t="s">
         <v>3182</v>
       </c>
@@ -28076,7 +28076,7 @@
         <v>3187</v>
       </c>
     </row>
-    <row r="580">
+    <row r="580" hidden="1">
       <c r="A580" t="s">
         <v>3188</v>
       </c>
@@ -28102,7 +28102,7 @@
         <v>3193</v>
       </c>
     </row>
-    <row r="581">
+    <row r="581" hidden="1">
       <c r="A581" t="s">
         <v>3194</v>
       </c>
@@ -28174,7 +28174,7 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="584">
+    <row r="584" hidden="1">
       <c r="A584" t="s">
         <v>3210</v>
       </c>
@@ -28200,7 +28200,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="585">
+    <row r="585" hidden="1">
       <c r="A585" t="s">
         <v>3216</v>
       </c>
@@ -28456,7 +28456,7 @@
         <v>3271</v>
       </c>
     </row>
-    <row r="596">
+    <row r="596" hidden="1">
       <c r="A596" t="s">
         <v>3272</v>
       </c>
@@ -28597,7 +28597,7 @@
         <v>3302</v>
       </c>
     </row>
-    <row r="602">
+    <row r="602" hidden="1">
       <c r="A602" t="s">
         <v>3303</v>
       </c>
@@ -28715,7 +28715,7 @@
         <v>3328</v>
       </c>
     </row>
-    <row r="607">
+    <row r="607" hidden="1">
       <c r="A607" t="s">
         <v>3329</v>
       </c>
@@ -28741,7 +28741,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="608">
+    <row r="608" hidden="1">
       <c r="A608" t="s">
         <v>3335</v>
       </c>
@@ -28767,7 +28767,7 @@
         <v>3340</v>
       </c>
     </row>
-    <row r="609">
+    <row r="609" hidden="1">
       <c r="A609" t="s">
         <v>3341</v>
       </c>
@@ -28793,7 +28793,7 @@
         <v>3346</v>
       </c>
     </row>
-    <row r="610">
+    <row r="610" hidden="1">
       <c r="A610" t="s">
         <v>3347</v>
       </c>
@@ -28819,7 +28819,7 @@
         <v>3352</v>
       </c>
     </row>
-    <row r="611">
+    <row r="611" hidden="1">
       <c r="A611" t="s">
         <v>3353</v>
       </c>
@@ -28845,7 +28845,7 @@
         <v>3358</v>
       </c>
     </row>
-    <row r="612">
+    <row r="612" hidden="1">
       <c r="A612" t="s">
         <v>3359</v>
       </c>
@@ -28871,7 +28871,7 @@
         <v>3364</v>
       </c>
     </row>
-    <row r="613">
+    <row r="613" hidden="1">
       <c r="A613" t="s">
         <v>3365</v>
       </c>
@@ -28943,7 +28943,7 @@
         <v>3380</v>
       </c>
     </row>
-    <row r="616">
+    <row r="616" hidden="1">
       <c r="A616" t="s">
         <v>3381</v>
       </c>
@@ -29015,7 +29015,7 @@
         <v>3396</v>
       </c>
     </row>
-    <row r="619">
+    <row r="619" hidden="1">
       <c r="A619" t="s">
         <v>3397</v>
       </c>
@@ -29041,7 +29041,7 @@
         <v>3402</v>
       </c>
     </row>
-    <row r="620">
+    <row r="620" hidden="1">
       <c r="A620" t="s">
         <v>3403</v>
       </c>
@@ -29067,7 +29067,7 @@
         <v>3408</v>
       </c>
     </row>
-    <row r="621">
+    <row r="621" hidden="1">
       <c r="A621" t="s">
         <v>3409</v>
       </c>
@@ -29093,7 +29093,7 @@
         <v>3414</v>
       </c>
     </row>
-    <row r="622">
+    <row r="622" hidden="1">
       <c r="A622" t="s">
         <v>3415</v>
       </c>
@@ -29142,7 +29142,7 @@
         <v>3425</v>
       </c>
     </row>
-    <row r="624">
+    <row r="624" hidden="1">
       <c r="A624" t="s">
         <v>3426</v>
       </c>
@@ -29214,7 +29214,7 @@
         <v>3441</v>
       </c>
     </row>
-    <row r="627">
+    <row r="627" hidden="1">
       <c r="A627" t="s">
         <v>3442</v>
       </c>
@@ -29240,7 +29240,7 @@
         <v>3447</v>
       </c>
     </row>
-    <row r="628">
+    <row r="628" hidden="1">
       <c r="A628" t="s">
         <v>3448</v>
       </c>
@@ -29266,7 +29266,7 @@
         <v>3453</v>
       </c>
     </row>
-    <row r="629">
+    <row r="629" hidden="1">
       <c r="A629" t="s">
         <v>3454</v>
       </c>
@@ -29315,7 +29315,7 @@
         <v>3464</v>
       </c>
     </row>
-    <row r="631">
+    <row r="631" hidden="1">
       <c r="A631" t="s">
         <v>3465</v>
       </c>
@@ -29341,7 +29341,7 @@
         <v>3470</v>
       </c>
     </row>
-    <row r="632">
+    <row r="632" hidden="1">
       <c r="A632" t="s">
         <v>3471</v>
       </c>
@@ -29367,7 +29367,7 @@
         <v>3476</v>
       </c>
     </row>
-    <row r="633">
+    <row r="633" hidden="1">
       <c r="A633" t="s">
         <v>3477</v>
       </c>
@@ -29393,7 +29393,7 @@
         <v>3482</v>
       </c>
     </row>
-    <row r="634">
+    <row r="634" hidden="1">
       <c r="A634" t="s">
         <v>3483</v>
       </c>
@@ -29419,7 +29419,7 @@
         <v>3488</v>
       </c>
     </row>
-    <row r="635">
+    <row r="635" hidden="1">
       <c r="A635" t="s">
         <v>3489</v>
       </c>
@@ -29445,7 +29445,7 @@
         <v>3494</v>
       </c>
     </row>
-    <row r="636">
+    <row r="636" hidden="1">
       <c r="A636" t="s">
         <v>3495</v>
       </c>
@@ -29471,7 +29471,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="637">
+    <row r="637" hidden="1">
       <c r="A637" t="s">
         <v>3501</v>
       </c>
@@ -29497,7 +29497,7 @@
         <v>3506</v>
       </c>
     </row>
-    <row r="638">
+    <row r="638" hidden="1">
       <c r="A638" t="s">
         <v>3507</v>
       </c>
@@ -29523,7 +29523,7 @@
         <v>3512</v>
       </c>
     </row>
-    <row r="639">
+    <row r="639" hidden="1">
       <c r="A639" t="s">
         <v>3513</v>
       </c>
@@ -29549,7 +29549,7 @@
         <v>3518</v>
       </c>
     </row>
-    <row r="640">
+    <row r="640" hidden="1">
       <c r="A640" t="s">
         <v>3519</v>
       </c>
@@ -29575,7 +29575,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="641">
+    <row r="641" hidden="1">
       <c r="A641" t="s">
         <v>3525</v>
       </c>
@@ -29601,7 +29601,7 @@
         <v>3530</v>
       </c>
     </row>
-    <row r="642">
+    <row r="642" hidden="1">
       <c r="A642" t="s">
         <v>3531</v>
       </c>
@@ -29673,7 +29673,7 @@
         <v>3546</v>
       </c>
     </row>
-    <row r="645">
+    <row r="645" hidden="1">
       <c r="A645" t="s">
         <v>3547</v>
       </c>
@@ -29699,7 +29699,7 @@
         <v>3552</v>
       </c>
     </row>
-    <row r="646">
+    <row r="646" hidden="1">
       <c r="A646" t="s">
         <v>3553</v>
       </c>
@@ -29748,7 +29748,7 @@
         <v>3563</v>
       </c>
     </row>
-    <row r="648">
+    <row r="648" hidden="1">
       <c r="A648" t="s">
         <v>3564</v>
       </c>
@@ -29774,7 +29774,7 @@
         <v>3569</v>
       </c>
     </row>
-    <row r="649">
+    <row r="649" hidden="1">
       <c r="A649" t="s">
         <v>3570</v>
       </c>
@@ -29823,7 +29823,7 @@
         <v>3580</v>
       </c>
     </row>
-    <row r="651">
+    <row r="651" hidden="1">
       <c r="A651" t="s">
         <v>3581</v>
       </c>
@@ -29849,7 +29849,7 @@
         <v>3586</v>
       </c>
     </row>
-    <row r="652">
+    <row r="652" hidden="1">
       <c r="A652" t="s">
         <v>3587</v>
       </c>
@@ -29875,7 +29875,7 @@
         <v>3592</v>
       </c>
     </row>
-    <row r="653">
+    <row r="653" hidden="1">
       <c r="A653" t="s">
         <v>3593</v>
       </c>
@@ -29924,7 +29924,7 @@
         <v>3603</v>
       </c>
     </row>
-    <row r="655">
+    <row r="655" hidden="1">
       <c r="A655" t="s">
         <v>3604</v>
       </c>
@@ -29950,7 +29950,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="656">
+    <row r="656" hidden="1">
       <c r="A656" t="s">
         <v>3610</v>
       </c>
@@ -30022,7 +30022,7 @@
         <v>3625</v>
       </c>
     </row>
-    <row r="659">
+    <row r="659" hidden="1">
       <c r="A659" t="s">
         <v>3626</v>
       </c>
@@ -30048,7 +30048,7 @@
         <v>3631</v>
       </c>
     </row>
-    <row r="660">
+    <row r="660" hidden="1">
       <c r="A660" t="s">
         <v>3632</v>
       </c>
@@ -30074,7 +30074,7 @@
         <v>3637</v>
       </c>
     </row>
-    <row r="661">
+    <row r="661" hidden="1">
       <c r="A661" t="s">
         <v>3638</v>
       </c>
@@ -30100,7 +30100,7 @@
         <v>3643</v>
       </c>
     </row>
-    <row r="662">
+    <row r="662" hidden="1">
       <c r="A662" t="s">
         <v>3644</v>
       </c>
@@ -30126,7 +30126,7 @@
         <v>3649</v>
       </c>
     </row>
-    <row r="663">
+    <row r="663" hidden="1">
       <c r="A663" t="s">
         <v>3650</v>
       </c>
@@ -30152,7 +30152,7 @@
         <v>3655</v>
       </c>
     </row>
-    <row r="664">
+    <row r="664" hidden="1">
       <c r="A664" t="s">
         <v>3656</v>
       </c>
@@ -30178,7 +30178,7 @@
         <v>3661</v>
       </c>
     </row>
-    <row r="665">
+    <row r="665" hidden="1">
       <c r="A665" t="s">
         <v>3662</v>
       </c>
@@ -30204,7 +30204,7 @@
         <v>3667</v>
       </c>
     </row>
-    <row r="666">
+    <row r="666" hidden="1">
       <c r="A666" t="s">
         <v>3668</v>
       </c>
@@ -30230,7 +30230,7 @@
         <v>3673</v>
       </c>
     </row>
-    <row r="667">
+    <row r="667" hidden="1">
       <c r="A667" t="s">
         <v>3674</v>
       </c>
@@ -30256,7 +30256,7 @@
         <v>3679</v>
       </c>
     </row>
-    <row r="668">
+    <row r="668" hidden="1">
       <c r="A668" t="s">
         <v>3680</v>
       </c>
@@ -30282,7 +30282,7 @@
         <v>3685</v>
       </c>
     </row>
-    <row r="669">
+    <row r="669" hidden="1">
       <c r="A669" t="s">
         <v>3686</v>
       </c>
@@ -30331,7 +30331,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="671">
+    <row r="671" hidden="1">
       <c r="A671" t="s">
         <v>3697</v>
       </c>
@@ -30403,7 +30403,7 @@
         <v>3712</v>
       </c>
     </row>
-    <row r="674">
+    <row r="674" hidden="1">
       <c r="A674" t="s">
         <v>3713</v>
       </c>
@@ -30429,7 +30429,7 @@
         <v>3718</v>
       </c>
     </row>
-    <row r="675">
+    <row r="675" hidden="1">
       <c r="A675" t="s">
         <v>3719</v>
       </c>
@@ -30455,7 +30455,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="676">
+    <row r="676" hidden="1">
       <c r="A676" t="s">
         <v>3725</v>
       </c>
@@ -30481,7 +30481,7 @@
         <v>3730</v>
       </c>
     </row>
-    <row r="677">
+    <row r="677" hidden="1">
       <c r="A677" t="s">
         <v>3731</v>
       </c>
@@ -30507,7 +30507,7 @@
         <v>3736</v>
       </c>
     </row>
-    <row r="678">
+    <row r="678" hidden="1">
       <c r="A678" t="s">
         <v>3737</v>
       </c>
@@ -30533,7 +30533,7 @@
         <v>3742</v>
       </c>
     </row>
-    <row r="679">
+    <row r="679" hidden="1">
       <c r="A679" t="s">
         <v>3743</v>
       </c>
@@ -30559,7 +30559,7 @@
         <v>3748</v>
       </c>
     </row>
-    <row r="680">
+    <row r="680" hidden="1">
       <c r="A680" t="s">
         <v>3749</v>
       </c>
@@ -30585,7 +30585,7 @@
         <v>3754</v>
       </c>
     </row>
-    <row r="681">
+    <row r="681" hidden="1">
       <c r="A681" t="s">
         <v>3755</v>
       </c>
@@ -30611,7 +30611,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="682">
+    <row r="682" hidden="1">
       <c r="A682" t="s">
         <v>3761</v>
       </c>
@@ -30637,7 +30637,7 @@
         <v>3766</v>
       </c>
     </row>
-    <row r="683">
+    <row r="683" hidden="1">
       <c r="A683" t="s">
         <v>3767</v>
       </c>
@@ -30663,7 +30663,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="684">
+    <row r="684" hidden="1">
       <c r="A684" t="s">
         <v>3773</v>
       </c>
@@ -30689,7 +30689,7 @@
         <v>3778</v>
       </c>
     </row>
-    <row r="685">
+    <row r="685" hidden="1">
       <c r="A685" t="s">
         <v>3779</v>
       </c>
@@ -30715,7 +30715,7 @@
         <v>3784</v>
       </c>
     </row>
-    <row r="686">
+    <row r="686" hidden="1">
       <c r="A686" t="s">
         <v>3785</v>
       </c>
@@ -30741,7 +30741,7 @@
         <v>3790</v>
       </c>
     </row>
-    <row r="687">
+    <row r="687" hidden="1">
       <c r="A687" t="s">
         <v>3791</v>
       </c>
@@ -30767,7 +30767,7 @@
         <v>3796</v>
       </c>
     </row>
-    <row r="688">
+    <row r="688" hidden="1">
       <c r="A688" t="s">
         <v>3797</v>
       </c>
@@ -30816,7 +30816,7 @@
         <v>3807</v>
       </c>
     </row>
-    <row r="690">
+    <row r="690" hidden="1">
       <c r="A690" t="s">
         <v>3808</v>
       </c>
@@ -31279,7 +31279,7 @@
         <v>3908</v>
       </c>
     </row>
-    <row r="710">
+    <row r="710" hidden="1">
       <c r="A710" t="s">
         <v>3909</v>
       </c>
@@ -31305,7 +31305,7 @@
         <v>3914</v>
       </c>
     </row>
-    <row r="711">
+    <row r="711" hidden="1">
       <c r="A711" t="s">
         <v>3915</v>
       </c>
@@ -31331,7 +31331,7 @@
         <v>3920</v>
       </c>
     </row>
-    <row r="712">
+    <row r="712" hidden="1">
       <c r="A712" t="s">
         <v>3921</v>
       </c>
@@ -31357,7 +31357,7 @@
         <v>3926</v>
       </c>
     </row>
-    <row r="713">
+    <row r="713" hidden="1">
       <c r="A713" t="s">
         <v>3927</v>
       </c>
@@ -31383,7 +31383,7 @@
         <v>3932</v>
       </c>
     </row>
-    <row r="714">
+    <row r="714" hidden="1">
       <c r="A714" t="s">
         <v>3933</v>
       </c>
@@ -31409,7 +31409,7 @@
         <v>3938</v>
       </c>
     </row>
-    <row r="715">
+    <row r="715" hidden="1">
       <c r="A715" t="s">
         <v>3939</v>
       </c>
@@ -31435,7 +31435,7 @@
         <v>3944</v>
       </c>
     </row>
-    <row r="716">
+    <row r="716" hidden="1">
       <c r="A716" t="s">
         <v>3945</v>
       </c>
@@ -31461,7 +31461,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="717">
+    <row r="717" hidden="1">
       <c r="A717" t="s">
         <v>3951</v>
       </c>
@@ -31487,7 +31487,7 @@
         <v>3956</v>
       </c>
     </row>
-    <row r="718">
+    <row r="718" hidden="1">
       <c r="A718" t="s">
         <v>3957</v>
       </c>
@@ -31513,7 +31513,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="719">
+    <row r="719" hidden="1">
       <c r="A719" t="s">
         <v>3963</v>
       </c>
@@ -31562,7 +31562,7 @@
         <v>3973</v>
       </c>
     </row>
-    <row r="721">
+    <row r="721" hidden="1">
       <c r="A721" t="s">
         <v>3974</v>
       </c>
@@ -31588,7 +31588,7 @@
         <v>3979</v>
       </c>
     </row>
-    <row r="722">
+    <row r="722" hidden="1">
       <c r="A722" t="s">
         <v>3980</v>
       </c>
@@ -31614,7 +31614,7 @@
         <v>3985</v>
       </c>
     </row>
-    <row r="723">
+    <row r="723" hidden="1">
       <c r="A723" t="s">
         <v>3986</v>
       </c>
@@ -31640,7 +31640,7 @@
         <v>3991</v>
       </c>
     </row>
-    <row r="724">
+    <row r="724" hidden="1">
       <c r="A724" t="s">
         <v>3992</v>
       </c>
@@ -31666,7 +31666,7 @@
         <v>3997</v>
       </c>
     </row>
-    <row r="725">
+    <row r="725" hidden="1">
       <c r="A725" t="s">
         <v>3998</v>
       </c>
@@ -31738,7 +31738,7 @@
         <v>4013</v>
       </c>
     </row>
-    <row r="728">
+    <row r="728" hidden="1">
       <c r="A728" t="s">
         <v>4014</v>
       </c>
@@ -31764,7 +31764,7 @@
         <v>4019</v>
       </c>
     </row>
-    <row r="729">
+    <row r="729" hidden="1">
       <c r="A729" t="s">
         <v>4020</v>
       </c>
@@ -31790,7 +31790,7 @@
         <v>4025</v>
       </c>
     </row>
-    <row r="730">
+    <row r="730" hidden="1">
       <c r="A730" t="s">
         <v>4026</v>
       </c>
@@ -31816,7 +31816,7 @@
         <v>4031</v>
       </c>
     </row>
-    <row r="731">
+    <row r="731" hidden="1">
       <c r="A731" t="s">
         <v>4032</v>
       </c>
@@ -31842,7 +31842,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="732">
+    <row r="732" hidden="1">
       <c r="A732" t="s">
         <v>4038</v>
       </c>
@@ -31868,7 +31868,7 @@
         <v>4043</v>
       </c>
     </row>
-    <row r="733">
+    <row r="733" hidden="1">
       <c r="A733" t="s">
         <v>4044</v>
       </c>
@@ -31894,7 +31894,7 @@
         <v>4049</v>
       </c>
     </row>
-    <row r="734">
+    <row r="734" hidden="1">
       <c r="A734" t="s">
         <v>4050</v>
       </c>
@@ -31920,7 +31920,7 @@
         <v>4055</v>
       </c>
     </row>
-    <row r="735">
+    <row r="735" hidden="1">
       <c r="A735" t="s">
         <v>4056</v>
       </c>
@@ -31946,7 +31946,7 @@
         <v>4061</v>
       </c>
     </row>
-    <row r="736">
+    <row r="736" hidden="1">
       <c r="A736" t="s">
         <v>4062</v>
       </c>
@@ -31972,7 +31972,7 @@
         <v>4067</v>
       </c>
     </row>
-    <row r="737">
+    <row r="737" hidden="1">
       <c r="A737" t="s">
         <v>4068</v>
       </c>
@@ -31998,7 +31998,7 @@
         <v>4073</v>
       </c>
     </row>
-    <row r="738">
+    <row r="738" hidden="1">
       <c r="A738" t="s">
         <v>4074</v>
       </c>
@@ -32024,7 +32024,7 @@
         <v>4079</v>
       </c>
     </row>
-    <row r="739">
+    <row r="739" hidden="1">
       <c r="A739" t="s">
         <v>4080</v>
       </c>
@@ -32050,7 +32050,7 @@
         <v>4085</v>
       </c>
     </row>
-    <row r="740">
+    <row r="740" hidden="1">
       <c r="A740" t="s">
         <v>4086</v>
       </c>
@@ -32076,7 +32076,7 @@
         <v>4091</v>
       </c>
     </row>
-    <row r="741">
+    <row r="741" hidden="1">
       <c r="A741" t="s">
         <v>4092</v>
       </c>
@@ -32102,7 +32102,7 @@
         <v>4097</v>
       </c>
     </row>
-    <row r="742">
+    <row r="742" hidden="1">
       <c r="A742" t="s">
         <v>4098</v>
       </c>
@@ -32128,7 +32128,7 @@
         <v>4103</v>
       </c>
     </row>
-    <row r="743">
+    <row r="743" hidden="1">
       <c r="A743" t="s">
         <v>4104</v>
       </c>
@@ -32154,7 +32154,7 @@
         <v>4109</v>
       </c>
     </row>
-    <row r="744">
+    <row r="744" hidden="1">
       <c r="A744" t="s">
         <v>4110</v>
       </c>
@@ -32180,7 +32180,7 @@
         <v>4115</v>
       </c>
     </row>
-    <row r="745">
+    <row r="745" hidden="1">
       <c r="A745" t="s">
         <v>4116</v>
       </c>
@@ -32206,7 +32206,7 @@
         <v>4121</v>
       </c>
     </row>
-    <row r="746">
+    <row r="746" hidden="1">
       <c r="A746" t="s">
         <v>4122</v>
       </c>
@@ -32237,6 +32237,11 @@
     <filterColumn colId="2">
       <filters>
         <filter val="Maps"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="SlateportCity"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:I746">
@@ -32251,7 +32256,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{F4CE5785-1475-48CA-A667-2EA718B41DF3}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{E7B4565E-93A5-494E-B986-8DE618A03874}">
             <xm:f>"Onvertaald"</xm:f>
             <x14:dxf>
               <font>
@@ -32268,7 +32273,7 @@
           <xm:sqref>G:G</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{37594E7E-F2F0-4660-9431-461FC046E25D}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{3B9826E0-72B4-4309-A11B-8A0A3A01709E}">
             <xm:f>"Vertaald"</xm:f>
             <x14:dxf>
               <font>

--- a/translation_dashboard.xlsx
+++ b/translation_dashboard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="10" documentId="11_FC6C07367B11BFA52A7DE7D135F6D12E1E2DAEB7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EB7C9F2-3291-46CD-9695-A22F1E0845F2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/translation_dashboard.xlsx
+++ b/translation_dashboard.xlsx
@@ -1,43 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acvcsc-my.sharepoint.com/personal/ancome_acv-csc_be/Documents/Documenten/Privé/pokemVertaling/pokeemerald/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_FC6C07367B11BFA52A7DE7D135F6D12E1E2DAEB7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EB7C9F2-3291-46CD-9695-A22F1E0845F2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$746</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4136" uniqueCount="4118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4117" uniqueCount="4117">
   <si>
     <t>Bestand</t>
   </si>
@@ -156,7 +140,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t>Enkel namen te vertalen</t>
+    <t xml:space="preserve">Enkel namen te vertalen</t>
   </si>
   <si>
     <t>trainers.inc</t>
@@ -219,7 +203,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t>Deze is echt groot</t>
+    <t xml:space="preserve">Deze is echt groot</t>
   </si>
   <si>
     <t>pokedex_text.h</t>
@@ -237,7 +221,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t>Deze is echt groot</t>
+    <t xml:space="preserve">Deze is echt groot</t>
   </si>
   <si>
     <t>apprentice.inc</t>
@@ -408,7 +392,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t>Optional, je kan de nicknames van opponents gek maken</t>
+    <t xml:space="preserve">Optional, je kan de nicknames van opponents gek maken</t>
   </si>
   <si>
     <t>scripts.inc</t>
@@ -2700,7 +2684,7 @@
     <t>SlateportCity</t>
   </si>
   <si>
-    <t>Onvertaald</t>
+    <t>Vertaald</t>
   </si>
   <si>
     <t>Hoog</t>
@@ -3174,7 +3158,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t>Dit is de ending van de vertaling :')</t>
+    <t xml:space="preserve">Dit is de ending van de vertaling :')</t>
   </si>
   <si>
     <t>scripts.inc</t>
@@ -5601,7 +5585,7 @@
     <t>Middel</t>
   </si>
   <si>
-    <t>"NAVEL ROCK"' LOCATIE NIET VERTAALD!</t>
+    <t xml:space="preserve">"NAVEL ROCK"' LOCATIE NIET VERTAALD!</t>
   </si>
   <si>
     <t>scripts.inc</t>
@@ -5934,7 +5918,7 @@
     <t>Middel</t>
   </si>
   <si>
-    <t>"NAVEL ROCK"' LOCATIE NIET VERTAALD!</t>
+    <t xml:space="preserve">"NAVEL ROCK"' LOCATIE NIET VERTAALD!</t>
   </si>
   <si>
     <t>scripts.inc</t>
@@ -11919,7 +11903,7 @@
     <t>Hoog</t>
   </si>
   <si>
-    <t>Enkel namen te vertalen</t>
+    <t xml:space="preserve">Enkel namen te vertalen</t>
   </si>
   <si>
     <t>scripts.inc</t>
@@ -12306,9 +12290,6 @@
     <t>NavelRock</t>
   </si>
   <si>
-    <t>Vertaald</t>
-  </si>
-  <si>
     <t>Laag</t>
   </si>
   <si>
@@ -12378,16 +12359,16 @@
     <t>Laag</t>
   </si>
   <si>
-    <t>Vertaalde tekens</t>
+    <t xml:space="preserve">Vertaalde tekens</t>
   </si>
   <si>
     <t>Tekens</t>
   </si>
   <si>
-    <t>Onvertaalde tekens</t>
-  </si>
-  <si>
-    <t>Totaal aantal tekens</t>
+    <t xml:space="preserve">Onvertaalde tekens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Totaal aantal tekens</t>
   </si>
   <si>
     <t>Vooruitgang</t>
@@ -12396,35 +12377,35 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="36"/>
+      <sz val="36.000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -12442,54 +12423,31 @@
   </fills>
   <borders count="1">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="2" borderId="0" applyFont="0" applyFill="0" applyBorder="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf fontId="1" fillId="2" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="10" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Procent" xfId="1" builtinId="5"/>
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -12503,12 +12461,12 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="nl-NL"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -12539,11 +12497,13 @@
               <a:rPr lang="nl-BE"/>
               <a:t>Progress</a:t>
             </a:r>
+            <a:endParaRPr/>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr>
+      <c:spPr bwMode="auto">
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12562,7 +12522,7 @@
     </c:view3D>
     <c:floor>
       <c:thickness val="0"/>
-      <c:spPr>
+      <c:spPr bwMode="auto">
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12574,7 +12534,7 @@
     </c:floor>
     <c:sideWall>
       <c:thickness val="0"/>
-      <c:spPr>
+      <c:spPr bwMode="auto">
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12586,7 +12546,7 @@
     </c:sideWall>
     <c:backWall>
       <c:thickness val="0"/>
-      <c:spPr>
+      <c:spPr bwMode="auto">
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12602,10 +12562,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.3239999999999999E-2"/>
-          <c:y val="0.18051"/>
-          <c:w val="0.93350999999999995"/>
-          <c:h val="0.71582000000000001"/>
+          <c:x val="0.033240"/>
+          <c:y val="0.180510"/>
+          <c:w val="0.933510"/>
+          <c:h val="0.715820"/>
         </c:manualLayout>
       </c:layout>
       <c:pie3DChart>
@@ -12627,7 +12587,7 @@
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
+            <c:spPr bwMode="auto">
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -12640,16 +12600,11 @@
                 </a:solidFill>
               </a:ln>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-2C02-4B1F-8601-8E6CB1085611}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
             <c:bubble3D val="0"/>
-            <c:spPr>
+            <c:spPr bwMode="auto">
               <a:prstGeom prst="rect">
                 <a:avLst/>
               </a:prstGeom>
@@ -12662,11 +12617,6 @@
                 </a:solidFill>
               </a:ln>
             </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000003-2C02-4B1F-8601-8E6CB1085611}"/>
-              </c:ext>
-            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -12697,23 +12647,18 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-2C02-4B1F-8601-8E6CB1085611}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLeaderLines val="0"/>
           <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
           <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="0"/>
         </c:dLbls>
       </c:pie3DChart>
-      <c:spPr>
+      <c:spPr bwMode="auto">
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12725,8 +12670,9 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
-      <c:spPr>
+      <c:spPr bwMode="auto">
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -12761,10 +12707,10 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr>
-    <a:xfrm>
-      <a:off x="3686175" y="0"/>
-      <a:ext cx="3689349" cy="2006599"/>
+  <c:spPr bwMode="auto">
+    <a:xfrm rot="0">
+      <a:off x="0" y="0"/>
+      <a:ext cx="0" cy="0"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -12801,15 +12747,15 @@
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
+  <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>530224</xdr:colOff>
@@ -12822,20 +12768,14 @@
       <xdr:row>9</xdr:row>
       <xdr:rowOff>6349</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="238760122" name="Grafiek 238760121">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-0000BA303B0E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="238760122" name="Grafiek 238760121"/>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
+      <xdr:xfrm rot="0">
         <a:off x="0" y="0"/>
         <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
@@ -12850,8 +12790,291 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Angsana New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
   <a:themeElements>
     <a:clrScheme name="">
       <a:dk1>
@@ -12903,7 +13126,7 @@
         <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -13006,25 +13229,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:I746"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1">
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+  </sheetPr>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="56.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="24.28515625"/>
+    <col customWidth="1" min="2" max="2" width="56.140625"/>
+    <col customWidth="1" min="3" max="3" width="15.7109375"/>
+    <col customWidth="1" min="4" max="4" width="14"/>
+    <col customWidth="1" min="5" max="5" width="15"/>
+    <col customWidth="1" min="6" max="6" width="13.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13053,7 +13277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -13076,7 +13300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" hidden="1">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -13099,7 +13323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" hidden="1">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -13122,7 +13346,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" hidden="1">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -13145,7 +13369,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" hidden="1">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -13168,7 +13392,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" hidden="1">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -13194,7 +13418,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" hidden="1">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -13217,7 +13441,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" hidden="1">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -13240,7 +13464,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" hidden="1">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -13263,7 +13487,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" hidden="1">
       <c r="A11" t="s">
         <v>55</v>
       </c>
@@ -13289,7 +13513,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" hidden="1">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -13315,7 +13539,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" hidden="1">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -13338,7 +13562,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" hidden="1">
       <c r="A14" t="s">
         <v>72</v>
       </c>
@@ -13361,7 +13585,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" hidden="1">
       <c r="A15" t="s">
         <v>77</v>
       </c>
@@ -13384,7 +13608,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" hidden="1">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -13407,7 +13631,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" hidden="1">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -13430,7 +13654,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" hidden="1">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -13453,7 +13677,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" hidden="1">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -13479,7 +13703,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" hidden="1">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -13502,7 +13726,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" hidden="1">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -13525,7 +13749,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" hidden="1">
       <c r="A22" t="s">
         <v>113</v>
       </c>
@@ -13548,7 +13772,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" hidden="1">
       <c r="A23" t="s">
         <v>118</v>
       </c>
@@ -13574,7 +13798,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" hidden="1">
       <c r="A24" t="s">
         <v>124</v>
       </c>
@@ -13600,7 +13824,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" hidden="1">
       <c r="A25" t="s">
         <v>130</v>
       </c>
@@ -13623,7 +13847,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" hidden="1">
       <c r="A26" t="s">
         <v>135</v>
       </c>
@@ -13646,7 +13870,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" hidden="1">
       <c r="A27" t="s">
         <v>140</v>
       </c>
@@ -13669,7 +13893,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" hidden="1">
       <c r="A28" t="s">
         <v>145</v>
       </c>
@@ -13692,7 +13916,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" hidden="1">
       <c r="A29" t="s">
         <v>150</v>
       </c>
@@ -13715,7 +13939,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" hidden="1">
       <c r="A30" t="s">
         <v>155</v>
       </c>
@@ -13738,7 +13962,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" hidden="1">
       <c r="A31" t="s">
         <v>160</v>
       </c>
@@ -13764,7 +13988,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" hidden="1">
       <c r="A32" t="s">
         <v>166</v>
       </c>
@@ -13787,7 +14011,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" hidden="1">
       <c r="A33" t="s">
         <v>171</v>
       </c>
@@ -13810,7 +14034,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" hidden="1">
       <c r="A34" t="s">
         <v>176</v>
       </c>
@@ -13833,7 +14057,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" hidden="1">
       <c r="A35" t="s">
         <v>181</v>
       </c>
@@ -13856,7 +14080,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" hidden="1">
       <c r="A36" t="s">
         <v>186</v>
       </c>
@@ -13879,7 +14103,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>191</v>
       </c>
@@ -13905,7 +14129,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" hidden="1">
       <c r="A38" t="s">
         <v>197</v>
       </c>
@@ -13928,7 +14152,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" hidden="1">
       <c r="A39" t="s">
         <v>202</v>
       </c>
@@ -13951,7 +14175,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" hidden="1">
       <c r="A40" t="s">
         <v>207</v>
       </c>
@@ -13977,7 +14201,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" hidden="1">
       <c r="A41" t="s">
         <v>213</v>
       </c>
@@ -14000,7 +14224,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" hidden="1">
       <c r="A42" t="s">
         <v>218</v>
       </c>
@@ -14026,7 +14250,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" hidden="1">
       <c r="A43" t="s">
         <v>224</v>
       </c>
@@ -14049,7 +14273,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" hidden="1">
       <c r="A44" t="s">
         <v>229</v>
       </c>
@@ -14075,7 +14299,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" hidden="1">
       <c r="A45" t="s">
         <v>235</v>
       </c>
@@ -14101,7 +14325,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" hidden="1">
       <c r="A46" t="s">
         <v>241</v>
       </c>
@@ -14124,7 +14348,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" hidden="1">
       <c r="A47" t="s">
         <v>246</v>
       </c>
@@ -14147,7 +14371,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" hidden="1">
       <c r="A48" t="s">
         <v>251</v>
       </c>
@@ -14170,7 +14394,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" hidden="1">
       <c r="A49" t="s">
         <v>256</v>
       </c>
@@ -14193,7 +14417,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" hidden="1">
       <c r="A50" t="s">
         <v>261</v>
       </c>
@@ -14216,7 +14440,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" hidden="1">
       <c r="A51" t="s">
         <v>266</v>
       </c>
@@ -14239,7 +14463,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" hidden="1">
       <c r="A52" t="s">
         <v>271</v>
       </c>
@@ -14262,7 +14486,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" hidden="1">
       <c r="A53" t="s">
         <v>276</v>
       </c>
@@ -14288,7 +14512,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" hidden="1">
       <c r="A54" t="s">
         <v>282</v>
       </c>
@@ -14311,7 +14535,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" hidden="1">
       <c r="A55" t="s">
         <v>287</v>
       </c>
@@ -14337,7 +14561,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" hidden="1">
       <c r="A56" t="s">
         <v>293</v>
       </c>
@@ -14363,7 +14587,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" hidden="1">
       <c r="A57" t="s">
         <v>299</v>
       </c>
@@ -14386,7 +14610,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" hidden="1">
       <c r="A58" t="s">
         <v>304</v>
       </c>
@@ -14409,7 +14633,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" hidden="1">
       <c r="A59" t="s">
         <v>309</v>
       </c>
@@ -14432,7 +14656,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" hidden="1">
       <c r="A60" t="s">
         <v>314</v>
       </c>
@@ -14455,7 +14679,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" hidden="1">
       <c r="A61" t="s">
         <v>319</v>
       </c>
@@ -14478,7 +14702,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" hidden="1">
       <c r="A62" t="s">
         <v>324</v>
       </c>
@@ -14501,7 +14725,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" hidden="1">
       <c r="A63" t="s">
         <v>329</v>
       </c>
@@ -14524,7 +14748,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" hidden="1">
       <c r="A64" t="s">
         <v>334</v>
       </c>
@@ -14547,7 +14771,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" hidden="1">
       <c r="A65" t="s">
         <v>339</v>
       </c>
@@ -14570,7 +14794,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" hidden="1">
       <c r="A66" t="s">
         <v>344</v>
       </c>
@@ -14593,7 +14817,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" hidden="1">
       <c r="A67" t="s">
         <v>349</v>
       </c>
@@ -14616,7 +14840,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" hidden="1">
       <c r="A68" t="s">
         <v>354</v>
       </c>
@@ -14639,7 +14863,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" hidden="1">
       <c r="A69" t="s">
         <v>359</v>
       </c>
@@ -14665,7 +14889,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" hidden="1">
       <c r="A70" t="s">
         <v>365</v>
       </c>
@@ -14691,7 +14915,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" hidden="1">
       <c r="A71" t="s">
         <v>371</v>
       </c>
@@ -14714,7 +14938,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" hidden="1">
       <c r="A72" t="s">
         <v>376</v>
       </c>
@@ -14737,7 +14961,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" hidden="1">
       <c r="A73" t="s">
         <v>381</v>
       </c>
@@ -14760,7 +14984,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" hidden="1">
       <c r="A74" t="s">
         <v>386</v>
       </c>
@@ -14783,7 +15007,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" hidden="1">
       <c r="A75" t="s">
         <v>391</v>
       </c>
@@ -14806,7 +15030,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" hidden="1">
       <c r="A76" t="s">
         <v>396</v>
       </c>
@@ -14832,7 +15056,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" hidden="1">
       <c r="A77" t="s">
         <v>402</v>
       </c>
@@ -14855,7 +15079,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" hidden="1">
       <c r="A78" t="s">
         <v>407</v>
       </c>
@@ -14878,7 +15102,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" hidden="1">
       <c r="A79" t="s">
         <v>412</v>
       </c>
@@ -14901,7 +15125,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" hidden="1">
       <c r="A80" t="s">
         <v>417</v>
       </c>
@@ -14924,7 +15148,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" hidden="1">
       <c r="A81" t="s">
         <v>422</v>
       </c>
@@ -14947,7 +15171,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" hidden="1">
       <c r="A82" t="s">
         <v>427</v>
       </c>
@@ -14970,7 +15194,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" hidden="1">
       <c r="A83" t="s">
         <v>432</v>
       </c>
@@ -14993,7 +15217,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" hidden="1">
       <c r="A84" t="s">
         <v>437</v>
       </c>
@@ -15016,7 +15240,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" hidden="1">
       <c r="A85" t="s">
         <v>442</v>
       </c>
@@ -15042,7 +15266,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" hidden="1">
       <c r="A86" t="s">
         <v>448</v>
       </c>
@@ -15065,7 +15289,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" hidden="1">
       <c r="A87" t="s">
         <v>453</v>
       </c>
@@ -15088,7 +15312,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" hidden="1">
       <c r="A88" t="s">
         <v>458</v>
       </c>
@@ -15111,7 +15335,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" hidden="1">
       <c r="A89" t="s">
         <v>463</v>
       </c>
@@ -15137,7 +15361,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" hidden="1">
       <c r="A90" t="s">
         <v>469</v>
       </c>
@@ -15160,7 +15384,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" hidden="1">
       <c r="A91" t="s">
         <v>474</v>
       </c>
@@ -15183,7 +15407,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" hidden="1">
       <c r="A92" t="s">
         <v>479</v>
       </c>
@@ -15209,7 +15433,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" hidden="1">
       <c r="A93" t="s">
         <v>485</v>
       </c>
@@ -15232,7 +15456,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" hidden="1">
       <c r="A94" t="s">
         <v>490</v>
       </c>
@@ -15255,7 +15479,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" hidden="1">
       <c r="A95" t="s">
         <v>495</v>
       </c>
@@ -15278,7 +15502,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" hidden="1">
       <c r="A96" t="s">
         <v>500</v>
       </c>
@@ -15304,7 +15528,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" hidden="1">
       <c r="A97" t="s">
         <v>506</v>
       </c>
@@ -15327,7 +15551,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" hidden="1">
       <c r="A98" t="s">
         <v>511</v>
       </c>
@@ -15350,7 +15574,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" hidden="1">
       <c r="A99" t="s">
         <v>516</v>
       </c>
@@ -15373,7 +15597,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" hidden="1">
       <c r="A100" t="s">
         <v>521</v>
       </c>
@@ -15399,7 +15623,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" hidden="1">
       <c r="A101" t="s">
         <v>527</v>
       </c>
@@ -15422,7 +15646,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" hidden="1">
       <c r="A102" t="s">
         <v>532</v>
       </c>
@@ -15445,7 +15669,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" hidden="1">
       <c r="A103" t="s">
         <v>537</v>
       </c>
@@ -15471,7 +15695,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" hidden="1">
       <c r="A104" t="s">
         <v>543</v>
       </c>
@@ -15497,7 +15721,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" hidden="1">
       <c r="A105" t="s">
         <v>549</v>
       </c>
@@ -15520,7 +15744,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" hidden="1">
       <c r="A106" t="s">
         <v>554</v>
       </c>
@@ -15543,7 +15767,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" hidden="1">
       <c r="A107" t="s">
         <v>559</v>
       </c>
@@ -15566,7 +15790,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" hidden="1">
       <c r="A108" t="s">
         <v>564</v>
       </c>
@@ -15592,7 +15816,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" hidden="1">
       <c r="A109" t="s">
         <v>570</v>
       </c>
@@ -15618,7 +15842,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" hidden="1">
       <c r="A110" t="s">
         <v>576</v>
       </c>
@@ -15641,7 +15865,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" hidden="1">
       <c r="A111" t="s">
         <v>581</v>
       </c>
@@ -15664,7 +15888,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" hidden="1">
       <c r="A112" t="s">
         <v>586</v>
       </c>
@@ -15690,7 +15914,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113">
       <c r="A113" t="s">
         <v>592</v>
       </c>
@@ -15716,7 +15940,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" hidden="1">
       <c r="A114" t="s">
         <v>597</v>
       </c>
@@ -15742,7 +15966,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" hidden="1">
       <c r="A115" t="s">
         <v>603</v>
       </c>
@@ -15765,7 +15989,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" hidden="1">
       <c r="A116" t="s">
         <v>608</v>
       </c>
@@ -15788,7 +16012,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" hidden="1">
       <c r="A117" t="s">
         <v>613</v>
       </c>
@@ -15811,7 +16035,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" hidden="1">
       <c r="A118" t="s">
         <v>618</v>
       </c>
@@ -15834,7 +16058,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" hidden="1">
       <c r="A119" t="s">
         <v>623</v>
       </c>
@@ -15857,7 +16081,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" hidden="1">
       <c r="A120" t="s">
         <v>628</v>
       </c>
@@ -15883,7 +16107,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" hidden="1">
       <c r="A121" t="s">
         <v>634</v>
       </c>
@@ -15906,7 +16130,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" hidden="1">
       <c r="A122" t="s">
         <v>639</v>
       </c>
@@ -15932,7 +16156,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" hidden="1">
       <c r="A123" t="s">
         <v>645</v>
       </c>
@@ -15955,7 +16179,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" hidden="1">
       <c r="A124" t="s">
         <v>650</v>
       </c>
@@ -15981,7 +16205,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" hidden="1">
       <c r="A125" t="s">
         <v>656</v>
       </c>
@@ -16004,7 +16228,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" hidden="1">
       <c r="A126" t="s">
         <v>661</v>
       </c>
@@ -16027,7 +16251,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" hidden="1">
       <c r="A127" t="s">
         <v>666</v>
       </c>
@@ -16053,7 +16277,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" hidden="1">
       <c r="A128" t="s">
         <v>672</v>
       </c>
@@ -16079,7 +16303,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" hidden="1">
       <c r="A129" t="s">
         <v>678</v>
       </c>
@@ -16102,7 +16326,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" hidden="1">
       <c r="A130" t="s">
         <v>683</v>
       </c>
@@ -16125,7 +16349,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" hidden="1">
       <c r="A131" t="s">
         <v>688</v>
       </c>
@@ -16148,7 +16372,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" hidden="1">
       <c r="A132" t="s">
         <v>693</v>
       </c>
@@ -16171,7 +16395,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" hidden="1">
       <c r="A133" t="s">
         <v>698</v>
       </c>
@@ -16197,7 +16421,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" hidden="1">
       <c r="A134" t="s">
         <v>704</v>
       </c>
@@ -16220,7 +16444,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" hidden="1">
       <c r="A135" t="s">
         <v>709</v>
       </c>
@@ -16246,7 +16470,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" hidden="1">
       <c r="A136" t="s">
         <v>715</v>
       </c>
@@ -16272,7 +16496,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" hidden="1">
       <c r="A137" t="s">
         <v>721</v>
       </c>
@@ -16298,7 +16522,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" hidden="1">
       <c r="A138" t="s">
         <v>727</v>
       </c>
@@ -16321,7 +16545,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" hidden="1">
       <c r="A139" t="s">
         <v>732</v>
       </c>
@@ -16344,7 +16568,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" hidden="1">
       <c r="A140" t="s">
         <v>737</v>
       </c>
@@ -16370,7 +16594,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" hidden="1">
       <c r="A141" t="s">
         <v>743</v>
       </c>
@@ -16396,7 +16620,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" hidden="1">
       <c r="A142" t="s">
         <v>749</v>
       </c>
@@ -16419,7 +16643,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" hidden="1">
       <c r="A143" t="s">
         <v>754</v>
       </c>
@@ -16445,7 +16669,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" hidden="1">
       <c r="A144" t="s">
         <v>760</v>
       </c>
@@ -16471,7 +16695,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" hidden="1">
       <c r="A145" t="s">
         <v>766</v>
       </c>
@@ -16494,7 +16718,7 @@
         <v>770</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" hidden="1">
       <c r="A146" t="s">
         <v>771</v>
       </c>
@@ -16517,7 +16741,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147">
       <c r="A147" t="s">
         <v>776</v>
       </c>
@@ -16543,7 +16767,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" hidden="1">
       <c r="A148" t="s">
         <v>782</v>
       </c>
@@ -16569,7 +16793,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" hidden="1">
       <c r="A149" t="s">
         <v>788</v>
       </c>
@@ -16592,7 +16816,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" hidden="1">
       <c r="A150" t="s">
         <v>793</v>
       </c>
@@ -16615,7 +16839,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" hidden="1">
       <c r="A151" t="s">
         <v>798</v>
       </c>
@@ -16638,7 +16862,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" hidden="1">
       <c r="A152" t="s">
         <v>803</v>
       </c>
@@ -16664,7 +16888,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" hidden="1">
       <c r="A153" t="s">
         <v>809</v>
       </c>
@@ -16687,7 +16911,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" hidden="1">
       <c r="A154" t="s">
         <v>814</v>
       </c>
@@ -16710,7 +16934,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" hidden="1">
       <c r="A155" t="s">
         <v>819</v>
       </c>
@@ -16736,7 +16960,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" hidden="1">
       <c r="A156" t="s">
         <v>825</v>
       </c>
@@ -16759,7 +16983,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" hidden="1">
       <c r="A157" t="s">
         <v>830</v>
       </c>
@@ -16785,7 +17009,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" hidden="1">
       <c r="A158" t="s">
         <v>836</v>
       </c>
@@ -16811,7 +17035,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" hidden="1">
       <c r="A159" t="s">
         <v>842</v>
       </c>
@@ -16837,7 +17061,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" hidden="1">
       <c r="A160" t="s">
         <v>848</v>
       </c>
@@ -16860,7 +17084,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" hidden="1">
       <c r="A161" t="s">
         <v>853</v>
       </c>
@@ -16883,7 +17107,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" hidden="1">
       <c r="A162" t="s">
         <v>858</v>
       </c>
@@ -16906,7 +17130,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" hidden="1">
       <c r="A163" t="s">
         <v>863</v>
       </c>
@@ -16929,7 +17153,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" hidden="1">
       <c r="A164" t="s">
         <v>868</v>
       </c>
@@ -16952,7 +17176,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" hidden="1">
       <c r="A165" t="s">
         <v>873</v>
       </c>
@@ -16975,7 +17199,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" hidden="1">
       <c r="A166" t="s">
         <v>878</v>
       </c>
@@ -16998,7 +17222,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167">
       <c r="A167" t="s">
         <v>883</v>
       </c>
@@ -17024,7 +17248,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" hidden="1">
       <c r="A168" t="s">
         <v>889</v>
       </c>
@@ -17047,7 +17271,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" hidden="1">
       <c r="A169" t="s">
         <v>894</v>
       </c>
@@ -17073,7 +17297,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" hidden="1">
       <c r="A170" t="s">
         <v>900</v>
       </c>
@@ -17099,7 +17323,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" hidden="1">
       <c r="A171" t="s">
         <v>906</v>
       </c>
@@ -17122,7 +17346,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" hidden="1">
       <c r="A172" t="s">
         <v>911</v>
       </c>
@@ -17148,7 +17372,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" hidden="1">
       <c r="A173" t="s">
         <v>917</v>
       </c>
@@ -17171,7 +17395,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" hidden="1">
       <c r="A174" t="s">
         <v>922</v>
       </c>
@@ -17194,7 +17418,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" hidden="1">
       <c r="A175" t="s">
         <v>927</v>
       </c>
@@ -17217,7 +17441,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" hidden="1">
       <c r="A176" t="s">
         <v>932</v>
       </c>
@@ -17240,7 +17464,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" hidden="1">
       <c r="A177" t="s">
         <v>937</v>
       </c>
@@ -17263,7 +17487,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" hidden="1">
       <c r="A178" t="s">
         <v>942</v>
       </c>
@@ -17289,7 +17513,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" hidden="1">
       <c r="A179" t="s">
         <v>948</v>
       </c>
@@ -17312,7 +17536,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" hidden="1">
       <c r="A180" t="s">
         <v>953</v>
       </c>
@@ -17338,7 +17562,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" hidden="1">
       <c r="A181" t="s">
         <v>959</v>
       </c>
@@ -17361,7 +17585,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" hidden="1">
       <c r="A182" t="s">
         <v>964</v>
       </c>
@@ -17387,7 +17611,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" hidden="1">
       <c r="A183" t="s">
         <v>970</v>
       </c>
@@ -17410,7 +17634,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" hidden="1">
       <c r="A184" t="s">
         <v>975</v>
       </c>
@@ -17433,7 +17657,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" hidden="1">
       <c r="A185" t="s">
         <v>980</v>
       </c>
@@ -17456,7 +17680,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" hidden="1">
       <c r="A186" t="s">
         <v>985</v>
       </c>
@@ -17482,7 +17706,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" hidden="1">
       <c r="A187" t="s">
         <v>991</v>
       </c>
@@ -17505,7 +17729,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" hidden="1">
       <c r="A188" t="s">
         <v>996</v>
       </c>
@@ -17531,7 +17755,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" hidden="1">
       <c r="A189" t="s">
         <v>1002</v>
       </c>
@@ -17554,7 +17778,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" hidden="1">
       <c r="A190" t="s">
         <v>1007</v>
       </c>
@@ -17577,7 +17801,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" hidden="1">
       <c r="A191" t="s">
         <v>1012</v>
       </c>
@@ -17603,7 +17827,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" hidden="1">
       <c r="A192" t="s">
         <v>1018</v>
       </c>
@@ -17626,7 +17850,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" hidden="1">
       <c r="A193" t="s">
         <v>1023</v>
       </c>
@@ -17652,7 +17876,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" hidden="1">
       <c r="A194" t="s">
         <v>1029</v>
       </c>
@@ -17675,7 +17899,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" hidden="1">
       <c r="A195" t="s">
         <v>1034</v>
       </c>
@@ -17698,7 +17922,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" hidden="1">
       <c r="A196" t="s">
         <v>1039</v>
       </c>
@@ -17727,7 +17951,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" hidden="1">
       <c r="A197" t="s">
         <v>1046</v>
       </c>
@@ -17753,7 +17977,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" hidden="1">
       <c r="A198" t="s">
         <v>1052</v>
       </c>
@@ -17779,7 +18003,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" hidden="1">
       <c r="A199" t="s">
         <v>1058</v>
       </c>
@@ -17802,7 +18026,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" hidden="1">
       <c r="A200" t="s">
         <v>1063</v>
       </c>
@@ -17825,7 +18049,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" hidden="1">
       <c r="A201" t="s">
         <v>1068</v>
       </c>
@@ -17848,7 +18072,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" hidden="1">
       <c r="A202" t="s">
         <v>1073</v>
       </c>
@@ -17874,7 +18098,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" hidden="1">
       <c r="A203" t="s">
         <v>1079</v>
       </c>
@@ -17900,7 +18124,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" hidden="1">
       <c r="A204" t="s">
         <v>1085</v>
       </c>
@@ -17926,7 +18150,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" hidden="1">
       <c r="A205" t="s">
         <v>1091</v>
       </c>
@@ -17952,7 +18176,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" hidden="1">
       <c r="A206" t="s">
         <v>1097</v>
       </c>
@@ -17975,7 +18199,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" hidden="1">
       <c r="A207" t="s">
         <v>1102</v>
       </c>
@@ -17998,7 +18222,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" hidden="1">
       <c r="A208" t="s">
         <v>1107</v>
       </c>
@@ -18024,7 +18248,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" hidden="1">
       <c r="A209" t="s">
         <v>1113</v>
       </c>
@@ -18047,7 +18271,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" hidden="1">
       <c r="A210" t="s">
         <v>1118</v>
       </c>
@@ -18073,7 +18297,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" hidden="1">
       <c r="A211" t="s">
         <v>1124</v>
       </c>
@@ -18096,7 +18320,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" hidden="1">
       <c r="A212" t="s">
         <v>1129</v>
       </c>
@@ -18119,7 +18343,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" hidden="1">
       <c r="A213" t="s">
         <v>1134</v>
       </c>
@@ -18142,7 +18366,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" hidden="1">
       <c r="A214" t="s">
         <v>1139</v>
       </c>
@@ -18168,7 +18392,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" hidden="1">
       <c r="A215" t="s">
         <v>1145</v>
       </c>
@@ -18191,7 +18415,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" hidden="1">
       <c r="A216" t="s">
         <v>1150</v>
       </c>
@@ -18214,7 +18438,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" hidden="1">
       <c r="A217" t="s">
         <v>1155</v>
       </c>
@@ -18237,7 +18461,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" hidden="1">
       <c r="A218" t="s">
         <v>1160</v>
       </c>
@@ -18263,7 +18487,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" hidden="1">
       <c r="A219" t="s">
         <v>1166</v>
       </c>
@@ -18286,7 +18510,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" hidden="1">
       <c r="A220" t="s">
         <v>1171</v>
       </c>
@@ -18312,7 +18536,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" hidden="1">
       <c r="A221" t="s">
         <v>1177</v>
       </c>
@@ -18338,7 +18562,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" hidden="1">
       <c r="A222" t="s">
         <v>1183</v>
       </c>
@@ -18361,7 +18585,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" hidden="1">
       <c r="A223" t="s">
         <v>1188</v>
       </c>
@@ -18387,7 +18611,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" hidden="1">
       <c r="A224" t="s">
         <v>1194</v>
       </c>
@@ -18410,7 +18634,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" hidden="1">
       <c r="A225" t="s">
         <v>1199</v>
       </c>
@@ -18436,7 +18660,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" hidden="1">
       <c r="A226" t="s">
         <v>1205</v>
       </c>
@@ -18459,7 +18683,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" hidden="1">
       <c r="A227" t="s">
         <v>1210</v>
       </c>
@@ -18482,7 +18706,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" hidden="1">
       <c r="A228" t="s">
         <v>1215</v>
       </c>
@@ -18505,7 +18729,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" hidden="1">
       <c r="A229" t="s">
         <v>1220</v>
       </c>
@@ -18528,7 +18752,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" hidden="1">
       <c r="A230" t="s">
         <v>1225</v>
       </c>
@@ -18551,7 +18775,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" hidden="1">
       <c r="A231" t="s">
         <v>1230</v>
       </c>
@@ -18577,7 +18801,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" hidden="1">
       <c r="A232" t="s">
         <v>1236</v>
       </c>
@@ -18600,7 +18824,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" hidden="1">
       <c r="A233" t="s">
         <v>1241</v>
       </c>
@@ -18626,7 +18850,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" hidden="1">
       <c r="A234" t="s">
         <v>1247</v>
       </c>
@@ -18649,7 +18873,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" hidden="1">
       <c r="A235" t="s">
         <v>1252</v>
       </c>
@@ -18672,7 +18896,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" hidden="1">
       <c r="A236" t="s">
         <v>1257</v>
       </c>
@@ -18698,7 +18922,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" hidden="1">
       <c r="A237" t="s">
         <v>1263</v>
       </c>
@@ -18721,7 +18945,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" hidden="1">
       <c r="A238" t="s">
         <v>1268</v>
       </c>
@@ -18744,7 +18968,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" hidden="1">
       <c r="A239" t="s">
         <v>1273</v>
       </c>
@@ -18767,7 +18991,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" hidden="1">
       <c r="A240" t="s">
         <v>1278</v>
       </c>
@@ -18790,7 +19014,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" hidden="1">
       <c r="A241" t="s">
         <v>1283</v>
       </c>
@@ -18813,7 +19037,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" hidden="1">
       <c r="A242" t="s">
         <v>1288</v>
       </c>
@@ -18836,7 +19060,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" hidden="1">
       <c r="A243" t="s">
         <v>1293</v>
       </c>
@@ -18862,7 +19086,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" hidden="1">
       <c r="A244" t="s">
         <v>1299</v>
       </c>
@@ -18885,7 +19109,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" hidden="1">
       <c r="A245" t="s">
         <v>1304</v>
       </c>
@@ -18911,7 +19135,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" hidden="1">
       <c r="A246" t="s">
         <v>1310</v>
       </c>
@@ -18934,7 +19158,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" hidden="1">
       <c r="A247" t="s">
         <v>1315</v>
       </c>
@@ -18960,7 +19184,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" hidden="1">
       <c r="A248" t="s">
         <v>1321</v>
       </c>
@@ -18986,7 +19210,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" hidden="1">
       <c r="A249" t="s">
         <v>1327</v>
       </c>
@@ -19009,7 +19233,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" hidden="1">
       <c r="A250" t="s">
         <v>1332</v>
       </c>
@@ -19035,7 +19259,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" hidden="1">
       <c r="A251" t="s">
         <v>1338</v>
       </c>
@@ -19058,7 +19282,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" hidden="1">
       <c r="A252" t="s">
         <v>1343</v>
       </c>
@@ -19084,7 +19308,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" hidden="1">
       <c r="A253" t="s">
         <v>1349</v>
       </c>
@@ -19107,7 +19331,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" hidden="1">
       <c r="A254" t="s">
         <v>1354</v>
       </c>
@@ -19133,7 +19357,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" hidden="1">
       <c r="A255" t="s">
         <v>1360</v>
       </c>
@@ -19159,7 +19383,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" hidden="1">
       <c r="A256" t="s">
         <v>1366</v>
       </c>
@@ -19185,7 +19409,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" hidden="1">
       <c r="A257" t="s">
         <v>1372</v>
       </c>
@@ -19208,7 +19432,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" hidden="1">
       <c r="A258" t="s">
         <v>1377</v>
       </c>
@@ -19234,7 +19458,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" hidden="1">
       <c r="A259" t="s">
         <v>1383</v>
       </c>
@@ -19257,7 +19481,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" hidden="1">
       <c r="A260" t="s">
         <v>1388</v>
       </c>
@@ -19280,7 +19504,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" hidden="1">
       <c r="A261" t="s">
         <v>1393</v>
       </c>
@@ -19306,7 +19530,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" hidden="1">
       <c r="A262" t="s">
         <v>1399</v>
       </c>
@@ -19332,7 +19556,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" hidden="1">
       <c r="A263" t="s">
         <v>1405</v>
       </c>
@@ -19358,7 +19582,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" hidden="1">
       <c r="A264" t="s">
         <v>1411</v>
       </c>
@@ -19381,7 +19605,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" hidden="1">
       <c r="A265" t="s">
         <v>1416</v>
       </c>
@@ -19404,7 +19628,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" hidden="1">
       <c r="A266" t="s">
         <v>1421</v>
       </c>
@@ -19427,7 +19651,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" hidden="1">
       <c r="A267" t="s">
         <v>1426</v>
       </c>
@@ -19450,7 +19674,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" hidden="1">
       <c r="A268" t="s">
         <v>1431</v>
       </c>
@@ -19473,7 +19697,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" hidden="1">
       <c r="A269" t="s">
         <v>1436</v>
       </c>
@@ -19496,7 +19720,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" hidden="1">
       <c r="A270" t="s">
         <v>1441</v>
       </c>
@@ -19519,7 +19743,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" hidden="1">
       <c r="A271" t="s">
         <v>1446</v>
       </c>
@@ -19545,7 +19769,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" hidden="1">
       <c r="A272" t="s">
         <v>1452</v>
       </c>
@@ -19568,7 +19792,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" hidden="1">
       <c r="A273" t="s">
         <v>1457</v>
       </c>
@@ -19591,7 +19815,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" hidden="1">
       <c r="A274" t="s">
         <v>1462</v>
       </c>
@@ -19617,7 +19841,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" hidden="1">
       <c r="A275" t="s">
         <v>1468</v>
       </c>
@@ -19643,7 +19867,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" hidden="1">
       <c r="A276" t="s">
         <v>1473</v>
       </c>
@@ -19669,7 +19893,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" hidden="1">
       <c r="A277" t="s">
         <v>1479</v>
       </c>
@@ -19695,7 +19919,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" hidden="1">
       <c r="A278" t="s">
         <v>1485</v>
       </c>
@@ -19718,7 +19942,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" hidden="1">
       <c r="A279" t="s">
         <v>1490</v>
       </c>
@@ -19744,7 +19968,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" hidden="1">
       <c r="A280" t="s">
         <v>1496</v>
       </c>
@@ -19767,7 +19991,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" hidden="1">
       <c r="A281" t="s">
         <v>1501</v>
       </c>
@@ -19793,7 +20017,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" hidden="1">
       <c r="A282" t="s">
         <v>1507</v>
       </c>
@@ -19819,7 +20043,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" hidden="1">
       <c r="A283" t="s">
         <v>1513</v>
       </c>
@@ -19845,7 +20069,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" hidden="1">
       <c r="A284" t="s">
         <v>1519</v>
       </c>
@@ -19871,7 +20095,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" hidden="1">
       <c r="A285" t="s">
         <v>1525</v>
       </c>
@@ -19894,7 +20118,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" hidden="1">
       <c r="A286" t="s">
         <v>1530</v>
       </c>
@@ -19920,7 +20144,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" hidden="1">
       <c r="A287" t="s">
         <v>1536</v>
       </c>
@@ -19943,7 +20167,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" hidden="1">
       <c r="A288" t="s">
         <v>1541</v>
       </c>
@@ -19969,7 +20193,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" hidden="1">
       <c r="A289" t="s">
         <v>1547</v>
       </c>
@@ -19995,7 +20219,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" hidden="1">
       <c r="A290" t="s">
         <v>1553</v>
       </c>
@@ -20021,7 +20245,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" hidden="1">
       <c r="A291" t="s">
         <v>1559</v>
       </c>
@@ -20044,7 +20268,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" hidden="1">
       <c r="A292" t="s">
         <v>1564</v>
       </c>
@@ -20070,7 +20294,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" hidden="1">
       <c r="A293" t="s">
         <v>1570</v>
       </c>
@@ -20093,7 +20317,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" hidden="1">
       <c r="A294" t="s">
         <v>1575</v>
       </c>
@@ -20119,7 +20343,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" hidden="1">
       <c r="A295" t="s">
         <v>1581</v>
       </c>
@@ -20145,7 +20369,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" hidden="1">
       <c r="A296" t="s">
         <v>1587</v>
       </c>
@@ -20168,7 +20392,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" hidden="1">
       <c r="A297" t="s">
         <v>1592</v>
       </c>
@@ -20194,7 +20418,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" hidden="1">
       <c r="A298" t="s">
         <v>1598</v>
       </c>
@@ -20220,7 +20444,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" hidden="1">
       <c r="A299" t="s">
         <v>1604</v>
       </c>
@@ -20246,7 +20470,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" hidden="1">
       <c r="A300" t="s">
         <v>1610</v>
       </c>
@@ -20269,7 +20493,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301">
       <c r="A301" t="s">
         <v>1615</v>
       </c>
@@ -20295,7 +20519,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" hidden="1">
       <c r="A302" t="s">
         <v>1621</v>
       </c>
@@ -20321,7 +20545,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" hidden="1">
       <c r="A303" t="s">
         <v>1627</v>
       </c>
@@ -20347,7 +20571,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" hidden="1">
       <c r="A304" t="s">
         <v>1633</v>
       </c>
@@ -20373,7 +20597,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" hidden="1">
       <c r="A305" t="s">
         <v>1639</v>
       </c>
@@ -20399,7 +20623,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" hidden="1">
       <c r="A306" t="s">
         <v>1645</v>
       </c>
@@ -20422,7 +20646,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" hidden="1">
       <c r="A307" t="s">
         <v>1650</v>
       </c>
@@ -20448,7 +20672,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" hidden="1">
       <c r="A308" t="s">
         <v>1656</v>
       </c>
@@ -20471,7 +20695,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" hidden="1">
       <c r="A309" t="s">
         <v>1661</v>
       </c>
@@ -20497,7 +20721,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" hidden="1">
       <c r="A310" t="s">
         <v>1667</v>
       </c>
@@ -20523,7 +20747,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" hidden="1">
       <c r="A311" t="s">
         <v>1673</v>
       </c>
@@ -20549,7 +20773,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" hidden="1">
       <c r="A312" t="s">
         <v>1679</v>
       </c>
@@ -20575,7 +20799,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" hidden="1">
       <c r="A313" t="s">
         <v>1685</v>
       </c>
@@ -20601,7 +20825,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" hidden="1">
       <c r="A314" t="s">
         <v>1691</v>
       </c>
@@ -20627,7 +20851,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" hidden="1">
       <c r="A315" t="s">
         <v>1697</v>
       </c>
@@ -20650,7 +20874,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" hidden="1">
       <c r="A316" t="s">
         <v>1702</v>
       </c>
@@ -20673,7 +20897,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" hidden="1">
       <c r="A317" t="s">
         <v>1707</v>
       </c>
@@ -20699,7 +20923,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" hidden="1">
       <c r="A318" t="s">
         <v>1713</v>
       </c>
@@ -20725,7 +20949,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" hidden="1">
       <c r="A319" t="s">
         <v>1719</v>
       </c>
@@ -20751,7 +20975,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" hidden="1">
       <c r="A320" t="s">
         <v>1725</v>
       </c>
@@ -20774,7 +20998,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" hidden="1">
       <c r="A321" t="s">
         <v>1730</v>
       </c>
@@ -20800,7 +21024,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" hidden="1">
       <c r="A322" t="s">
         <v>1736</v>
       </c>
@@ -20826,7 +21050,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" hidden="1">
       <c r="A323" t="s">
         <v>1742</v>
       </c>
@@ -20849,7 +21073,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" hidden="1">
       <c r="A324" t="s">
         <v>1747</v>
       </c>
@@ -20875,7 +21099,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" hidden="1">
       <c r="A325" t="s">
         <v>1753</v>
       </c>
@@ -20901,7 +21125,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" hidden="1">
       <c r="A326" t="s">
         <v>1759</v>
       </c>
@@ -20924,7 +21148,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" hidden="1">
       <c r="A327" t="s">
         <v>1764</v>
       </c>
@@ -20947,7 +21171,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" hidden="1">
       <c r="A328" t="s">
         <v>1769</v>
       </c>
@@ -20970,7 +21194,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329">
       <c r="A329" t="s">
         <v>1774</v>
       </c>
@@ -20996,7 +21220,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" hidden="1">
       <c r="A330" t="s">
         <v>1779</v>
       </c>
@@ -21022,7 +21246,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" hidden="1">
       <c r="A331" t="s">
         <v>1785</v>
       </c>
@@ -21048,7 +21272,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" hidden="1">
       <c r="A332" t="s">
         <v>1791</v>
       </c>
@@ -21074,7 +21298,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" hidden="1">
       <c r="A333" t="s">
         <v>1797</v>
       </c>
@@ -21100,7 +21324,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" hidden="1">
       <c r="A334" t="s">
         <v>1803</v>
       </c>
@@ -21126,7 +21350,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" hidden="1">
       <c r="A335" t="s">
         <v>1809</v>
       </c>
@@ -21149,7 +21373,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" hidden="1">
       <c r="A336" t="s">
         <v>1814</v>
       </c>
@@ -21175,7 +21399,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" hidden="1">
       <c r="A337" t="s">
         <v>1820</v>
       </c>
@@ -21201,7 +21425,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" hidden="1">
       <c r="A338" t="s">
         <v>1826</v>
       </c>
@@ -21224,7 +21448,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" hidden="1">
       <c r="A339" t="s">
         <v>1831</v>
       </c>
@@ -21250,7 +21474,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" hidden="1">
       <c r="A340" t="s">
         <v>1837</v>
       </c>
@@ -21273,7 +21497,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" hidden="1">
       <c r="A341" t="s">
         <v>1842</v>
       </c>
@@ -21299,7 +21523,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" hidden="1">
       <c r="A342" t="s">
         <v>1848</v>
       </c>
@@ -21328,7 +21552,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" hidden="1">
       <c r="A343" t="s">
         <v>1855</v>
       </c>
@@ -21351,7 +21575,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" hidden="1">
       <c r="A344" t="s">
         <v>1860</v>
       </c>
@@ -21377,7 +21601,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" hidden="1">
       <c r="A345" t="s">
         <v>1866</v>
       </c>
@@ -21403,7 +21627,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" hidden="1">
       <c r="A346" t="s">
         <v>1872</v>
       </c>
@@ -21429,7 +21653,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" hidden="1">
       <c r="A347" t="s">
         <v>1878</v>
       </c>
@@ -21455,7 +21679,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" hidden="1">
       <c r="A348" t="s">
         <v>1884</v>
       </c>
@@ -21481,7 +21705,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" hidden="1">
       <c r="A349" t="s">
         <v>1890</v>
       </c>
@@ -21507,7 +21731,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" hidden="1">
       <c r="A350" t="s">
         <v>1896</v>
       </c>
@@ -21530,7 +21754,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" hidden="1">
       <c r="A351" t="s">
         <v>1901</v>
       </c>
@@ -21556,7 +21780,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" hidden="1">
       <c r="A352" t="s">
         <v>1907</v>
       </c>
@@ -21582,7 +21806,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" hidden="1">
       <c r="A353" t="s">
         <v>1913</v>
       </c>
@@ -21608,7 +21832,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" hidden="1">
       <c r="A354" t="s">
         <v>1919</v>
       </c>
@@ -21631,7 +21855,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" hidden="1">
       <c r="A355" t="s">
         <v>1924</v>
       </c>
@@ -21654,7 +21878,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" hidden="1">
       <c r="A356" t="s">
         <v>1929</v>
       </c>
@@ -21677,7 +21901,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" hidden="1">
       <c r="A357" t="s">
         <v>1933</v>
       </c>
@@ -21700,7 +21924,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" hidden="1">
       <c r="A358" t="s">
         <v>1937</v>
       </c>
@@ -21723,7 +21947,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" hidden="1">
       <c r="A359" t="s">
         <v>1942</v>
       </c>
@@ -21749,7 +21973,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" hidden="1">
       <c r="A360" t="s">
         <v>1948</v>
       </c>
@@ -21775,7 +21999,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" hidden="1">
       <c r="A361" t="s">
         <v>1954</v>
       </c>
@@ -21798,7 +22022,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" hidden="1">
       <c r="A362" t="s">
         <v>1959</v>
       </c>
@@ -21827,7 +22051,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" hidden="1">
       <c r="A363" t="s">
         <v>1966</v>
       </c>
@@ -21853,7 +22077,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" hidden="1">
       <c r="A364" t="s">
         <v>1972</v>
       </c>
@@ -21876,7 +22100,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" hidden="1">
       <c r="A365" t="s">
         <v>1977</v>
       </c>
@@ -21899,7 +22123,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" hidden="1">
       <c r="A366" t="s">
         <v>1982</v>
       </c>
@@ -21925,7 +22149,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" hidden="1">
       <c r="A367" t="s">
         <v>1988</v>
       </c>
@@ -21951,7 +22175,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" hidden="1">
       <c r="A368" t="s">
         <v>1994</v>
       </c>
@@ -21974,7 +22198,7 @@
         <v>1998</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" hidden="1">
       <c r="A369" t="s">
         <v>1999</v>
       </c>
@@ -21997,7 +22221,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" hidden="1">
       <c r="A370" t="s">
         <v>2004</v>
       </c>
@@ -22020,7 +22244,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" hidden="1">
       <c r="A371" t="s">
         <v>2009</v>
       </c>
@@ -22043,7 +22267,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" hidden="1">
       <c r="A372" t="s">
         <v>2014</v>
       </c>
@@ -22066,7 +22290,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" hidden="1">
       <c r="A373" t="s">
         <v>2018</v>
       </c>
@@ -22092,7 +22316,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" hidden="1">
       <c r="A374" t="s">
         <v>2024</v>
       </c>
@@ -22115,7 +22339,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" hidden="1">
       <c r="A375" t="s">
         <v>2029</v>
       </c>
@@ -22138,7 +22362,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" hidden="1">
       <c r="A376" t="s">
         <v>2034</v>
       </c>
@@ -22164,7 +22388,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" hidden="1">
       <c r="A377" t="s">
         <v>2040</v>
       </c>
@@ -22190,7 +22414,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" hidden="1">
       <c r="A378" t="s">
         <v>2046</v>
       </c>
@@ -22216,7 +22440,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" hidden="1">
       <c r="A379" t="s">
         <v>2052</v>
       </c>
@@ -22242,7 +22466,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" hidden="1">
       <c r="A380" t="s">
         <v>2058</v>
       </c>
@@ -22265,7 +22489,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" hidden="1">
       <c r="A381" t="s">
         <v>2063</v>
       </c>
@@ -22288,7 +22512,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" hidden="1">
       <c r="A382" t="s">
         <v>2068</v>
       </c>
@@ -22314,7 +22538,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" hidden="1">
       <c r="A383" t="s">
         <v>2074</v>
       </c>
@@ -22337,7 +22561,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" hidden="1">
       <c r="A384" t="s">
         <v>2079</v>
       </c>
@@ -22360,7 +22584,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" hidden="1">
       <c r="A385" t="s">
         <v>2084</v>
       </c>
@@ -22386,7 +22610,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" hidden="1">
       <c r="A386" t="s">
         <v>2090</v>
       </c>
@@ -22412,7 +22636,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" hidden="1">
       <c r="A387" t="s">
         <v>2096</v>
       </c>
@@ -22435,7 +22659,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" hidden="1">
       <c r="A388" t="s">
         <v>2101</v>
       </c>
@@ -22458,7 +22682,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" hidden="1">
       <c r="A389" t="s">
         <v>2106</v>
       </c>
@@ -22484,7 +22708,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" hidden="1">
       <c r="A390" t="s">
         <v>2112</v>
       </c>
@@ -22510,7 +22734,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" hidden="1">
       <c r="A391" t="s">
         <v>2118</v>
       </c>
@@ -22536,7 +22760,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" hidden="1">
       <c r="A392" t="s">
         <v>2124</v>
       </c>
@@ -22562,7 +22786,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" hidden="1">
       <c r="A393" t="s">
         <v>2130</v>
       </c>
@@ -22588,7 +22812,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" hidden="1">
       <c r="A394" t="s">
         <v>2136</v>
       </c>
@@ -22614,7 +22838,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" hidden="1">
       <c r="A395" t="s">
         <v>2142</v>
       </c>
@@ -22640,7 +22864,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" hidden="1">
       <c r="A396" t="s">
         <v>2148</v>
       </c>
@@ -22666,7 +22890,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" hidden="1">
       <c r="A397" t="s">
         <v>2154</v>
       </c>
@@ -22692,7 +22916,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" hidden="1">
       <c r="A398" t="s">
         <v>2160</v>
       </c>
@@ -22715,7 +22939,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" hidden="1">
       <c r="A399" t="s">
         <v>2165</v>
       </c>
@@ -22738,7 +22962,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" hidden="1">
       <c r="A400" t="s">
         <v>2170</v>
       </c>
@@ -22764,7 +22988,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" hidden="1">
       <c r="A401" t="s">
         <v>2176</v>
       </c>
@@ -22790,7 +23014,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" hidden="1">
       <c r="A402" t="s">
         <v>2182</v>
       </c>
@@ -22813,7 +23037,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" hidden="1">
       <c r="A403" t="s">
         <v>2187</v>
       </c>
@@ -22836,7 +23060,7 @@
         <v>2191</v>
       </c>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" hidden="1">
       <c r="A404" t="s">
         <v>2192</v>
       </c>
@@ -22859,7 +23083,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" hidden="1">
       <c r="A405" t="s">
         <v>2197</v>
       </c>
@@ -22882,7 +23106,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" hidden="1">
       <c r="A406" t="s">
         <v>2202</v>
       </c>
@@ -22908,7 +23132,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" hidden="1">
       <c r="A407" t="s">
         <v>2208</v>
       </c>
@@ -22934,7 +23158,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" hidden="1">
       <c r="A408" t="s">
         <v>2214</v>
       </c>
@@ -22957,7 +23181,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" hidden="1">
       <c r="A409" t="s">
         <v>2219</v>
       </c>
@@ -22983,7 +23207,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" hidden="1">
       <c r="A410" t="s">
         <v>2225</v>
       </c>
@@ -23006,7 +23230,7 @@
         <v>2229</v>
       </c>
     </row>
-    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" hidden="1">
       <c r="A411" t="s">
         <v>2230</v>
       </c>
@@ -23029,7 +23253,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" hidden="1">
       <c r="A412" t="s">
         <v>2235</v>
       </c>
@@ -23052,7 +23276,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" hidden="1">
       <c r="A413" t="s">
         <v>2240</v>
       </c>
@@ -23078,7 +23302,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" hidden="1">
       <c r="A414" t="s">
         <v>2246</v>
       </c>
@@ -23101,7 +23325,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" hidden="1">
       <c r="A415" t="s">
         <v>2251</v>
       </c>
@@ -23124,7 +23348,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" hidden="1">
       <c r="A416" t="s">
         <v>2256</v>
       </c>
@@ -23147,7 +23371,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" hidden="1">
       <c r="A417" t="s">
         <v>2261</v>
       </c>
@@ -23173,7 +23397,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" hidden="1">
       <c r="A418" t="s">
         <v>2267</v>
       </c>
@@ -23199,7 +23423,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" hidden="1">
       <c r="A419" t="s">
         <v>2273</v>
       </c>
@@ -23222,7 +23446,7 @@
         <v>2277</v>
       </c>
     </row>
-    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" hidden="1">
       <c r="A420" t="s">
         <v>2278</v>
       </c>
@@ -23245,7 +23469,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" hidden="1">
       <c r="A421" t="s">
         <v>2283</v>
       </c>
@@ -23271,7 +23495,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" hidden="1">
       <c r="A422" t="s">
         <v>2289</v>
       </c>
@@ -23297,7 +23521,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" hidden="1">
       <c r="A423" t="s">
         <v>2295</v>
       </c>
@@ -23320,7 +23544,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" hidden="1">
       <c r="A424" t="s">
         <v>2300</v>
       </c>
@@ -23346,7 +23570,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" hidden="1">
       <c r="A425" t="s">
         <v>2306</v>
       </c>
@@ -23369,7 +23593,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" hidden="1">
       <c r="A426" t="s">
         <v>2311</v>
       </c>
@@ -23395,7 +23619,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" hidden="1">
       <c r="A427" t="s">
         <v>2317</v>
       </c>
@@ -23418,7 +23642,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" hidden="1">
       <c r="A428" t="s">
         <v>2322</v>
       </c>
@@ -23444,7 +23668,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" hidden="1">
       <c r="A429" t="s">
         <v>2328</v>
       </c>
@@ -23467,7 +23691,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" hidden="1">
       <c r="A430" t="s">
         <v>2333</v>
       </c>
@@ -23490,7 +23714,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" hidden="1">
       <c r="A431" t="s">
         <v>2338</v>
       </c>
@@ -23516,7 +23740,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" hidden="1">
       <c r="A432" t="s">
         <v>2344</v>
       </c>
@@ -23542,7 +23766,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" hidden="1">
       <c r="A433" t="s">
         <v>2350</v>
       </c>
@@ -23568,7 +23792,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" hidden="1">
       <c r="A434" t="s">
         <v>2356</v>
       </c>
@@ -23594,7 +23818,7 @@
         <v>2361</v>
       </c>
     </row>
-    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" hidden="1">
       <c r="A435" t="s">
         <v>2362</v>
       </c>
@@ -23620,7 +23844,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" hidden="1">
       <c r="A436" t="s">
         <v>2368</v>
       </c>
@@ -23646,7 +23870,7 @@
         <v>2373</v>
       </c>
     </row>
-    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" hidden="1">
       <c r="A437" t="s">
         <v>2374</v>
       </c>
@@ -23669,7 +23893,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" hidden="1">
       <c r="A438" t="s">
         <v>2379</v>
       </c>
@@ -23695,7 +23919,7 @@
         <v>2384</v>
       </c>
     </row>
-    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" hidden="1">
       <c r="A439" t="s">
         <v>2385</v>
       </c>
@@ -23721,7 +23945,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" hidden="1">
       <c r="A440" t="s">
         <v>2391</v>
       </c>
@@ -23747,7 +23971,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" hidden="1">
       <c r="A441" t="s">
         <v>2397</v>
       </c>
@@ -23773,7 +23997,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" hidden="1">
       <c r="A442" t="s">
         <v>2403</v>
       </c>
@@ -23799,7 +24023,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" hidden="1">
       <c r="A443" t="s">
         <v>2409</v>
       </c>
@@ -23825,7 +24049,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" hidden="1">
       <c r="A444" t="s">
         <v>2415</v>
       </c>
@@ -23848,7 +24072,7 @@
         <v>2419</v>
       </c>
     </row>
-    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" hidden="1">
       <c r="A445" t="s">
         <v>2420</v>
       </c>
@@ -23871,7 +24095,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" hidden="1">
       <c r="A446" t="s">
         <v>2425</v>
       </c>
@@ -23897,7 +24121,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" hidden="1">
       <c r="A447" t="s">
         <v>2431</v>
       </c>
@@ -23920,7 +24144,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" hidden="1">
       <c r="A448" t="s">
         <v>2436</v>
       </c>
@@ -23946,7 +24170,7 @@
         <v>2441</v>
       </c>
     </row>
-    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" hidden="1">
       <c r="A449" t="s">
         <v>2442</v>
       </c>
@@ -23969,7 +24193,7 @@
         <v>2446</v>
       </c>
     </row>
-    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" hidden="1">
       <c r="A450" t="s">
         <v>2447</v>
       </c>
@@ -23995,7 +24219,7 @@
         <v>2452</v>
       </c>
     </row>
-    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" hidden="1">
       <c r="A451" t="s">
         <v>2453</v>
       </c>
@@ -24021,7 +24245,7 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" hidden="1">
       <c r="A452" t="s">
         <v>2459</v>
       </c>
@@ -24047,7 +24271,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" hidden="1">
       <c r="A453" t="s">
         <v>2464</v>
       </c>
@@ -24073,7 +24297,7 @@
         <v>2469</v>
       </c>
     </row>
-    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" hidden="1">
       <c r="A454" t="s">
         <v>2470</v>
       </c>
@@ -24096,7 +24320,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" hidden="1">
       <c r="A455" t="s">
         <v>2475</v>
       </c>
@@ -24122,7 +24346,7 @@
         <v>2480</v>
       </c>
     </row>
-    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" hidden="1">
       <c r="A456" t="s">
         <v>2481</v>
       </c>
@@ -24148,7 +24372,7 @@
         <v>2486</v>
       </c>
     </row>
-    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" hidden="1">
       <c r="A457" t="s">
         <v>2487</v>
       </c>
@@ -24171,7 +24395,7 @@
         <v>2491</v>
       </c>
     </row>
-    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" hidden="1">
       <c r="A458" t="s">
         <v>2492</v>
       </c>
@@ -24194,7 +24418,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" hidden="1">
       <c r="A459" t="s">
         <v>2497</v>
       </c>
@@ -24220,7 +24444,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" hidden="1">
       <c r="A460" t="s">
         <v>2503</v>
       </c>
@@ -24246,7 +24470,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" hidden="1">
       <c r="A461" t="s">
         <v>2509</v>
       </c>
@@ -24272,7 +24496,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" hidden="1">
       <c r="A462" t="s">
         <v>2515</v>
       </c>
@@ -24298,7 +24522,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" hidden="1">
       <c r="A463" t="s">
         <v>2521</v>
       </c>
@@ -24324,7 +24548,7 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" hidden="1">
       <c r="A464" t="s">
         <v>2527</v>
       </c>
@@ -24350,7 +24574,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" hidden="1">
       <c r="A465" t="s">
         <v>2533</v>
       </c>
@@ -24373,7 +24597,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" hidden="1">
       <c r="A466" t="s">
         <v>2538</v>
       </c>
@@ -24396,7 +24620,7 @@
         <v>2542</v>
       </c>
     </row>
-    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" hidden="1">
       <c r="A467" t="s">
         <v>2543</v>
       </c>
@@ -24419,7 +24643,7 @@
         <v>2547</v>
       </c>
     </row>
-    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" hidden="1">
       <c r="A468" t="s">
         <v>2548</v>
       </c>
@@ -24445,7 +24669,7 @@
         <v>2553</v>
       </c>
     </row>
-    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" hidden="1">
       <c r="A469" t="s">
         <v>2554</v>
       </c>
@@ -24471,7 +24695,7 @@
         <v>2559</v>
       </c>
     </row>
-    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" hidden="1">
       <c r="A470" t="s">
         <v>2560</v>
       </c>
@@ -24497,7 +24721,7 @@
         <v>2565</v>
       </c>
     </row>
-    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" hidden="1">
       <c r="A471" t="s">
         <v>2566</v>
       </c>
@@ -24523,7 +24747,7 @@
         <v>2571</v>
       </c>
     </row>
-    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" hidden="1">
       <c r="A472" t="s">
         <v>2572</v>
       </c>
@@ -24546,7 +24770,7 @@
         <v>2576</v>
       </c>
     </row>
-    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" hidden="1">
       <c r="A473" t="s">
         <v>2577</v>
       </c>
@@ -24569,7 +24793,7 @@
         <v>2581</v>
       </c>
     </row>
-    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" hidden="1">
       <c r="A474" t="s">
         <v>2582</v>
       </c>
@@ -24595,7 +24819,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" hidden="1">
       <c r="A475" t="s">
         <v>2588</v>
       </c>
@@ -24618,7 +24842,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" hidden="1">
       <c r="A476" t="s">
         <v>2593</v>
       </c>
@@ -24644,7 +24868,7 @@
         <v>2598</v>
       </c>
     </row>
-    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" hidden="1">
       <c r="A477" t="s">
         <v>2599</v>
       </c>
@@ -24670,7 +24894,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" hidden="1">
       <c r="A478" t="s">
         <v>2605</v>
       </c>
@@ -24696,7 +24920,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" hidden="1">
       <c r="A479" t="s">
         <v>2611</v>
       </c>
@@ -24722,7 +24946,7 @@
         <v>2616</v>
       </c>
     </row>
-    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" hidden="1">
       <c r="A480" t="s">
         <v>2617</v>
       </c>
@@ -24745,7 +24969,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" hidden="1">
       <c r="A481" t="s">
         <v>2622</v>
       </c>
@@ -24771,7 +24995,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" hidden="1">
       <c r="A482" t="s">
         <v>2628</v>
       </c>
@@ -24797,7 +25021,7 @@
         <v>2632</v>
       </c>
     </row>
-    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" hidden="1">
       <c r="A483" t="s">
         <v>2633</v>
       </c>
@@ -24820,7 +25044,7 @@
         <v>2637</v>
       </c>
     </row>
-    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" hidden="1">
       <c r="A484" t="s">
         <v>2638</v>
       </c>
@@ -24846,7 +25070,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" hidden="1">
       <c r="A485" t="s">
         <v>2643</v>
       </c>
@@ -24869,7 +25093,7 @@
         <v>2647</v>
       </c>
     </row>
-    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" hidden="1">
       <c r="A486" t="s">
         <v>2648</v>
       </c>
@@ -24892,7 +25116,7 @@
         <v>2652</v>
       </c>
     </row>
-    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" hidden="1">
       <c r="A487" t="s">
         <v>2653</v>
       </c>
@@ -24918,7 +25142,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" hidden="1">
       <c r="A488" t="s">
         <v>2659</v>
       </c>
@@ -24941,7 +25165,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" hidden="1">
       <c r="A489" t="s">
         <v>2664</v>
       </c>
@@ -24967,7 +25191,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" hidden="1">
       <c r="A490" t="s">
         <v>2670</v>
       </c>
@@ -24993,7 +25217,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" hidden="1">
       <c r="A491" t="s">
         <v>2675</v>
       </c>
@@ -25019,7 +25243,7 @@
         <v>2680</v>
       </c>
     </row>
-    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" hidden="1">
       <c r="A492" t="s">
         <v>2681</v>
       </c>
@@ -25042,7 +25266,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" hidden="1">
       <c r="A493" t="s">
         <v>2686</v>
       </c>
@@ -25068,7 +25292,7 @@
         <v>2691</v>
       </c>
     </row>
-    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" hidden="1">
       <c r="A494" t="s">
         <v>2692</v>
       </c>
@@ -25094,7 +25318,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" hidden="1">
       <c r="A495" t="s">
         <v>2698</v>
       </c>
@@ -25117,7 +25341,7 @@
         <v>2702</v>
       </c>
     </row>
-    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" hidden="1">
       <c r="A496" t="s">
         <v>2703</v>
       </c>
@@ -25140,7 +25364,7 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" hidden="1">
       <c r="A497" t="s">
         <v>2708</v>
       </c>
@@ -25166,7 +25390,7 @@
         <v>2713</v>
       </c>
     </row>
-    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" hidden="1">
       <c r="A498" t="s">
         <v>2714</v>
       </c>
@@ -25189,7 +25413,7 @@
         <v>2718</v>
       </c>
     </row>
-    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" hidden="1">
       <c r="A499" t="s">
         <v>2719</v>
       </c>
@@ -25215,7 +25439,7 @@
         <v>2724</v>
       </c>
     </row>
-    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" hidden="1">
       <c r="A500" t="s">
         <v>2725</v>
       </c>
@@ -25241,7 +25465,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" hidden="1">
       <c r="A501" t="s">
         <v>2731</v>
       </c>
@@ -25267,7 +25491,7 @@
         <v>2736</v>
       </c>
     </row>
-    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" hidden="1">
       <c r="A502" t="s">
         <v>2737</v>
       </c>
@@ -25290,7 +25514,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" hidden="1">
       <c r="A503" t="s">
         <v>2742</v>
       </c>
@@ -25313,7 +25537,7 @@
         <v>2746</v>
       </c>
     </row>
-    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" hidden="1">
       <c r="A504" t="s">
         <v>2747</v>
       </c>
@@ -25336,7 +25560,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" hidden="1">
       <c r="A505" t="s">
         <v>2752</v>
       </c>
@@ -25362,7 +25586,7 @@
         <v>2757</v>
       </c>
     </row>
-    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" hidden="1">
       <c r="A506" t="s">
         <v>2758</v>
       </c>
@@ -25388,7 +25612,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" hidden="1">
       <c r="A507" t="s">
         <v>2764</v>
       </c>
@@ -25414,7 +25638,7 @@
         <v>2769</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="508">
       <c r="A508" t="s">
         <v>2770</v>
       </c>
@@ -25440,7 +25664,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" hidden="1">
       <c r="A509" t="s">
         <v>2775</v>
       </c>
@@ -25463,7 +25687,7 @@
         <v>2779</v>
       </c>
     </row>
-    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" hidden="1">
       <c r="A510" t="s">
         <v>2780</v>
       </c>
@@ -25486,7 +25710,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" hidden="1">
       <c r="A511" t="s">
         <v>2785</v>
       </c>
@@ -25512,7 +25736,7 @@
         <v>2790</v>
       </c>
     </row>
-    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" hidden="1">
       <c r="A512" t="s">
         <v>2791</v>
       </c>
@@ -25535,7 +25759,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" hidden="1">
       <c r="A513" t="s">
         <v>2796</v>
       </c>
@@ -25561,7 +25785,7 @@
         <v>2801</v>
       </c>
     </row>
-    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" hidden="1">
       <c r="A514" t="s">
         <v>2802</v>
       </c>
@@ -25584,7 +25808,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" hidden="1">
       <c r="A515" t="s">
         <v>2807</v>
       </c>
@@ -25610,7 +25834,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" hidden="1">
       <c r="A516" t="s">
         <v>2813</v>
       </c>
@@ -25633,7 +25857,7 @@
         <v>2817</v>
       </c>
     </row>
-    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" hidden="1">
       <c r="A517" t="s">
         <v>2818</v>
       </c>
@@ -25659,7 +25883,7 @@
         <v>2823</v>
       </c>
     </row>
-    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" hidden="1">
       <c r="A518" t="s">
         <v>2824</v>
       </c>
@@ -25682,7 +25906,7 @@
         <v>2828</v>
       </c>
     </row>
-    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" hidden="1">
       <c r="A519" t="s">
         <v>2829</v>
       </c>
@@ -25708,7 +25932,7 @@
         <v>2834</v>
       </c>
     </row>
-    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" hidden="1">
       <c r="A520" t="s">
         <v>2835</v>
       </c>
@@ -25731,7 +25955,7 @@
         <v>2839</v>
       </c>
     </row>
-    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" hidden="1">
       <c r="A521" t="s">
         <v>2840</v>
       </c>
@@ -25754,7 +25978,7 @@
         <v>2844</v>
       </c>
     </row>
-    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" hidden="1">
       <c r="A522" t="s">
         <v>2845</v>
       </c>
@@ -25777,7 +26001,7 @@
         <v>2849</v>
       </c>
     </row>
-    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" hidden="1">
       <c r="A523" t="s">
         <v>2850</v>
       </c>
@@ -25803,7 +26027,7 @@
         <v>2855</v>
       </c>
     </row>
-    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" hidden="1">
       <c r="A524" t="s">
         <v>2856</v>
       </c>
@@ -25829,7 +26053,7 @@
         <v>2861</v>
       </c>
     </row>
-    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" hidden="1">
       <c r="A525" t="s">
         <v>2862</v>
       </c>
@@ -25855,7 +26079,7 @@
         <v>2867</v>
       </c>
     </row>
-    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" hidden="1">
       <c r="A526" t="s">
         <v>2868</v>
       </c>
@@ -25878,7 +26102,7 @@
         <v>2872</v>
       </c>
     </row>
-    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" hidden="1">
       <c r="A527" t="s">
         <v>2873</v>
       </c>
@@ -25904,7 +26128,7 @@
         <v>2878</v>
       </c>
     </row>
-    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" hidden="1">
       <c r="A528" t="s">
         <v>2879</v>
       </c>
@@ -25927,7 +26151,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" hidden="1">
       <c r="A529" t="s">
         <v>2884</v>
       </c>
@@ -25953,7 +26177,7 @@
         <v>2889</v>
       </c>
     </row>
-    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" hidden="1">
       <c r="A530" t="s">
         <v>2890</v>
       </c>
@@ -25979,7 +26203,7 @@
         <v>2895</v>
       </c>
     </row>
-    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" hidden="1">
       <c r="A531" t="s">
         <v>2896</v>
       </c>
@@ -26002,7 +26226,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" hidden="1">
       <c r="A532" t="s">
         <v>2901</v>
       </c>
@@ -26025,7 +26249,7 @@
         <v>2905</v>
       </c>
     </row>
-    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" hidden="1">
       <c r="A533" t="s">
         <v>2906</v>
       </c>
@@ -26051,7 +26275,7 @@
         <v>2911</v>
       </c>
     </row>
-    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" hidden="1">
       <c r="A534" t="s">
         <v>2912</v>
       </c>
@@ -26077,7 +26301,7 @@
         <v>2917</v>
       </c>
     </row>
-    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" hidden="1">
       <c r="A535" t="s">
         <v>2918</v>
       </c>
@@ -26103,7 +26327,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" hidden="1">
       <c r="A536" t="s">
         <v>2924</v>
       </c>
@@ -26129,7 +26353,7 @@
         <v>2929</v>
       </c>
     </row>
-    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" hidden="1">
       <c r="A537" t="s">
         <v>2930</v>
       </c>
@@ -26155,7 +26379,7 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" hidden="1">
       <c r="A538" t="s">
         <v>2936</v>
       </c>
@@ -26181,7 +26405,7 @@
         <v>2941</v>
       </c>
     </row>
-    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" hidden="1">
       <c r="A539" t="s">
         <v>2942</v>
       </c>
@@ -26204,7 +26428,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" hidden="1">
       <c r="A540" t="s">
         <v>2947</v>
       </c>
@@ -26230,7 +26454,7 @@
         <v>2952</v>
       </c>
     </row>
-    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" hidden="1">
       <c r="A541" t="s">
         <v>2953</v>
       </c>
@@ -26253,7 +26477,7 @@
         <v>2957</v>
       </c>
     </row>
-    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" hidden="1">
       <c r="A542" t="s">
         <v>2958</v>
       </c>
@@ -26279,7 +26503,7 @@
         <v>2962</v>
       </c>
     </row>
-    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" hidden="1">
       <c r="A543" t="s">
         <v>2963</v>
       </c>
@@ -26305,7 +26529,7 @@
         <v>2968</v>
       </c>
     </row>
-    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" hidden="1">
       <c r="A544" t="s">
         <v>2969</v>
       </c>
@@ -26331,7 +26555,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" hidden="1">
       <c r="A545" t="s">
         <v>2975</v>
       </c>
@@ -26354,7 +26578,7 @@
         <v>2979</v>
       </c>
     </row>
-    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" hidden="1">
       <c r="A546" t="s">
         <v>2980</v>
       </c>
@@ -26380,7 +26604,7 @@
         <v>2985</v>
       </c>
     </row>
-    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" hidden="1">
       <c r="A547" t="s">
         <v>2986</v>
       </c>
@@ -26406,7 +26630,7 @@
         <v>2991</v>
       </c>
     </row>
-    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" hidden="1">
       <c r="A548" t="s">
         <v>2992</v>
       </c>
@@ -26432,7 +26656,7 @@
         <v>2997</v>
       </c>
     </row>
-    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" hidden="1">
       <c r="A549" t="s">
         <v>2998</v>
       </c>
@@ -26458,7 +26682,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" hidden="1">
       <c r="A550" t="s">
         <v>3004</v>
       </c>
@@ -26481,7 +26705,7 @@
         <v>3008</v>
       </c>
     </row>
-    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" hidden="1">
       <c r="A551" t="s">
         <v>3009</v>
       </c>
@@ -26507,7 +26731,7 @@
         <v>3014</v>
       </c>
     </row>
-    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" hidden="1">
       <c r="A552" t="s">
         <v>3015</v>
       </c>
@@ -26530,7 +26754,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" hidden="1">
       <c r="A553" t="s">
         <v>3020</v>
       </c>
@@ -26556,7 +26780,7 @@
         <v>3025</v>
       </c>
     </row>
-    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" hidden="1">
       <c r="A554" t="s">
         <v>3026</v>
       </c>
@@ -26579,7 +26803,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" hidden="1">
       <c r="A555" t="s">
         <v>3031</v>
       </c>
@@ -26602,7 +26826,7 @@
         <v>3035</v>
       </c>
     </row>
-    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" hidden="1">
       <c r="A556" t="s">
         <v>3036</v>
       </c>
@@ -26628,7 +26852,7 @@
         <v>3041</v>
       </c>
     </row>
-    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" hidden="1">
       <c r="A557" t="s">
         <v>3042</v>
       </c>
@@ -26651,7 +26875,7 @@
         <v>3046</v>
       </c>
     </row>
-    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" hidden="1">
       <c r="A558" t="s">
         <v>3047</v>
       </c>
@@ -26677,7 +26901,7 @@
         <v>3052</v>
       </c>
     </row>
-    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" hidden="1">
       <c r="A559" t="s">
         <v>3053</v>
       </c>
@@ -26703,7 +26927,7 @@
         <v>3058</v>
       </c>
     </row>
-    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" hidden="1">
       <c r="A560" t="s">
         <v>3059</v>
       </c>
@@ -26726,7 +26950,7 @@
         <v>3063</v>
       </c>
     </row>
-    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" hidden="1">
       <c r="A561" t="s">
         <v>3064</v>
       </c>
@@ -26752,7 +26976,7 @@
         <v>3069</v>
       </c>
     </row>
-    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" hidden="1">
       <c r="A562" t="s">
         <v>3070</v>
       </c>
@@ -26778,7 +27002,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" hidden="1">
       <c r="A563" t="s">
         <v>3076</v>
       </c>
@@ -26804,7 +27028,7 @@
         <v>3081</v>
       </c>
     </row>
-    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" hidden="1">
       <c r="A564" t="s">
         <v>3082</v>
       </c>
@@ -26827,7 +27051,7 @@
         <v>3086</v>
       </c>
     </row>
-    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" hidden="1">
       <c r="A565" t="s">
         <v>3087</v>
       </c>
@@ -26853,7 +27077,7 @@
         <v>3092</v>
       </c>
     </row>
-    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" hidden="1">
       <c r="A566" t="s">
         <v>3093</v>
       </c>
@@ -26879,7 +27103,7 @@
         <v>3098</v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="567">
       <c r="A567" t="s">
         <v>3099</v>
       </c>
@@ -26905,7 +27129,7 @@
         <v>3104</v>
       </c>
     </row>
-    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" hidden="1">
       <c r="A568" t="s">
         <v>3105</v>
       </c>
@@ -26931,7 +27155,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" hidden="1">
       <c r="A569" t="s">
         <v>3111</v>
       </c>
@@ -26954,7 +27178,7 @@
         <v>3115</v>
       </c>
     </row>
-    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" hidden="1">
       <c r="A570" t="s">
         <v>3116</v>
       </c>
@@ -26980,7 +27204,7 @@
         <v>3121</v>
       </c>
     </row>
-    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" hidden="1">
       <c r="A571" t="s">
         <v>3122</v>
       </c>
@@ -27006,7 +27230,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" hidden="1">
       <c r="A572" t="s">
         <v>3128</v>
       </c>
@@ -27032,7 +27256,7 @@
         <v>3133</v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="573">
       <c r="A573" t="s">
         <v>3134</v>
       </c>
@@ -27058,7 +27282,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" hidden="1">
       <c r="A574" t="s">
         <v>3139</v>
       </c>
@@ -27084,7 +27308,7 @@
         <v>3144</v>
       </c>
     </row>
-    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" hidden="1">
       <c r="A575" t="s">
         <v>3145</v>
       </c>
@@ -27110,7 +27334,7 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" hidden="1">
       <c r="A576" t="s">
         <v>3151</v>
       </c>
@@ -27133,7 +27357,7 @@
         <v>3155</v>
       </c>
     </row>
-    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" hidden="1">
       <c r="A577" t="s">
         <v>3156</v>
       </c>
@@ -27159,7 +27383,7 @@
         <v>3161</v>
       </c>
     </row>
-    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" hidden="1">
       <c r="A578" t="s">
         <v>3162</v>
       </c>
@@ -27185,7 +27409,7 @@
         <v>3167</v>
       </c>
     </row>
-    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" hidden="1">
       <c r="A579" t="s">
         <v>3168</v>
       </c>
@@ -27211,7 +27435,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" hidden="1">
       <c r="A580" t="s">
         <v>3174</v>
       </c>
@@ -27237,7 +27461,7 @@
         <v>3179</v>
       </c>
     </row>
-    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" hidden="1">
       <c r="A581" t="s">
         <v>3180</v>
       </c>
@@ -27263,7 +27487,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" hidden="1">
       <c r="A582" t="s">
         <v>3186</v>
       </c>
@@ -27286,7 +27510,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" hidden="1">
       <c r="A583" t="s">
         <v>3191</v>
       </c>
@@ -27309,7 +27533,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" hidden="1">
       <c r="A584" t="s">
         <v>3196</v>
       </c>
@@ -27335,7 +27559,7 @@
         <v>3201</v>
       </c>
     </row>
-    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" hidden="1">
       <c r="A585" t="s">
         <v>3202</v>
       </c>
@@ -27361,7 +27585,7 @@
         <v>3207</v>
       </c>
     </row>
-    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" hidden="1">
       <c r="A586" t="s">
         <v>3208</v>
       </c>
@@ -27384,7 +27608,7 @@
         <v>3212</v>
       </c>
     </row>
-    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" hidden="1">
       <c r="A587" t="s">
         <v>3213</v>
       </c>
@@ -27407,7 +27631,7 @@
         <v>3217</v>
       </c>
     </row>
-    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" hidden="1">
       <c r="A588" t="s">
         <v>3218</v>
       </c>
@@ -27430,7 +27654,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" hidden="1">
       <c r="A589" t="s">
         <v>3223</v>
       </c>
@@ -27453,7 +27677,7 @@
         <v>3227</v>
       </c>
     </row>
-    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" hidden="1">
       <c r="A590" t="s">
         <v>3228</v>
       </c>
@@ -27476,7 +27700,7 @@
         <v>3232</v>
       </c>
     </row>
-    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" hidden="1">
       <c r="A591" t="s">
         <v>3233</v>
       </c>
@@ -27499,7 +27723,7 @@
         <v>3237</v>
       </c>
     </row>
-    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" hidden="1">
       <c r="A592" t="s">
         <v>3238</v>
       </c>
@@ -27522,7 +27746,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" hidden="1">
       <c r="A593" t="s">
         <v>3243</v>
       </c>
@@ -27545,7 +27769,7 @@
         <v>3247</v>
       </c>
     </row>
-    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" hidden="1">
       <c r="A594" t="s">
         <v>3248</v>
       </c>
@@ -27568,7 +27792,7 @@
         <v>3252</v>
       </c>
     </row>
-    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" hidden="1">
       <c r="A595" t="s">
         <v>3253</v>
       </c>
@@ -27591,7 +27815,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" hidden="1">
       <c r="A596" t="s">
         <v>3258</v>
       </c>
@@ -27617,7 +27841,7 @@
         <v>3263</v>
       </c>
     </row>
-    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" hidden="1">
       <c r="A597" t="s">
         <v>3264</v>
       </c>
@@ -27640,7 +27864,7 @@
         <v>3268</v>
       </c>
     </row>
-    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" hidden="1">
       <c r="A598" t="s">
         <v>3269</v>
       </c>
@@ -27663,7 +27887,7 @@
         <v>3273</v>
       </c>
     </row>
-    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" hidden="1">
       <c r="A599" t="s">
         <v>3274</v>
       </c>
@@ -27686,7 +27910,7 @@
         <v>3278</v>
       </c>
     </row>
-    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" hidden="1">
       <c r="A600" t="s">
         <v>3279</v>
       </c>
@@ -27709,7 +27933,7 @@
         <v>3283</v>
       </c>
     </row>
-    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" hidden="1">
       <c r="A601" t="s">
         <v>3284</v>
       </c>
@@ -27732,7 +27956,7 @@
         <v>3288</v>
       </c>
     </row>
-    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" hidden="1">
       <c r="A602" t="s">
         <v>3289</v>
       </c>
@@ -27758,7 +27982,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" hidden="1">
       <c r="A603" t="s">
         <v>3295</v>
       </c>
@@ -27781,7 +28005,7 @@
         <v>3299</v>
       </c>
     </row>
-    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" hidden="1">
       <c r="A604" t="s">
         <v>3300</v>
       </c>
@@ -27804,7 +28028,7 @@
         <v>3304</v>
       </c>
     </row>
-    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" hidden="1">
       <c r="A605" t="s">
         <v>3305</v>
       </c>
@@ -27827,7 +28051,7 @@
         <v>3309</v>
       </c>
     </row>
-    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" hidden="1">
       <c r="A606" t="s">
         <v>3310</v>
       </c>
@@ -27850,7 +28074,7 @@
         <v>3314</v>
       </c>
     </row>
-    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" hidden="1">
       <c r="A607" t="s">
         <v>3315</v>
       </c>
@@ -27876,7 +28100,7 @@
         <v>3320</v>
       </c>
     </row>
-    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" hidden="1">
       <c r="A608" t="s">
         <v>3321</v>
       </c>
@@ -27902,7 +28126,7 @@
         <v>3326</v>
       </c>
     </row>
-    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" hidden="1">
       <c r="A609" t="s">
         <v>3327</v>
       </c>
@@ -27928,7 +28152,7 @@
         <v>3332</v>
       </c>
     </row>
-    <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" hidden="1">
       <c r="A610" t="s">
         <v>3333</v>
       </c>
@@ -27954,7 +28178,7 @@
         <v>3338</v>
       </c>
     </row>
-    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" hidden="1">
       <c r="A611" t="s">
         <v>3339</v>
       </c>
@@ -27980,7 +28204,7 @@
         <v>3344</v>
       </c>
     </row>
-    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" hidden="1">
       <c r="A612" t="s">
         <v>3345</v>
       </c>
@@ -28006,7 +28230,7 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" hidden="1">
       <c r="A613" t="s">
         <v>3351</v>
       </c>
@@ -28032,7 +28256,7 @@
         <v>3356</v>
       </c>
     </row>
-    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" hidden="1">
       <c r="A614" t="s">
         <v>3357</v>
       </c>
@@ -28055,7 +28279,7 @@
         <v>3361</v>
       </c>
     </row>
-    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" hidden="1">
       <c r="A615" t="s">
         <v>3362</v>
       </c>
@@ -28078,7 +28302,7 @@
         <v>3366</v>
       </c>
     </row>
-    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" hidden="1">
       <c r="A616" t="s">
         <v>3367</v>
       </c>
@@ -28104,7 +28328,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" hidden="1">
       <c r="A617" t="s">
         <v>3373</v>
       </c>
@@ -28127,7 +28351,7 @@
         <v>3377</v>
       </c>
     </row>
-    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" hidden="1">
       <c r="A618" t="s">
         <v>3378</v>
       </c>
@@ -28150,7 +28374,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" hidden="1">
       <c r="A619" t="s">
         <v>3383</v>
       </c>
@@ -28176,7 +28400,7 @@
         <v>3388</v>
       </c>
     </row>
-    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" hidden="1">
       <c r="A620" t="s">
         <v>3389</v>
       </c>
@@ -28202,7 +28426,7 @@
         <v>3394</v>
       </c>
     </row>
-    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" hidden="1">
       <c r="A621" t="s">
         <v>3395</v>
       </c>
@@ -28228,7 +28452,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" hidden="1">
       <c r="A622" t="s">
         <v>3401</v>
       </c>
@@ -28254,7 +28478,7 @@
         <v>3406</v>
       </c>
     </row>
-    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" hidden="1">
       <c r="A623" t="s">
         <v>3407</v>
       </c>
@@ -28277,7 +28501,7 @@
         <v>3411</v>
       </c>
     </row>
-    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" hidden="1">
       <c r="A624" t="s">
         <v>3412</v>
       </c>
@@ -28303,7 +28527,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" hidden="1">
       <c r="A625" t="s">
         <v>3418</v>
       </c>
@@ -28326,7 +28550,7 @@
         <v>3422</v>
       </c>
     </row>
-    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" hidden="1">
       <c r="A626" t="s">
         <v>3423</v>
       </c>
@@ -28349,7 +28573,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" hidden="1">
       <c r="A627" t="s">
         <v>3428</v>
       </c>
@@ -28375,7 +28599,7 @@
         <v>3433</v>
       </c>
     </row>
-    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" hidden="1">
       <c r="A628" t="s">
         <v>3434</v>
       </c>
@@ -28401,7 +28625,7 @@
         <v>3439</v>
       </c>
     </row>
-    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" hidden="1">
       <c r="A629" t="s">
         <v>3440</v>
       </c>
@@ -28427,7 +28651,7 @@
         <v>3445</v>
       </c>
     </row>
-    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" hidden="1">
       <c r="A630" t="s">
         <v>3446</v>
       </c>
@@ -28450,7 +28674,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" hidden="1">
       <c r="A631" t="s">
         <v>3451</v>
       </c>
@@ -28476,7 +28700,7 @@
         <v>3456</v>
       </c>
     </row>
-    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" hidden="1">
       <c r="A632" t="s">
         <v>3457</v>
       </c>
@@ -28502,7 +28726,7 @@
         <v>3462</v>
       </c>
     </row>
-    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" hidden="1">
       <c r="A633" t="s">
         <v>3463</v>
       </c>
@@ -28528,7 +28752,7 @@
         <v>3468</v>
       </c>
     </row>
-    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" hidden="1">
       <c r="A634" t="s">
         <v>3469</v>
       </c>
@@ -28554,7 +28778,7 @@
         <v>3474</v>
       </c>
     </row>
-    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" hidden="1">
       <c r="A635" t="s">
         <v>3475</v>
       </c>
@@ -28580,7 +28804,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" hidden="1">
       <c r="A636" t="s">
         <v>3481</v>
       </c>
@@ -28606,7 +28830,7 @@
         <v>3486</v>
       </c>
     </row>
-    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" hidden="1">
       <c r="A637" t="s">
         <v>3487</v>
       </c>
@@ -28632,7 +28856,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" hidden="1">
       <c r="A638" t="s">
         <v>3493</v>
       </c>
@@ -28658,7 +28882,7 @@
         <v>3498</v>
       </c>
     </row>
-    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" hidden="1">
       <c r="A639" t="s">
         <v>3499</v>
       </c>
@@ -28684,7 +28908,7 @@
         <v>3504</v>
       </c>
     </row>
-    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" hidden="1">
       <c r="A640" t="s">
         <v>3505</v>
       </c>
@@ -28710,7 +28934,7 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" hidden="1">
       <c r="A641" t="s">
         <v>3511</v>
       </c>
@@ -28736,7 +28960,7 @@
         <v>3516</v>
       </c>
     </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" hidden="1">
       <c r="A642" t="s">
         <v>3517</v>
       </c>
@@ -28762,7 +28986,7 @@
         <v>3522</v>
       </c>
     </row>
-    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" hidden="1">
       <c r="A643" t="s">
         <v>3523</v>
       </c>
@@ -28785,7 +29009,7 @@
         <v>3527</v>
       </c>
     </row>
-    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" hidden="1">
       <c r="A644" t="s">
         <v>3528</v>
       </c>
@@ -28808,7 +29032,7 @@
         <v>3532</v>
       </c>
     </row>
-    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" hidden="1">
       <c r="A645" t="s">
         <v>3533</v>
       </c>
@@ -28834,7 +29058,7 @@
         <v>3538</v>
       </c>
     </row>
-    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" hidden="1">
       <c r="A646" t="s">
         <v>3539</v>
       </c>
@@ -28860,7 +29084,7 @@
         <v>3544</v>
       </c>
     </row>
-    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" hidden="1">
       <c r="A647" t="s">
         <v>3545</v>
       </c>
@@ -28883,7 +29107,7 @@
         <v>3549</v>
       </c>
     </row>
-    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" hidden="1">
       <c r="A648" t="s">
         <v>3550</v>
       </c>
@@ -28909,7 +29133,7 @@
         <v>3555</v>
       </c>
     </row>
-    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" hidden="1">
       <c r="A649" t="s">
         <v>3556</v>
       </c>
@@ -28935,7 +29159,7 @@
         <v>3561</v>
       </c>
     </row>
-    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" hidden="1">
       <c r="A650" t="s">
         <v>3562</v>
       </c>
@@ -28958,7 +29182,7 @@
         <v>3566</v>
       </c>
     </row>
-    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" hidden="1">
       <c r="A651" t="s">
         <v>3567</v>
       </c>
@@ -28984,7 +29208,7 @@
         <v>3572</v>
       </c>
     </row>
-    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" hidden="1">
       <c r="A652" t="s">
         <v>3573</v>
       </c>
@@ -29010,7 +29234,7 @@
         <v>3578</v>
       </c>
     </row>
-    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" hidden="1">
       <c r="A653" t="s">
         <v>3579</v>
       </c>
@@ -29036,7 +29260,7 @@
         <v>3584</v>
       </c>
     </row>
-    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" hidden="1">
       <c r="A654" t="s">
         <v>3585</v>
       </c>
@@ -29059,7 +29283,7 @@
         <v>3589</v>
       </c>
     </row>
-    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" hidden="1">
       <c r="A655" t="s">
         <v>3590</v>
       </c>
@@ -29085,7 +29309,7 @@
         <v>3595</v>
       </c>
     </row>
-    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" hidden="1">
       <c r="A656" t="s">
         <v>3596</v>
       </c>
@@ -29111,7 +29335,7 @@
         <v>3601</v>
       </c>
     </row>
-    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" hidden="1">
       <c r="A657" t="s">
         <v>3602</v>
       </c>
@@ -29134,7 +29358,7 @@
         <v>3606</v>
       </c>
     </row>
-    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" hidden="1">
       <c r="A658" t="s">
         <v>3607</v>
       </c>
@@ -29157,7 +29381,7 @@
         <v>3611</v>
       </c>
     </row>
-    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" hidden="1">
       <c r="A659" t="s">
         <v>3612</v>
       </c>
@@ -29183,7 +29407,7 @@
         <v>3617</v>
       </c>
     </row>
-    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" hidden="1">
       <c r="A660" t="s">
         <v>3618</v>
       </c>
@@ -29209,7 +29433,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" hidden="1">
       <c r="A661" t="s">
         <v>3624</v>
       </c>
@@ -29235,7 +29459,7 @@
         <v>3629</v>
       </c>
     </row>
-    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" hidden="1">
       <c r="A662" t="s">
         <v>3630</v>
       </c>
@@ -29261,7 +29485,7 @@
         <v>3635</v>
       </c>
     </row>
-    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" hidden="1">
       <c r="A663" t="s">
         <v>3636</v>
       </c>
@@ -29287,7 +29511,7 @@
         <v>3641</v>
       </c>
     </row>
-    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" hidden="1">
       <c r="A664" t="s">
         <v>3642</v>
       </c>
@@ -29313,7 +29537,7 @@
         <v>3647</v>
       </c>
     </row>
-    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" hidden="1">
       <c r="A665" t="s">
         <v>3648</v>
       </c>
@@ -29339,7 +29563,7 @@
         <v>3653</v>
       </c>
     </row>
-    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" hidden="1">
       <c r="A666" t="s">
         <v>3654</v>
       </c>
@@ -29365,7 +29589,7 @@
         <v>3659</v>
       </c>
     </row>
-    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" hidden="1">
       <c r="A667" t="s">
         <v>3660</v>
       </c>
@@ -29391,7 +29615,7 @@
         <v>3665</v>
       </c>
     </row>
-    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" hidden="1">
       <c r="A668" t="s">
         <v>3666</v>
       </c>
@@ -29417,7 +29641,7 @@
         <v>3671</v>
       </c>
     </row>
-    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" hidden="1">
       <c r="A669" t="s">
         <v>3672</v>
       </c>
@@ -29443,7 +29667,7 @@
         <v>3677</v>
       </c>
     </row>
-    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" hidden="1">
       <c r="A670" t="s">
         <v>3678</v>
       </c>
@@ -29466,7 +29690,7 @@
         <v>3682</v>
       </c>
     </row>
-    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" hidden="1">
       <c r="A671" t="s">
         <v>3683</v>
       </c>
@@ -29492,7 +29716,7 @@
         <v>3688</v>
       </c>
     </row>
-    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" hidden="1">
       <c r="A672" t="s">
         <v>3689</v>
       </c>
@@ -29515,7 +29739,7 @@
         <v>3693</v>
       </c>
     </row>
-    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" hidden="1">
       <c r="A673" t="s">
         <v>3694</v>
       </c>
@@ -29538,7 +29762,7 @@
         <v>3698</v>
       </c>
     </row>
-    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" hidden="1">
       <c r="A674" t="s">
         <v>3699</v>
       </c>
@@ -29564,7 +29788,7 @@
         <v>3704</v>
       </c>
     </row>
-    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" hidden="1">
       <c r="A675" t="s">
         <v>3705</v>
       </c>
@@ -29590,7 +29814,7 @@
         <v>3710</v>
       </c>
     </row>
-    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" hidden="1">
       <c r="A676" t="s">
         <v>3711</v>
       </c>
@@ -29616,7 +29840,7 @@
         <v>3716</v>
       </c>
     </row>
-    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" hidden="1">
       <c r="A677" t="s">
         <v>3717</v>
       </c>
@@ -29642,7 +29866,7 @@
         <v>3722</v>
       </c>
     </row>
-    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" hidden="1">
       <c r="A678" t="s">
         <v>3723</v>
       </c>
@@ -29668,7 +29892,7 @@
         <v>3728</v>
       </c>
     </row>
-    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" hidden="1">
       <c r="A679" t="s">
         <v>3729</v>
       </c>
@@ -29694,7 +29918,7 @@
         <v>3734</v>
       </c>
     </row>
-    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" hidden="1">
       <c r="A680" t="s">
         <v>3735</v>
       </c>
@@ -29720,7 +29944,7 @@
         <v>3740</v>
       </c>
     </row>
-    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" hidden="1">
       <c r="A681" t="s">
         <v>3741</v>
       </c>
@@ -29746,7 +29970,7 @@
         <v>3746</v>
       </c>
     </row>
-    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" hidden="1">
       <c r="A682" t="s">
         <v>3747</v>
       </c>
@@ -29772,7 +29996,7 @@
         <v>3752</v>
       </c>
     </row>
-    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" hidden="1">
       <c r="A683" t="s">
         <v>3753</v>
       </c>
@@ -29798,7 +30022,7 @@
         <v>3758</v>
       </c>
     </row>
-    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" hidden="1">
       <c r="A684" t="s">
         <v>3759</v>
       </c>
@@ -29824,7 +30048,7 @@
         <v>3764</v>
       </c>
     </row>
-    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" hidden="1">
       <c r="A685" t="s">
         <v>3765</v>
       </c>
@@ -29850,7 +30074,7 @@
         <v>3770</v>
       </c>
     </row>
-    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" hidden="1">
       <c r="A686" t="s">
         <v>3771</v>
       </c>
@@ -29876,7 +30100,7 @@
         <v>3776</v>
       </c>
     </row>
-    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" hidden="1">
       <c r="A687" t="s">
         <v>3777</v>
       </c>
@@ -29902,7 +30126,7 @@
         <v>3782</v>
       </c>
     </row>
-    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" hidden="1">
       <c r="A688" t="s">
         <v>3783</v>
       </c>
@@ -29928,7 +30152,7 @@
         <v>3788</v>
       </c>
     </row>
-    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" hidden="1">
       <c r="A689" t="s">
         <v>3789</v>
       </c>
@@ -29951,7 +30175,7 @@
         <v>3793</v>
       </c>
     </row>
-    <row r="690" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" hidden="1">
       <c r="A690" t="s">
         <v>3794</v>
       </c>
@@ -29977,7 +30201,7 @@
         <v>3799</v>
       </c>
     </row>
-    <row r="691" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" hidden="1">
       <c r="A691" t="s">
         <v>3800</v>
       </c>
@@ -30000,7 +30224,7 @@
         <v>3804</v>
       </c>
     </row>
-    <row r="692" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" hidden="1">
       <c r="A692" t="s">
         <v>3805</v>
       </c>
@@ -30023,7 +30247,7 @@
         <v>3809</v>
       </c>
     </row>
-    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" hidden="1">
       <c r="A693" t="s">
         <v>3810</v>
       </c>
@@ -30046,7 +30270,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="694" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" hidden="1">
       <c r="A694" t="s">
         <v>3815</v>
       </c>
@@ -30069,7 +30293,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="695" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" hidden="1">
       <c r="A695" t="s">
         <v>3820</v>
       </c>
@@ -30092,7 +30316,7 @@
         <v>3824</v>
       </c>
     </row>
-    <row r="696" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" hidden="1">
       <c r="A696" t="s">
         <v>3825</v>
       </c>
@@ -30115,7 +30339,7 @@
         <v>3829</v>
       </c>
     </row>
-    <row r="697" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" hidden="1">
       <c r="A697" t="s">
         <v>3830</v>
       </c>
@@ -30138,7 +30362,7 @@
         <v>3834</v>
       </c>
     </row>
-    <row r="698" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" hidden="1">
       <c r="A698" t="s">
         <v>3835</v>
       </c>
@@ -30161,7 +30385,7 @@
         <v>3839</v>
       </c>
     </row>
-    <row r="699" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" hidden="1">
       <c r="A699" t="s">
         <v>3840</v>
       </c>
@@ -30184,7 +30408,7 @@
         <v>3844</v>
       </c>
     </row>
-    <row r="700" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" hidden="1">
       <c r="A700" t="s">
         <v>3845</v>
       </c>
@@ -30207,7 +30431,7 @@
         <v>3849</v>
       </c>
     </row>
-    <row r="701" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" hidden="1">
       <c r="A701" t="s">
         <v>3850</v>
       </c>
@@ -30230,7 +30454,7 @@
         <v>3854</v>
       </c>
     </row>
-    <row r="702" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" hidden="1">
       <c r="A702" t="s">
         <v>3855</v>
       </c>
@@ -30253,7 +30477,7 @@
         <v>3859</v>
       </c>
     </row>
-    <row r="703" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" hidden="1">
       <c r="A703" t="s">
         <v>3860</v>
       </c>
@@ -30276,7 +30500,7 @@
         <v>3864</v>
       </c>
     </row>
-    <row r="704" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" hidden="1">
       <c r="A704" t="s">
         <v>3865</v>
       </c>
@@ -30299,7 +30523,7 @@
         <v>3869</v>
       </c>
     </row>
-    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" hidden="1">
       <c r="A705" t="s">
         <v>3870</v>
       </c>
@@ -30322,7 +30546,7 @@
         <v>3874</v>
       </c>
     </row>
-    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" hidden="1">
       <c r="A706" t="s">
         <v>3875</v>
       </c>
@@ -30345,7 +30569,7 @@
         <v>3879</v>
       </c>
     </row>
-    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" hidden="1">
       <c r="A707" t="s">
         <v>3880</v>
       </c>
@@ -30368,7 +30592,7 @@
         <v>3884</v>
       </c>
     </row>
-    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" hidden="1">
       <c r="A708" t="s">
         <v>3885</v>
       </c>
@@ -30391,7 +30615,7 @@
         <v>3889</v>
       </c>
     </row>
-    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" hidden="1">
       <c r="A709" t="s">
         <v>3890</v>
       </c>
@@ -30414,7 +30638,7 @@
         <v>3894</v>
       </c>
     </row>
-    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" hidden="1">
       <c r="A710" t="s">
         <v>3895</v>
       </c>
@@ -30440,7 +30664,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" hidden="1">
       <c r="A711" t="s">
         <v>3901</v>
       </c>
@@ -30466,7 +30690,7 @@
         <v>3906</v>
       </c>
     </row>
-    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" hidden="1">
       <c r="A712" t="s">
         <v>3907</v>
       </c>
@@ -30492,7 +30716,7 @@
         <v>3912</v>
       </c>
     </row>
-    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" hidden="1">
       <c r="A713" t="s">
         <v>3913</v>
       </c>
@@ -30518,7 +30742,7 @@
         <v>3918</v>
       </c>
     </row>
-    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" hidden="1">
       <c r="A714" t="s">
         <v>3919</v>
       </c>
@@ -30544,7 +30768,7 @@
         <v>3924</v>
       </c>
     </row>
-    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" hidden="1">
       <c r="A715" t="s">
         <v>3925</v>
       </c>
@@ -30570,7 +30794,7 @@
         <v>3930</v>
       </c>
     </row>
-    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" hidden="1">
       <c r="A716" t="s">
         <v>3931</v>
       </c>
@@ -30596,7 +30820,7 @@
         <v>3936</v>
       </c>
     </row>
-    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" hidden="1">
       <c r="A717" t="s">
         <v>3937</v>
       </c>
@@ -30622,7 +30846,7 @@
         <v>3942</v>
       </c>
     </row>
-    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" hidden="1">
       <c r="A718" t="s">
         <v>3943</v>
       </c>
@@ -30648,7 +30872,7 @@
         <v>3948</v>
       </c>
     </row>
-    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" hidden="1">
       <c r="A719" t="s">
         <v>3949</v>
       </c>
@@ -30674,7 +30898,7 @@
         <v>3954</v>
       </c>
     </row>
-    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" hidden="1">
       <c r="A720" t="s">
         <v>3955</v>
       </c>
@@ -30700,7 +30924,7 @@
         <v>3960</v>
       </c>
     </row>
-    <row r="721" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" hidden="1">
       <c r="A721" t="s">
         <v>3961</v>
       </c>
@@ -30726,7 +30950,7 @@
         <v>3966</v>
       </c>
     </row>
-    <row r="722" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" hidden="1">
       <c r="A722" t="s">
         <v>3967</v>
       </c>
@@ -30752,7 +30976,7 @@
         <v>3972</v>
       </c>
     </row>
-    <row r="723" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" hidden="1">
       <c r="A723" t="s">
         <v>3973</v>
       </c>
@@ -30778,7 +31002,7 @@
         <v>3978</v>
       </c>
     </row>
-    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" hidden="1">
       <c r="A724" t="s">
         <v>3979</v>
       </c>
@@ -30804,7 +31028,7 @@
         <v>3984</v>
       </c>
     </row>
-    <row r="725" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" hidden="1">
       <c r="A725" t="s">
         <v>3985</v>
       </c>
@@ -30830,7 +31054,7 @@
         <v>3990</v>
       </c>
     </row>
-    <row r="726" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" hidden="1">
       <c r="A726" t="s">
         <v>3991</v>
       </c>
@@ -30853,7 +31077,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" hidden="1">
       <c r="A727" t="s">
         <v>3996</v>
       </c>
@@ -30876,7 +31100,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" hidden="1">
       <c r="A728" t="s">
         <v>4001</v>
       </c>
@@ -30902,7 +31126,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="729" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" hidden="1">
       <c r="A729" t="s">
         <v>4007</v>
       </c>
@@ -30928,7 +31152,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="730" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" hidden="1">
       <c r="A730" t="s">
         <v>4013</v>
       </c>
@@ -30954,7 +31178,7 @@
         <v>4018</v>
       </c>
     </row>
-    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" hidden="1">
       <c r="A731" t="s">
         <v>4019</v>
       </c>
@@ -30980,7 +31204,7 @@
         <v>4024</v>
       </c>
     </row>
-    <row r="732" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" hidden="1">
       <c r="A732" t="s">
         <v>4025</v>
       </c>
@@ -31006,7 +31230,7 @@
         <v>4030</v>
       </c>
     </row>
-    <row r="733" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" hidden="1">
       <c r="A733" t="s">
         <v>4031</v>
       </c>
@@ -31032,7 +31256,7 @@
         <v>4036</v>
       </c>
     </row>
-    <row r="734" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" hidden="1">
       <c r="A734" t="s">
         <v>4037</v>
       </c>
@@ -31058,7 +31282,7 @@
         <v>4042</v>
       </c>
     </row>
-    <row r="735" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" hidden="1">
       <c r="A735" t="s">
         <v>4043</v>
       </c>
@@ -31084,7 +31308,7 @@
         <v>4048</v>
       </c>
     </row>
-    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" hidden="1">
       <c r="A736" t="s">
         <v>4049</v>
       </c>
@@ -31110,7 +31334,7 @@
         <v>4054</v>
       </c>
     </row>
-    <row r="737" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" hidden="1">
       <c r="A737" t="s">
         <v>4055</v>
       </c>
@@ -31136,7 +31360,7 @@
         <v>4060</v>
       </c>
     </row>
-    <row r="738" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" hidden="1">
       <c r="A738" t="s">
         <v>4061</v>
       </c>
@@ -31162,7 +31386,7 @@
         <v>4066</v>
       </c>
     </row>
-    <row r="739" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" hidden="1">
       <c r="A739" t="s">
         <v>4067</v>
       </c>
@@ -31188,7 +31412,7 @@
         <v>4072</v>
       </c>
     </row>
-    <row r="740" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" hidden="1">
       <c r="A740" t="s">
         <v>4073</v>
       </c>
@@ -31214,7 +31438,7 @@
         <v>4078</v>
       </c>
     </row>
-    <row r="741" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" hidden="1">
       <c r="A741" t="s">
         <v>4079</v>
       </c>
@@ -31240,7 +31464,7 @@
         <v>4084</v>
       </c>
     </row>
-    <row r="742" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" hidden="1">
       <c r="A742" t="s">
         <v>4085</v>
       </c>
@@ -31260,24 +31484,24 @@
         <v>3</v>
       </c>
       <c r="G742" t="s">
+        <v>887</v>
+      </c>
+      <c r="H742" t="s">
         <v>4089</v>
       </c>
-      <c r="H742" t="s">
+    </row>
+    <row r="743" hidden="1">
+      <c r="A743" t="s">
         <v>4090</v>
       </c>
-    </row>
-    <row r="743" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A743" t="s">
+      <c r="B743" t="s">
         <v>4091</v>
       </c>
-      <c r="B743" t="s">
+      <c r="C743" t="s">
         <v>4092</v>
       </c>
-      <c r="C743" t="s">
+      <c r="D743" t="s">
         <v>4093</v>
-      </c>
-      <c r="D743" t="s">
-        <v>4094</v>
       </c>
       <c r="E743">
         <v>36</v>
@@ -31289,21 +31513,21 @@
         <v>702</v>
       </c>
       <c r="H743" t="s">
+        <v>4094</v>
+      </c>
+    </row>
+    <row r="744" hidden="1">
+      <c r="A744" t="s">
         <v>4095</v>
       </c>
-    </row>
-    <row r="744" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A744" t="s">
+      <c r="B744" t="s">
         <v>4096</v>
       </c>
-      <c r="B744" t="s">
+      <c r="C744" t="s">
         <v>4097</v>
       </c>
-      <c r="C744" t="s">
+      <c r="D744" t="s">
         <v>4098</v>
-      </c>
-      <c r="D744" t="s">
-        <v>4099</v>
       </c>
       <c r="E744">
         <v>36</v>
@@ -31315,21 +31539,21 @@
         <v>195</v>
       </c>
       <c r="H744" t="s">
+        <v>4099</v>
+      </c>
+    </row>
+    <row r="745" hidden="1">
+      <c r="A745" t="s">
         <v>4100</v>
       </c>
-    </row>
-    <row r="745" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A745" t="s">
+      <c r="B745" t="s">
         <v>4101</v>
       </c>
-      <c r="B745" t="s">
+      <c r="C745" t="s">
         <v>4102</v>
       </c>
-      <c r="C745" t="s">
+      <c r="D745" t="s">
         <v>4103</v>
-      </c>
-      <c r="D745" t="s">
-        <v>4104</v>
       </c>
       <c r="E745">
         <v>35</v>
@@ -31338,24 +31562,24 @@
         <v>3</v>
       </c>
       <c r="G745" t="s">
+        <v>4104</v>
+      </c>
+      <c r="H745" t="s">
         <v>4105</v>
       </c>
-      <c r="H745" t="s">
+    </row>
+    <row r="746" hidden="1">
+      <c r="A746" t="s">
         <v>4106</v>
       </c>
-    </row>
-    <row r="746" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A746" t="s">
+      <c r="B746" t="s">
         <v>4107</v>
       </c>
-      <c r="B746" t="s">
+      <c r="C746" t="s">
         <v>4108</v>
       </c>
-      <c r="C746" t="s">
+      <c r="D746" t="s">
         <v>4109</v>
-      </c>
-      <c r="D746" t="s">
-        <v>4110</v>
       </c>
       <c r="E746">
         <v>34</v>
@@ -31364,14 +31588,14 @@
         <v>3</v>
       </c>
       <c r="G746" t="s">
+        <v>4110</v>
+      </c>
+      <c r="H746" t="s">
         <v>4111</v>
       </c>
-      <c r="H746" t="s">
-        <v>4112</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I746" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:I746">
     <filterColumn colId="2">
       <filters>
         <filter val="Maps"/>
@@ -31383,88 +31607,123 @@
       </filters>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"Vertaald"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"Onvertaald"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{95B020A7-C0FB-4292-B40E-FE5B959A638D}">
+            <xm:f>"Vertaald"</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF006100"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFC6EFCE"/>
+                  <bgColor rgb="FFC6EFCE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G:G</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{B3E5C46B-EECF-4E19-A663-21BE19D49B9E}">
+            <xm:f>"Onvertaald"</xm:f>
+            <x14:dxf>
+              <font>
+                <color rgb="FF9C0006"/>
+              </font>
+              <fill>
+                <patternFill patternType="solid">
+                  <fgColor rgb="FFFFC7CE"/>
+                  <bgColor rgb="FFFFC7CE"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>G:G</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1"/>
+    <col customWidth="1" min="1" max="1" width="22"/>
+    <col customWidth="1" min="2" max="2" width="25.28515625"/>
+    <col bestFit="1" min="3" max="3" width="9.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4113</v>
+        <v>4112</v>
       </c>
       <c r="B1" s="2">
         <f>SUMIF(Sheet1!G2:G997,"Vertaald",Sheet1!E2:E997)</f>
-        <v>646759</v>
+        <v>660264</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
       <c r="E1" t="s">
+        <v>4113</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
         <v>4114</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>4115</v>
       </c>
       <c r="B2" s="2">
         <f>SUMIF(Sheet1!G2:G997,"Onvertaald",Sheet1!E2:E997)</f>
-        <v>7438151</v>
+        <v>7424646</v>
       </c>
       <c r="D2" t="s">
         <v>195</v>
       </c>
       <c r="E2">
         <f>SUMIF(Sheet1!G2:G997,"Vertaald",Sheet1!E2:E997)</f>
-        <v>646759</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+        <v>660264</v>
+      </c>
+    </row>
+    <row r="3" ht="15">
       <c r="A3" s="1" t="s">
-        <v>4116</v>
+        <v>4115</v>
       </c>
       <c r="B3" s="3">
         <f>SUM(Sheet1!E2:E997)</f>
         <v>8084910</v>
       </c>
       <c r="D3" t="s">
-        <v>4111</v>
+        <v>4110</v>
       </c>
       <c r="E3">
         <f>SUMIF(Sheet1!G2:G997,"Onvertaald",Sheet1!E2:E997)</f>
-        <v>7438151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="46.5" x14ac:dyDescent="0.7">
+        <v>7424646</v>
+      </c>
+    </row>
+    <row r="4" ht="45">
       <c r="A4" s="1" t="s">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="B4" s="4">
         <f>B1/B3</f>
-        <v>7.9995819372138954E-2</v>
+        <v>0.08166621520833256</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/translation_dashboard.xlsx
+++ b/translation_dashboard.xlsx
@@ -13238,7 +13238,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="24.28515625"/>
     <col customWidth="1" min="2" max="2" width="56.140625"/>
@@ -13677,7 +13677,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -13798,7 +13798,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" hidden="1">
+    <row r="24">
       <c r="A24" t="s">
         <v>124</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="31" hidden="1">
+    <row r="31">
       <c r="A31" t="s">
         <v>160</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" hidden="1">
+    <row r="40">
       <c r="A40" t="s">
         <v>207</v>
       </c>
@@ -14224,7 +14224,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="42" hidden="1">
+    <row r="42">
       <c r="A42" t="s">
         <v>218</v>
       </c>
@@ -14273,7 +14273,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="44" hidden="1">
+    <row r="44">
       <c r="A44" t="s">
         <v>229</v>
       </c>
@@ -14299,7 +14299,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="45" hidden="1">
+    <row r="45">
       <c r="A45" t="s">
         <v>235</v>
       </c>
@@ -14486,7 +14486,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="53" hidden="1">
+    <row r="53">
       <c r="A53" t="s">
         <v>276</v>
       </c>
@@ -14535,7 +14535,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="55" hidden="1">
+    <row r="55">
       <c r="A55" t="s">
         <v>287</v>
       </c>
@@ -14561,7 +14561,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="56" hidden="1">
+    <row r="56">
       <c r="A56" t="s">
         <v>293</v>
       </c>
@@ -14863,7 +14863,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="69" hidden="1">
+    <row r="69">
       <c r="A69" t="s">
         <v>359</v>
       </c>
@@ -14889,7 +14889,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="70" hidden="1">
+    <row r="70">
       <c r="A70" t="s">
         <v>365</v>
       </c>
@@ -15030,7 +15030,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="76" hidden="1">
+    <row r="76">
       <c r="A76" t="s">
         <v>396</v>
       </c>
@@ -15240,7 +15240,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="85" hidden="1">
+    <row r="85">
       <c r="A85" t="s">
         <v>442</v>
       </c>
@@ -15335,7 +15335,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="89" hidden="1">
+    <row r="89">
       <c r="A89" t="s">
         <v>463</v>
       </c>
@@ -15407,7 +15407,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="92" hidden="1">
+    <row r="92">
       <c r="A92" t="s">
         <v>479</v>
       </c>
@@ -15502,7 +15502,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="96" hidden="1">
+    <row r="96">
       <c r="A96" t="s">
         <v>500</v>
       </c>
@@ -15597,7 +15597,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="100" hidden="1">
+    <row r="100">
       <c r="A100" t="s">
         <v>521</v>
       </c>
@@ -15669,7 +15669,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="103" hidden="1">
+    <row r="103">
       <c r="A103" t="s">
         <v>537</v>
       </c>
@@ -15695,7 +15695,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="104" hidden="1">
+    <row r="104">
       <c r="A104" t="s">
         <v>543</v>
       </c>
@@ -15790,7 +15790,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="108" hidden="1">
+    <row r="108">
       <c r="A108" t="s">
         <v>564</v>
       </c>
@@ -15816,7 +15816,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="109" hidden="1">
+    <row r="109">
       <c r="A109" t="s">
         <v>570</v>
       </c>
@@ -15888,7 +15888,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="112" hidden="1">
+    <row r="112">
       <c r="A112" t="s">
         <v>586</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="114" hidden="1">
+    <row r="114">
       <c r="A114" t="s">
         <v>597</v>
       </c>
@@ -16081,7 +16081,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="120" hidden="1">
+    <row r="120">
       <c r="A120" t="s">
         <v>628</v>
       </c>
@@ -16130,7 +16130,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="122" hidden="1">
+    <row r="122">
       <c r="A122" t="s">
         <v>639</v>
       </c>
@@ -16179,7 +16179,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="124" hidden="1">
+    <row r="124">
       <c r="A124" t="s">
         <v>650</v>
       </c>
@@ -16251,7 +16251,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="127" hidden="1">
+    <row r="127">
       <c r="A127" t="s">
         <v>666</v>
       </c>
@@ -16277,7 +16277,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="128" hidden="1">
+    <row r="128">
       <c r="A128" t="s">
         <v>672</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="133" hidden="1">
+    <row r="133">
       <c r="A133" t="s">
         <v>698</v>
       </c>
@@ -16444,7 +16444,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="135" hidden="1">
+    <row r="135">
       <c r="A135" t="s">
         <v>709</v>
       </c>
@@ -16470,7 +16470,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="136" hidden="1">
+    <row r="136">
       <c r="A136" t="s">
         <v>715</v>
       </c>
@@ -16496,7 +16496,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="137" hidden="1">
+    <row r="137">
       <c r="A137" t="s">
         <v>721</v>
       </c>
@@ -16568,7 +16568,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="140" hidden="1">
+    <row r="140">
       <c r="A140" t="s">
         <v>737</v>
       </c>
@@ -16594,7 +16594,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="141" hidden="1">
+    <row r="141">
       <c r="A141" t="s">
         <v>743</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="143" hidden="1">
+    <row r="143">
       <c r="A143" t="s">
         <v>754</v>
       </c>
@@ -16669,7 +16669,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="144" hidden="1">
+    <row r="144">
       <c r="A144" t="s">
         <v>760</v>
       </c>
@@ -16767,7 +16767,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="148" hidden="1">
+    <row r="148">
       <c r="A148" t="s">
         <v>782</v>
       </c>
@@ -16862,7 +16862,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="152" hidden="1">
+    <row r="152">
       <c r="A152" t="s">
         <v>803</v>
       </c>
@@ -16934,7 +16934,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="155" hidden="1">
+    <row r="155">
       <c r="A155" t="s">
         <v>819</v>
       </c>
@@ -16983,7 +16983,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="157" hidden="1">
+    <row r="157">
       <c r="A157" t="s">
         <v>830</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="158" hidden="1">
+    <row r="158">
       <c r="A158" t="s">
         <v>836</v>
       </c>
@@ -17035,7 +17035,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="159" hidden="1">
+    <row r="159">
       <c r="A159" t="s">
         <v>842</v>
       </c>
@@ -17271,7 +17271,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="169" hidden="1">
+    <row r="169">
       <c r="A169" t="s">
         <v>894</v>
       </c>
@@ -17297,7 +17297,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="170" hidden="1">
+    <row r="170">
       <c r="A170" t="s">
         <v>900</v>
       </c>
@@ -17346,7 +17346,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="172" hidden="1">
+    <row r="172">
       <c r="A172" t="s">
         <v>911</v>
       </c>
@@ -17487,7 +17487,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="178" hidden="1">
+    <row r="178">
       <c r="A178" t="s">
         <v>942</v>
       </c>
@@ -17536,7 +17536,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="180" hidden="1">
+    <row r="180">
       <c r="A180" t="s">
         <v>953</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="182" hidden="1">
+    <row r="182">
       <c r="A182" t="s">
         <v>964</v>
       </c>
@@ -17680,7 +17680,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="186" hidden="1">
+    <row r="186">
       <c r="A186" t="s">
         <v>985</v>
       </c>
@@ -17729,7 +17729,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="188" hidden="1">
+    <row r="188">
       <c r="A188" t="s">
         <v>996</v>
       </c>
@@ -17801,7 +17801,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="191" hidden="1">
+    <row r="191">
       <c r="A191" t="s">
         <v>1012</v>
       </c>
@@ -17850,7 +17850,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="193" hidden="1">
+    <row r="193">
       <c r="A193" t="s">
         <v>1023</v>
       </c>
@@ -17922,7 +17922,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="196" hidden="1">
+    <row r="196">
       <c r="A196" t="s">
         <v>1039</v>
       </c>
@@ -17951,7 +17951,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="197" hidden="1">
+    <row r="197">
       <c r="A197" t="s">
         <v>1046</v>
       </c>
@@ -17977,7 +17977,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="198" hidden="1">
+    <row r="198">
       <c r="A198" t="s">
         <v>1052</v>
       </c>
@@ -18072,7 +18072,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="202" hidden="1">
+    <row r="202">
       <c r="A202" t="s">
         <v>1073</v>
       </c>
@@ -18098,7 +18098,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="203" hidden="1">
+    <row r="203">
       <c r="A203" t="s">
         <v>1079</v>
       </c>
@@ -18124,7 +18124,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="204" hidden="1">
+    <row r="204">
       <c r="A204" t="s">
         <v>1085</v>
       </c>
@@ -18150,7 +18150,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="205" hidden="1">
+    <row r="205">
       <c r="A205" t="s">
         <v>1091</v>
       </c>
@@ -18222,7 +18222,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="208" hidden="1">
+    <row r="208">
       <c r="A208" t="s">
         <v>1107</v>
       </c>
@@ -18271,7 +18271,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="210" hidden="1">
+    <row r="210">
       <c r="A210" t="s">
         <v>1118</v>
       </c>
@@ -18366,7 +18366,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="214" hidden="1">
+    <row r="214">
       <c r="A214" t="s">
         <v>1139</v>
       </c>
@@ -18461,7 +18461,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="218" hidden="1">
+    <row r="218">
       <c r="A218" t="s">
         <v>1160</v>
       </c>
@@ -18510,7 +18510,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="220" hidden="1">
+    <row r="220">
       <c r="A220" t="s">
         <v>1171</v>
       </c>
@@ -18536,7 +18536,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="221" hidden="1">
+    <row r="221">
       <c r="A221" t="s">
         <v>1177</v>
       </c>
@@ -18585,7 +18585,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="223" hidden="1">
+    <row r="223">
       <c r="A223" t="s">
         <v>1188</v>
       </c>
@@ -18634,7 +18634,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="225" hidden="1">
+    <row r="225">
       <c r="A225" t="s">
         <v>1199</v>
       </c>
@@ -18775,7 +18775,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="231" hidden="1">
+    <row r="231">
       <c r="A231" t="s">
         <v>1230</v>
       </c>
@@ -18824,7 +18824,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="233" hidden="1">
+    <row r="233">
       <c r="A233" t="s">
         <v>1241</v>
       </c>
@@ -18896,7 +18896,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="236" hidden="1">
+    <row r="236">
       <c r="A236" t="s">
         <v>1257</v>
       </c>
@@ -19060,7 +19060,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="243" hidden="1">
+    <row r="243">
       <c r="A243" t="s">
         <v>1293</v>
       </c>
@@ -19109,7 +19109,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="245" hidden="1">
+    <row r="245">
       <c r="A245" t="s">
         <v>1304</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="247" hidden="1">
+    <row r="247">
       <c r="A247" t="s">
         <v>1315</v>
       </c>
@@ -19184,7 +19184,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="248" hidden="1">
+    <row r="248">
       <c r="A248" t="s">
         <v>1321</v>
       </c>
@@ -19233,7 +19233,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="250" hidden="1">
+    <row r="250">
       <c r="A250" t="s">
         <v>1332</v>
       </c>
@@ -19282,7 +19282,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="252" hidden="1">
+    <row r="252">
       <c r="A252" t="s">
         <v>1343</v>
       </c>
@@ -19331,7 +19331,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="254" hidden="1">
+    <row r="254">
       <c r="A254" t="s">
         <v>1354</v>
       </c>
@@ -19357,7 +19357,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="255" hidden="1">
+    <row r="255">
       <c r="A255" t="s">
         <v>1360</v>
       </c>
@@ -19383,7 +19383,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="256" hidden="1">
+    <row r="256">
       <c r="A256" t="s">
         <v>1366</v>
       </c>
@@ -19432,7 +19432,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="258" hidden="1">
+    <row r="258">
       <c r="A258" t="s">
         <v>1377</v>
       </c>
@@ -19504,7 +19504,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="261" hidden="1">
+    <row r="261">
       <c r="A261" t="s">
         <v>1393</v>
       </c>
@@ -19530,7 +19530,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="262" hidden="1">
+    <row r="262">
       <c r="A262" t="s">
         <v>1399</v>
       </c>
@@ -19556,7 +19556,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="263" hidden="1">
+    <row r="263">
       <c r="A263" t="s">
         <v>1405</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="271" hidden="1">
+    <row r="271">
       <c r="A271" t="s">
         <v>1446</v>
       </c>
@@ -19815,7 +19815,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="274" hidden="1">
+    <row r="274">
       <c r="A274" t="s">
         <v>1462</v>
       </c>
@@ -19841,7 +19841,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="275" hidden="1">
+    <row r="275">
       <c r="A275" t="s">
         <v>1468</v>
       </c>
@@ -19867,7 +19867,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="276" hidden="1">
+    <row r="276">
       <c r="A276" t="s">
         <v>1473</v>
       </c>
@@ -19893,7 +19893,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="277" hidden="1">
+    <row r="277">
       <c r="A277" t="s">
         <v>1479</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="279" hidden="1">
+    <row r="279">
       <c r="A279" t="s">
         <v>1490</v>
       </c>
@@ -19991,7 +19991,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="281" hidden="1">
+    <row r="281">
       <c r="A281" t="s">
         <v>1501</v>
       </c>
@@ -20017,7 +20017,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="282" hidden="1">
+    <row r="282">
       <c r="A282" t="s">
         <v>1507</v>
       </c>
@@ -20043,7 +20043,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="283" hidden="1">
+    <row r="283">
       <c r="A283" t="s">
         <v>1513</v>
       </c>
@@ -20069,7 +20069,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="284" hidden="1">
+    <row r="284">
       <c r="A284" t="s">
         <v>1519</v>
       </c>
@@ -20118,7 +20118,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="286" hidden="1">
+    <row r="286">
       <c r="A286" t="s">
         <v>1530</v>
       </c>
@@ -20167,7 +20167,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="288" hidden="1">
+    <row r="288">
       <c r="A288" t="s">
         <v>1541</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="289" hidden="1">
+    <row r="289">
       <c r="A289" t="s">
         <v>1547</v>
       </c>
@@ -20219,7 +20219,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="290" hidden="1">
+    <row r="290">
       <c r="A290" t="s">
         <v>1553</v>
       </c>
@@ -20268,7 +20268,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="292" hidden="1">
+    <row r="292">
       <c r="A292" t="s">
         <v>1564</v>
       </c>
@@ -20317,7 +20317,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="294" hidden="1">
+    <row r="294">
       <c r="A294" t="s">
         <v>1575</v>
       </c>
@@ -20343,7 +20343,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="295" hidden="1">
+    <row r="295">
       <c r="A295" t="s">
         <v>1581</v>
       </c>
@@ -20392,7 +20392,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="297" hidden="1">
+    <row r="297">
       <c r="A297" t="s">
         <v>1592</v>
       </c>
@@ -20418,7 +20418,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="298" hidden="1">
+    <row r="298">
       <c r="A298" t="s">
         <v>1598</v>
       </c>
@@ -20444,7 +20444,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="299" hidden="1">
+    <row r="299">
       <c r="A299" t="s">
         <v>1604</v>
       </c>
@@ -20519,7 +20519,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="302" hidden="1">
+    <row r="302">
       <c r="A302" t="s">
         <v>1621</v>
       </c>
@@ -20545,7 +20545,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="303" hidden="1">
+    <row r="303">
       <c r="A303" t="s">
         <v>1627</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>1632</v>
       </c>
     </row>
-    <row r="304" hidden="1">
+    <row r="304">
       <c r="A304" t="s">
         <v>1633</v>
       </c>
@@ -20597,7 +20597,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="305" hidden="1">
+    <row r="305">
       <c r="A305" t="s">
         <v>1639</v>
       </c>
@@ -20646,7 +20646,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="307" hidden="1">
+    <row r="307">
       <c r="A307" t="s">
         <v>1650</v>
       </c>
@@ -20695,7 +20695,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="309" hidden="1">
+    <row r="309">
       <c r="A309" t="s">
         <v>1661</v>
       </c>
@@ -20721,7 +20721,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="310" hidden="1">
+    <row r="310">
       <c r="A310" t="s">
         <v>1667</v>
       </c>
@@ -20747,7 +20747,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="311" hidden="1">
+    <row r="311">
       <c r="A311" t="s">
         <v>1673</v>
       </c>
@@ -20773,7 +20773,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="312" hidden="1">
+    <row r="312">
       <c r="A312" t="s">
         <v>1679</v>
       </c>
@@ -20799,7 +20799,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="313" hidden="1">
+    <row r="313">
       <c r="A313" t="s">
         <v>1685</v>
       </c>
@@ -20825,7 +20825,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="314" hidden="1">
+    <row r="314">
       <c r="A314" t="s">
         <v>1691</v>
       </c>
@@ -20897,7 +20897,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="317" hidden="1">
+    <row r="317">
       <c r="A317" t="s">
         <v>1707</v>
       </c>
@@ -20923,7 +20923,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="318" hidden="1">
+    <row r="318">
       <c r="A318" t="s">
         <v>1713</v>
       </c>
@@ -20949,7 +20949,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="319" hidden="1">
+    <row r="319">
       <c r="A319" t="s">
         <v>1719</v>
       </c>
@@ -20998,7 +20998,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="321" hidden="1">
+    <row r="321">
       <c r="A321" t="s">
         <v>1730</v>
       </c>
@@ -21024,7 +21024,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="322" hidden="1">
+    <row r="322">
       <c r="A322" t="s">
         <v>1736</v>
       </c>
@@ -21073,7 +21073,7 @@
         <v>1746</v>
       </c>
     </row>
-    <row r="324" hidden="1">
+    <row r="324">
       <c r="A324" t="s">
         <v>1747</v>
       </c>
@@ -21099,7 +21099,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="325" hidden="1">
+    <row r="325">
       <c r="A325" t="s">
         <v>1753</v>
       </c>
@@ -21220,7 +21220,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="330" hidden="1">
+    <row r="330">
       <c r="A330" t="s">
         <v>1779</v>
       </c>
@@ -21246,7 +21246,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="331" hidden="1">
+    <row r="331">
       <c r="A331" t="s">
         <v>1785</v>
       </c>
@@ -21272,7 +21272,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="332" hidden="1">
+    <row r="332">
       <c r="A332" t="s">
         <v>1791</v>
       </c>
@@ -21298,7 +21298,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="333" hidden="1">
+    <row r="333">
       <c r="A333" t="s">
         <v>1797</v>
       </c>
@@ -21324,7 +21324,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="334" hidden="1">
+    <row r="334">
       <c r="A334" t="s">
         <v>1803</v>
       </c>
@@ -21373,7 +21373,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="336" hidden="1">
+    <row r="336">
       <c r="A336" t="s">
         <v>1814</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="337" hidden="1">
+    <row r="337">
       <c r="A337" t="s">
         <v>1820</v>
       </c>
@@ -21448,7 +21448,7 @@
         <v>1830</v>
       </c>
     </row>
-    <row r="339" hidden="1">
+    <row r="339">
       <c r="A339" t="s">
         <v>1831</v>
       </c>
@@ -21497,7 +21497,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="341" hidden="1">
+    <row r="341">
       <c r="A341" t="s">
         <v>1842</v>
       </c>
@@ -21523,7 +21523,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="342" hidden="1">
+    <row r="342">
       <c r="A342" t="s">
         <v>1848</v>
       </c>
@@ -21575,7 +21575,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="344" hidden="1">
+    <row r="344">
       <c r="A344" t="s">
         <v>1860</v>
       </c>
@@ -21601,7 +21601,7 @@
         <v>1865</v>
       </c>
     </row>
-    <row r="345" hidden="1">
+    <row r="345">
       <c r="A345" t="s">
         <v>1866</v>
       </c>
@@ -21627,7 +21627,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="346" hidden="1">
+    <row r="346">
       <c r="A346" t="s">
         <v>1872</v>
       </c>
@@ -21653,7 +21653,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="347" hidden="1">
+    <row r="347">
       <c r="A347" t="s">
         <v>1878</v>
       </c>
@@ -21679,7 +21679,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="348" hidden="1">
+    <row r="348">
       <c r="A348" t="s">
         <v>1884</v>
       </c>
@@ -21705,7 +21705,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="349" hidden="1">
+    <row r="349">
       <c r="A349" t="s">
         <v>1890</v>
       </c>
@@ -21754,7 +21754,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="351" hidden="1">
+    <row r="351">
       <c r="A351" t="s">
         <v>1901</v>
       </c>
@@ -21780,7 +21780,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="352" hidden="1">
+    <row r="352">
       <c r="A352" t="s">
         <v>1907</v>
       </c>
@@ -21806,7 +21806,7 @@
         <v>1912</v>
       </c>
     </row>
-    <row r="353" hidden="1">
+    <row r="353">
       <c r="A353" t="s">
         <v>1913</v>
       </c>
@@ -21947,7 +21947,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="359" hidden="1">
+    <row r="359">
       <c r="A359" t="s">
         <v>1942</v>
       </c>
@@ -21973,7 +21973,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="360" hidden="1">
+    <row r="360">
       <c r="A360" t="s">
         <v>1948</v>
       </c>
@@ -22022,7 +22022,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="362" hidden="1">
+    <row r="362">
       <c r="A362" t="s">
         <v>1959</v>
       </c>
@@ -22051,7 +22051,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="363" hidden="1">
+    <row r="363">
       <c r="A363" t="s">
         <v>1966</v>
       </c>
@@ -22123,7 +22123,7 @@
         <v>1981</v>
       </c>
     </row>
-    <row r="366" hidden="1">
+    <row r="366">
       <c r="A366" t="s">
         <v>1982</v>
       </c>
@@ -22149,7 +22149,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="367" hidden="1">
+    <row r="367">
       <c r="A367" t="s">
         <v>1988</v>
       </c>
@@ -22290,7 +22290,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="373" hidden="1">
+    <row r="373">
       <c r="A373" t="s">
         <v>2018</v>
       </c>
@@ -22362,7 +22362,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="376" hidden="1">
+    <row r="376">
       <c r="A376" t="s">
         <v>2034</v>
       </c>
@@ -22388,7 +22388,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="377" hidden="1">
+    <row r="377">
       <c r="A377" t="s">
         <v>2040</v>
       </c>
@@ -22414,7 +22414,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="378" hidden="1">
+    <row r="378">
       <c r="A378" t="s">
         <v>2046</v>
       </c>
@@ -22440,7 +22440,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="379" hidden="1">
+    <row r="379">
       <c r="A379" t="s">
         <v>2052</v>
       </c>
@@ -22512,7 +22512,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="382" hidden="1">
+    <row r="382">
       <c r="A382" t="s">
         <v>2068</v>
       </c>
@@ -22584,7 +22584,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="385" hidden="1">
+    <row r="385">
       <c r="A385" t="s">
         <v>2084</v>
       </c>
@@ -22610,7 +22610,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="386" hidden="1">
+    <row r="386">
       <c r="A386" t="s">
         <v>2090</v>
       </c>
@@ -22682,7 +22682,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="389" hidden="1">
+    <row r="389">
       <c r="A389" t="s">
         <v>2106</v>
       </c>
@@ -22708,7 +22708,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="390" hidden="1">
+    <row r="390">
       <c r="A390" t="s">
         <v>2112</v>
       </c>
@@ -22734,7 +22734,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="391" hidden="1">
+    <row r="391">
       <c r="A391" t="s">
         <v>2118</v>
       </c>
@@ -22760,7 +22760,7 @@
         <v>2123</v>
       </c>
     </row>
-    <row r="392" hidden="1">
+    <row r="392">
       <c r="A392" t="s">
         <v>2124</v>
       </c>
@@ -22786,7 +22786,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="393" hidden="1">
+    <row r="393">
       <c r="A393" t="s">
         <v>2130</v>
       </c>
@@ -22812,7 +22812,7 @@
         <v>2135</v>
       </c>
     </row>
-    <row r="394" hidden="1">
+    <row r="394">
       <c r="A394" t="s">
         <v>2136</v>
       </c>
@@ -22838,7 +22838,7 @@
         <v>2141</v>
       </c>
     </row>
-    <row r="395" hidden="1">
+    <row r="395">
       <c r="A395" t="s">
         <v>2142</v>
       </c>
@@ -22864,7 +22864,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="396" hidden="1">
+    <row r="396">
       <c r="A396" t="s">
         <v>2148</v>
       </c>
@@ -22890,7 +22890,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="397" hidden="1">
+    <row r="397">
       <c r="A397" t="s">
         <v>2154</v>
       </c>
@@ -22962,7 +22962,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="400" hidden="1">
+    <row r="400">
       <c r="A400" t="s">
         <v>2170</v>
       </c>
@@ -22988,7 +22988,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="401" hidden="1">
+    <row r="401">
       <c r="A401" t="s">
         <v>2176</v>
       </c>
@@ -23106,7 +23106,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="406" hidden="1">
+    <row r="406">
       <c r="A406" t="s">
         <v>2202</v>
       </c>
@@ -23132,7 +23132,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="407" hidden="1">
+    <row r="407">
       <c r="A407" t="s">
         <v>2208</v>
       </c>
@@ -23181,7 +23181,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="409" hidden="1">
+    <row r="409">
       <c r="A409" t="s">
         <v>2219</v>
       </c>
@@ -23276,7 +23276,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="413" hidden="1">
+    <row r="413">
       <c r="A413" t="s">
         <v>2240</v>
       </c>
@@ -23371,7 +23371,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="417" hidden="1">
+    <row r="417">
       <c r="A417" t="s">
         <v>2261</v>
       </c>
@@ -23397,7 +23397,7 @@
         <v>2266</v>
       </c>
     </row>
-    <row r="418" hidden="1">
+    <row r="418">
       <c r="A418" t="s">
         <v>2267</v>
       </c>
@@ -23469,7 +23469,7 @@
         <v>2282</v>
       </c>
     </row>
-    <row r="421" hidden="1">
+    <row r="421">
       <c r="A421" t="s">
         <v>2283</v>
       </c>
@@ -23495,7 +23495,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="422" hidden="1">
+    <row r="422">
       <c r="A422" t="s">
         <v>2289</v>
       </c>
@@ -23544,7 +23544,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="424" hidden="1">
+    <row r="424">
       <c r="A424" t="s">
         <v>2300</v>
       </c>
@@ -23593,7 +23593,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="426" hidden="1">
+    <row r="426">
       <c r="A426" t="s">
         <v>2311</v>
       </c>
@@ -23642,7 +23642,7 @@
         <v>2321</v>
       </c>
     </row>
-    <row r="428" hidden="1">
+    <row r="428">
       <c r="A428" t="s">
         <v>2322</v>
       </c>
@@ -23714,7 +23714,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="431" hidden="1">
+    <row r="431">
       <c r="A431" t="s">
         <v>2338</v>
       </c>
@@ -23740,7 +23740,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="432" hidden="1">
+    <row r="432">
       <c r="A432" t="s">
         <v>2344</v>
       </c>
@@ -23766,7 +23766,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="433" hidden="1">
+    <row r="433">
       <c r="A433" t="s">
         <v>2350</v>
       </c>
@@ -23792,7 +23792,7 @@
         <v>2355</v>
       </c>
     </row>
-    <row r="434" hidden="1">
+    <row r="434">
       <c r="A434" t="s">
         <v>2356</v>
       </c>
@@ -23818,7 +23818,7 @@
         <v>2361</v>
       </c>
     </row>
-    <row r="435" hidden="1">
+    <row r="435">
       <c r="A435" t="s">
         <v>2362</v>
       </c>
@@ -23844,7 +23844,7 @@
         <v>2367</v>
       </c>
     </row>
-    <row r="436" hidden="1">
+    <row r="436">
       <c r="A436" t="s">
         <v>2368</v>
       </c>
@@ -23893,7 +23893,7 @@
         <v>2378</v>
       </c>
     </row>
-    <row r="438" hidden="1">
+    <row r="438">
       <c r="A438" t="s">
         <v>2379</v>
       </c>
@@ -23919,7 +23919,7 @@
         <v>2384</v>
       </c>
     </row>
-    <row r="439" hidden="1">
+    <row r="439">
       <c r="A439" t="s">
         <v>2385</v>
       </c>
@@ -23945,7 +23945,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="440" hidden="1">
+    <row r="440">
       <c r="A440" t="s">
         <v>2391</v>
       </c>
@@ -23971,7 +23971,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="441" hidden="1">
+    <row r="441">
       <c r="A441" t="s">
         <v>2397</v>
       </c>
@@ -23997,7 +23997,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="442" hidden="1">
+    <row r="442">
       <c r="A442" t="s">
         <v>2403</v>
       </c>
@@ -24023,7 +24023,7 @@
         <v>2408</v>
       </c>
     </row>
-    <row r="443" hidden="1">
+    <row r="443">
       <c r="A443" t="s">
         <v>2409</v>
       </c>
@@ -24095,7 +24095,7 @@
         <v>2424</v>
       </c>
     </row>
-    <row r="446" hidden="1">
+    <row r="446">
       <c r="A446" t="s">
         <v>2425</v>
       </c>
@@ -24144,7 +24144,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="448" hidden="1">
+    <row r="448">
       <c r="A448" t="s">
         <v>2436</v>
       </c>
@@ -24193,7 +24193,7 @@
         <v>2446</v>
       </c>
     </row>
-    <row r="450" hidden="1">
+    <row r="450">
       <c r="A450" t="s">
         <v>2447</v>
       </c>
@@ -24219,7 +24219,7 @@
         <v>2452</v>
       </c>
     </row>
-    <row r="451" hidden="1">
+    <row r="451">
       <c r="A451" t="s">
         <v>2453</v>
       </c>
@@ -24245,7 +24245,7 @@
         <v>2458</v>
       </c>
     </row>
-    <row r="452" hidden="1">
+    <row r="452">
       <c r="A452" t="s">
         <v>2459</v>
       </c>
@@ -24271,7 +24271,7 @@
         <v>2463</v>
       </c>
     </row>
-    <row r="453" hidden="1">
+    <row r="453">
       <c r="A453" t="s">
         <v>2464</v>
       </c>
@@ -24320,7 +24320,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="455" hidden="1">
+    <row r="455">
       <c r="A455" t="s">
         <v>2475</v>
       </c>
@@ -24346,7 +24346,7 @@
         <v>2480</v>
       </c>
     </row>
-    <row r="456" hidden="1">
+    <row r="456">
       <c r="A456" t="s">
         <v>2481</v>
       </c>
@@ -24418,7 +24418,7 @@
         <v>2496</v>
       </c>
     </row>
-    <row r="459" hidden="1">
+    <row r="459">
       <c r="A459" t="s">
         <v>2497</v>
       </c>
@@ -24444,7 +24444,7 @@
         <v>2502</v>
       </c>
     </row>
-    <row r="460" hidden="1">
+    <row r="460">
       <c r="A460" t="s">
         <v>2503</v>
       </c>
@@ -24470,7 +24470,7 @@
         <v>2508</v>
       </c>
     </row>
-    <row r="461" hidden="1">
+    <row r="461">
       <c r="A461" t="s">
         <v>2509</v>
       </c>
@@ -24496,7 +24496,7 @@
         <v>2514</v>
       </c>
     </row>
-    <row r="462" hidden="1">
+    <row r="462">
       <c r="A462" t="s">
         <v>2515</v>
       </c>
@@ -24522,7 +24522,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="463" hidden="1">
+    <row r="463">
       <c r="A463" t="s">
         <v>2521</v>
       </c>
@@ -24548,7 +24548,7 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="464" hidden="1">
+    <row r="464">
       <c r="A464" t="s">
         <v>2527</v>
       </c>
@@ -24643,7 +24643,7 @@
         <v>2547</v>
       </c>
     </row>
-    <row r="468" hidden="1">
+    <row r="468">
       <c r="A468" t="s">
         <v>2548</v>
       </c>
@@ -24669,7 +24669,7 @@
         <v>2553</v>
       </c>
     </row>
-    <row r="469" hidden="1">
+    <row r="469">
       <c r="A469" t="s">
         <v>2554</v>
       </c>
@@ -24695,7 +24695,7 @@
         <v>2559</v>
       </c>
     </row>
-    <row r="470" hidden="1">
+    <row r="470">
       <c r="A470" t="s">
         <v>2560</v>
       </c>
@@ -24721,7 +24721,7 @@
         <v>2565</v>
       </c>
     </row>
-    <row r="471" hidden="1">
+    <row r="471">
       <c r="A471" t="s">
         <v>2566</v>
       </c>
@@ -24793,7 +24793,7 @@
         <v>2581</v>
       </c>
     </row>
-    <row r="474" hidden="1">
+    <row r="474">
       <c r="A474" t="s">
         <v>2582</v>
       </c>
@@ -24842,7 +24842,7 @@
         <v>2592</v>
       </c>
     </row>
-    <row r="476" hidden="1">
+    <row r="476">
       <c r="A476" t="s">
         <v>2593</v>
       </c>
@@ -24868,7 +24868,7 @@
         <v>2598</v>
       </c>
     </row>
-    <row r="477" hidden="1">
+    <row r="477">
       <c r="A477" t="s">
         <v>2599</v>
       </c>
@@ -24894,7 +24894,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="478" hidden="1">
+    <row r="478">
       <c r="A478" t="s">
         <v>2605</v>
       </c>
@@ -24920,7 +24920,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="479" hidden="1">
+    <row r="479">
       <c r="A479" t="s">
         <v>2611</v>
       </c>
@@ -24969,7 +24969,7 @@
         <v>2621</v>
       </c>
     </row>
-    <row r="481" hidden="1">
+    <row r="481">
       <c r="A481" t="s">
         <v>2622</v>
       </c>
@@ -24995,7 +24995,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="482" hidden="1">
+    <row r="482">
       <c r="A482" t="s">
         <v>2628</v>
       </c>
@@ -25044,7 +25044,7 @@
         <v>2637</v>
       </c>
     </row>
-    <row r="484" hidden="1">
+    <row r="484">
       <c r="A484" t="s">
         <v>2638</v>
       </c>
@@ -25116,7 +25116,7 @@
         <v>2652</v>
       </c>
     </row>
-    <row r="487" hidden="1">
+    <row r="487">
       <c r="A487" t="s">
         <v>2653</v>
       </c>
@@ -25165,7 +25165,7 @@
         <v>2663</v>
       </c>
     </row>
-    <row r="489" hidden="1">
+    <row r="489">
       <c r="A489" t="s">
         <v>2664</v>
       </c>
@@ -25191,7 +25191,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="490" hidden="1">
+    <row r="490">
       <c r="A490" t="s">
         <v>2670</v>
       </c>
@@ -25217,7 +25217,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="491" hidden="1">
+    <row r="491">
       <c r="A491" t="s">
         <v>2675</v>
       </c>
@@ -25266,7 +25266,7 @@
         <v>2685</v>
       </c>
     </row>
-    <row r="493" hidden="1">
+    <row r="493">
       <c r="A493" t="s">
         <v>2686</v>
       </c>
@@ -25292,7 +25292,7 @@
         <v>2691</v>
       </c>
     </row>
-    <row r="494" hidden="1">
+    <row r="494">
       <c r="A494" t="s">
         <v>2692</v>
       </c>
@@ -25364,7 +25364,7 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="497" hidden="1">
+    <row r="497">
       <c r="A497" t="s">
         <v>2708</v>
       </c>
@@ -25413,7 +25413,7 @@
         <v>2718</v>
       </c>
     </row>
-    <row r="499" hidden="1">
+    <row r="499">
       <c r="A499" t="s">
         <v>2719</v>
       </c>
@@ -25439,7 +25439,7 @@
         <v>2724</v>
       </c>
     </row>
-    <row r="500" hidden="1">
+    <row r="500">
       <c r="A500" t="s">
         <v>2725</v>
       </c>
@@ -25465,7 +25465,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="501" hidden="1">
+    <row r="501">
       <c r="A501" t="s">
         <v>2731</v>
       </c>
@@ -25560,7 +25560,7 @@
         <v>2751</v>
       </c>
     </row>
-    <row r="505" hidden="1">
+    <row r="505">
       <c r="A505" t="s">
         <v>2752</v>
       </c>
@@ -25586,7 +25586,7 @@
         <v>2757</v>
       </c>
     </row>
-    <row r="506" hidden="1">
+    <row r="506">
       <c r="A506" t="s">
         <v>2758</v>
       </c>
@@ -25612,7 +25612,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="507" hidden="1">
+    <row r="507">
       <c r="A507" t="s">
         <v>2764</v>
       </c>
@@ -25710,7 +25710,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="511" hidden="1">
+    <row r="511">
       <c r="A511" t="s">
         <v>2785</v>
       </c>
@@ -25759,7 +25759,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="513" hidden="1">
+    <row r="513">
       <c r="A513" t="s">
         <v>2796</v>
       </c>
@@ -25808,7 +25808,7 @@
         <v>2806</v>
       </c>
     </row>
-    <row r="515" hidden="1">
+    <row r="515">
       <c r="A515" t="s">
         <v>2807</v>
       </c>
@@ -25857,7 +25857,7 @@
         <v>2817</v>
       </c>
     </row>
-    <row r="517" hidden="1">
+    <row r="517">
       <c r="A517" t="s">
         <v>2818</v>
       </c>
@@ -25906,7 +25906,7 @@
         <v>2828</v>
       </c>
     </row>
-    <row r="519" hidden="1">
+    <row r="519">
       <c r="A519" t="s">
         <v>2829</v>
       </c>
@@ -26001,7 +26001,7 @@
         <v>2849</v>
       </c>
     </row>
-    <row r="523" hidden="1">
+    <row r="523">
       <c r="A523" t="s">
         <v>2850</v>
       </c>
@@ -26027,7 +26027,7 @@
         <v>2855</v>
       </c>
     </row>
-    <row r="524" hidden="1">
+    <row r="524">
       <c r="A524" t="s">
         <v>2856</v>
       </c>
@@ -26053,7 +26053,7 @@
         <v>2861</v>
       </c>
     </row>
-    <row r="525" hidden="1">
+    <row r="525">
       <c r="A525" t="s">
         <v>2862</v>
       </c>
@@ -26102,7 +26102,7 @@
         <v>2872</v>
       </c>
     </row>
-    <row r="527" hidden="1">
+    <row r="527">
       <c r="A527" t="s">
         <v>2873</v>
       </c>
@@ -26151,7 +26151,7 @@
         <v>2883</v>
       </c>
     </row>
-    <row r="529" hidden="1">
+    <row r="529">
       <c r="A529" t="s">
         <v>2884</v>
       </c>
@@ -26177,7 +26177,7 @@
         <v>2889</v>
       </c>
     </row>
-    <row r="530" hidden="1">
+    <row r="530">
       <c r="A530" t="s">
         <v>2890</v>
       </c>
@@ -26249,7 +26249,7 @@
         <v>2905</v>
       </c>
     </row>
-    <row r="533" hidden="1">
+    <row r="533">
       <c r="A533" t="s">
         <v>2906</v>
       </c>
@@ -26275,7 +26275,7 @@
         <v>2911</v>
       </c>
     </row>
-    <row r="534" hidden="1">
+    <row r="534">
       <c r="A534" t="s">
         <v>2912</v>
       </c>
@@ -26301,7 +26301,7 @@
         <v>2917</v>
       </c>
     </row>
-    <row r="535" hidden="1">
+    <row r="535">
       <c r="A535" t="s">
         <v>2918</v>
       </c>
@@ -26327,7 +26327,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="536" hidden="1">
+    <row r="536">
       <c r="A536" t="s">
         <v>2924</v>
       </c>
@@ -26353,7 +26353,7 @@
         <v>2929</v>
       </c>
     </row>
-    <row r="537" hidden="1">
+    <row r="537">
       <c r="A537" t="s">
         <v>2930</v>
       </c>
@@ -26379,7 +26379,7 @@
         <v>2935</v>
       </c>
     </row>
-    <row r="538" hidden="1">
+    <row r="538">
       <c r="A538" t="s">
         <v>2936</v>
       </c>
@@ -26428,7 +26428,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="540" hidden="1">
+    <row r="540">
       <c r="A540" t="s">
         <v>2947</v>
       </c>
@@ -26477,7 +26477,7 @@
         <v>2957</v>
       </c>
     </row>
-    <row r="542" hidden="1">
+    <row r="542">
       <c r="A542" t="s">
         <v>2958</v>
       </c>
@@ -26503,7 +26503,7 @@
         <v>2962</v>
       </c>
     </row>
-    <row r="543" hidden="1">
+    <row r="543">
       <c r="A543" t="s">
         <v>2963</v>
       </c>
@@ -26529,7 +26529,7 @@
         <v>2968</v>
       </c>
     </row>
-    <row r="544" hidden="1">
+    <row r="544">
       <c r="A544" t="s">
         <v>2969</v>
       </c>
@@ -26578,7 +26578,7 @@
         <v>2979</v>
       </c>
     </row>
-    <row r="546" hidden="1">
+    <row r="546">
       <c r="A546" t="s">
         <v>2980</v>
       </c>
@@ -26604,7 +26604,7 @@
         <v>2985</v>
       </c>
     </row>
-    <row r="547" hidden="1">
+    <row r="547">
       <c r="A547" t="s">
         <v>2986</v>
       </c>
@@ -26630,7 +26630,7 @@
         <v>2991</v>
       </c>
     </row>
-    <row r="548" hidden="1">
+    <row r="548">
       <c r="A548" t="s">
         <v>2992</v>
       </c>
@@ -26656,7 +26656,7 @@
         <v>2997</v>
       </c>
     </row>
-    <row r="549" hidden="1">
+    <row r="549">
       <c r="A549" t="s">
         <v>2998</v>
       </c>
@@ -26705,7 +26705,7 @@
         <v>3008</v>
       </c>
     </row>
-    <row r="551" hidden="1">
+    <row r="551">
       <c r="A551" t="s">
         <v>3009</v>
       </c>
@@ -26754,7 +26754,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="553" hidden="1">
+    <row r="553">
       <c r="A553" t="s">
         <v>3020</v>
       </c>
@@ -26826,7 +26826,7 @@
         <v>3035</v>
       </c>
     </row>
-    <row r="556" hidden="1">
+    <row r="556">
       <c r="A556" t="s">
         <v>3036</v>
       </c>
@@ -26875,7 +26875,7 @@
         <v>3046</v>
       </c>
     </row>
-    <row r="558" hidden="1">
+    <row r="558">
       <c r="A558" t="s">
         <v>3047</v>
       </c>
@@ -26901,7 +26901,7 @@
         <v>3052</v>
       </c>
     </row>
-    <row r="559" hidden="1">
+    <row r="559">
       <c r="A559" t="s">
         <v>3053</v>
       </c>
@@ -26950,7 +26950,7 @@
         <v>3063</v>
       </c>
     </row>
-    <row r="561" hidden="1">
+    <row r="561">
       <c r="A561" t="s">
         <v>3064</v>
       </c>
@@ -26976,7 +26976,7 @@
         <v>3069</v>
       </c>
     </row>
-    <row r="562" hidden="1">
+    <row r="562">
       <c r="A562" t="s">
         <v>3070</v>
       </c>
@@ -27002,7 +27002,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="563" hidden="1">
+    <row r="563">
       <c r="A563" t="s">
         <v>3076</v>
       </c>
@@ -27051,7 +27051,7 @@
         <v>3086</v>
       </c>
     </row>
-    <row r="565" hidden="1">
+    <row r="565">
       <c r="A565" t="s">
         <v>3087</v>
       </c>
@@ -27077,7 +27077,7 @@
         <v>3092</v>
       </c>
     </row>
-    <row r="566" hidden="1">
+    <row r="566">
       <c r="A566" t="s">
         <v>3093</v>
       </c>
@@ -27129,7 +27129,7 @@
         <v>3104</v>
       </c>
     </row>
-    <row r="568" hidden="1">
+    <row r="568">
       <c r="A568" t="s">
         <v>3105</v>
       </c>
@@ -27178,7 +27178,7 @@
         <v>3115</v>
       </c>
     </row>
-    <row r="570" hidden="1">
+    <row r="570">
       <c r="A570" t="s">
         <v>3116</v>
       </c>
@@ -27204,7 +27204,7 @@
         <v>3121</v>
       </c>
     </row>
-    <row r="571" hidden="1">
+    <row r="571">
       <c r="A571" t="s">
         <v>3122</v>
       </c>
@@ -27230,7 +27230,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="572" hidden="1">
+    <row r="572">
       <c r="A572" t="s">
         <v>3128</v>
       </c>
@@ -27282,7 +27282,7 @@
         <v>3138</v>
       </c>
     </row>
-    <row r="574" hidden="1">
+    <row r="574">
       <c r="A574" t="s">
         <v>3139</v>
       </c>
@@ -27308,7 +27308,7 @@
         <v>3144</v>
       </c>
     </row>
-    <row r="575" hidden="1">
+    <row r="575">
       <c r="A575" t="s">
         <v>3145</v>
       </c>
@@ -27357,7 +27357,7 @@
         <v>3155</v>
       </c>
     </row>
-    <row r="577" hidden="1">
+    <row r="577">
       <c r="A577" t="s">
         <v>3156</v>
       </c>
@@ -27383,7 +27383,7 @@
         <v>3161</v>
       </c>
     </row>
-    <row r="578" hidden="1">
+    <row r="578">
       <c r="A578" t="s">
         <v>3162</v>
       </c>
@@ -27409,7 +27409,7 @@
         <v>3167</v>
       </c>
     </row>
-    <row r="579" hidden="1">
+    <row r="579">
       <c r="A579" t="s">
         <v>3168</v>
       </c>
@@ -27435,7 +27435,7 @@
         <v>3173</v>
       </c>
     </row>
-    <row r="580" hidden="1">
+    <row r="580">
       <c r="A580" t="s">
         <v>3174</v>
       </c>
@@ -27461,7 +27461,7 @@
         <v>3179</v>
       </c>
     </row>
-    <row r="581" hidden="1">
+    <row r="581">
       <c r="A581" t="s">
         <v>3180</v>
       </c>
@@ -27533,7 +27533,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="584" hidden="1">
+    <row r="584">
       <c r="A584" t="s">
         <v>3196</v>
       </c>
@@ -27559,7 +27559,7 @@
         <v>3201</v>
       </c>
     </row>
-    <row r="585" hidden="1">
+    <row r="585">
       <c r="A585" t="s">
         <v>3202</v>
       </c>
@@ -27815,7 +27815,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="596" hidden="1">
+    <row r="596">
       <c r="A596" t="s">
         <v>3258</v>
       </c>
@@ -27956,7 +27956,7 @@
         <v>3288</v>
       </c>
     </row>
-    <row r="602" hidden="1">
+    <row r="602">
       <c r="A602" t="s">
         <v>3289</v>
       </c>
@@ -28074,7 +28074,7 @@
         <v>3314</v>
       </c>
     </row>
-    <row r="607" hidden="1">
+    <row r="607">
       <c r="A607" t="s">
         <v>3315</v>
       </c>
@@ -28100,7 +28100,7 @@
         <v>3320</v>
       </c>
     </row>
-    <row r="608" hidden="1">
+    <row r="608">
       <c r="A608" t="s">
         <v>3321</v>
       </c>
@@ -28126,7 +28126,7 @@
         <v>3326</v>
       </c>
     </row>
-    <row r="609" hidden="1">
+    <row r="609">
       <c r="A609" t="s">
         <v>3327</v>
       </c>
@@ -28152,7 +28152,7 @@
         <v>3332</v>
       </c>
     </row>
-    <row r="610" hidden="1">
+    <row r="610">
       <c r="A610" t="s">
         <v>3333</v>
       </c>
@@ -28178,7 +28178,7 @@
         <v>3338</v>
       </c>
     </row>
-    <row r="611" hidden="1">
+    <row r="611">
       <c r="A611" t="s">
         <v>3339</v>
       </c>
@@ -28204,7 +28204,7 @@
         <v>3344</v>
       </c>
     </row>
-    <row r="612" hidden="1">
+    <row r="612">
       <c r="A612" t="s">
         <v>3345</v>
       </c>
@@ -28230,7 +28230,7 @@
         <v>3350</v>
       </c>
     </row>
-    <row r="613" hidden="1">
+    <row r="613">
       <c r="A613" t="s">
         <v>3351</v>
       </c>
@@ -28302,7 +28302,7 @@
         <v>3366</v>
       </c>
     </row>
-    <row r="616" hidden="1">
+    <row r="616">
       <c r="A616" t="s">
         <v>3367</v>
       </c>
@@ -28374,7 +28374,7 @@
         <v>3382</v>
       </c>
     </row>
-    <row r="619" hidden="1">
+    <row r="619">
       <c r="A619" t="s">
         <v>3383</v>
       </c>
@@ -28400,7 +28400,7 @@
         <v>3388</v>
       </c>
     </row>
-    <row r="620" hidden="1">
+    <row r="620">
       <c r="A620" t="s">
         <v>3389</v>
       </c>
@@ -28426,7 +28426,7 @@
         <v>3394</v>
       </c>
     </row>
-    <row r="621" hidden="1">
+    <row r="621">
       <c r="A621" t="s">
         <v>3395</v>
       </c>
@@ -28452,7 +28452,7 @@
         <v>3400</v>
       </c>
     </row>
-    <row r="622" hidden="1">
+    <row r="622">
       <c r="A622" t="s">
         <v>3401</v>
       </c>
@@ -28501,7 +28501,7 @@
         <v>3411</v>
       </c>
     </row>
-    <row r="624" hidden="1">
+    <row r="624">
       <c r="A624" t="s">
         <v>3412</v>
       </c>
@@ -28573,7 +28573,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="627" hidden="1">
+    <row r="627">
       <c r="A627" t="s">
         <v>3428</v>
       </c>
@@ -28599,7 +28599,7 @@
         <v>3433</v>
       </c>
     </row>
-    <row r="628" hidden="1">
+    <row r="628">
       <c r="A628" t="s">
         <v>3434</v>
       </c>
@@ -28625,7 +28625,7 @@
         <v>3439</v>
       </c>
     </row>
-    <row r="629" hidden="1">
+    <row r="629">
       <c r="A629" t="s">
         <v>3440</v>
       </c>
@@ -28674,7 +28674,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="631" hidden="1">
+    <row r="631">
       <c r="A631" t="s">
         <v>3451</v>
       </c>
@@ -28700,7 +28700,7 @@
         <v>3456</v>
       </c>
     </row>
-    <row r="632" hidden="1">
+    <row r="632">
       <c r="A632" t="s">
         <v>3457</v>
       </c>
@@ -28726,7 +28726,7 @@
         <v>3462</v>
       </c>
     </row>
-    <row r="633" hidden="1">
+    <row r="633">
       <c r="A633" t="s">
         <v>3463</v>
       </c>
@@ -28752,7 +28752,7 @@
         <v>3468</v>
       </c>
     </row>
-    <row r="634" hidden="1">
+    <row r="634">
       <c r="A634" t="s">
         <v>3469</v>
       </c>
@@ -28778,7 +28778,7 @@
         <v>3474</v>
       </c>
     </row>
-    <row r="635" hidden="1">
+    <row r="635">
       <c r="A635" t="s">
         <v>3475</v>
       </c>
@@ -28804,7 +28804,7 @@
         <v>3480</v>
       </c>
     </row>
-    <row r="636" hidden="1">
+    <row r="636">
       <c r="A636" t="s">
         <v>3481</v>
       </c>
@@ -28830,7 +28830,7 @@
         <v>3486</v>
       </c>
     </row>
-    <row r="637" hidden="1">
+    <row r="637">
       <c r="A637" t="s">
         <v>3487</v>
       </c>
@@ -28856,7 +28856,7 @@
         <v>3492</v>
       </c>
     </row>
-    <row r="638" hidden="1">
+    <row r="638">
       <c r="A638" t="s">
         <v>3493</v>
       </c>
@@ -28882,7 +28882,7 @@
         <v>3498</v>
       </c>
     </row>
-    <row r="639" hidden="1">
+    <row r="639">
       <c r="A639" t="s">
         <v>3499</v>
       </c>
@@ -28908,7 +28908,7 @@
         <v>3504</v>
       </c>
     </row>
-    <row r="640" hidden="1">
+    <row r="640">
       <c r="A640" t="s">
         <v>3505</v>
       </c>
@@ -28934,7 +28934,7 @@
         <v>3510</v>
       </c>
     </row>
-    <row r="641" hidden="1">
+    <row r="641">
       <c r="A641" t="s">
         <v>3511</v>
       </c>
@@ -28960,7 +28960,7 @@
         <v>3516</v>
       </c>
     </row>
-    <row r="642" hidden="1">
+    <row r="642">
       <c r="A642" t="s">
         <v>3517</v>
       </c>
@@ -29032,7 +29032,7 @@
         <v>3532</v>
       </c>
     </row>
-    <row r="645" hidden="1">
+    <row r="645">
       <c r="A645" t="s">
         <v>3533</v>
       </c>
@@ -29058,7 +29058,7 @@
         <v>3538</v>
       </c>
     </row>
-    <row r="646" hidden="1">
+    <row r="646">
       <c r="A646" t="s">
         <v>3539</v>
       </c>
@@ -29107,7 +29107,7 @@
         <v>3549</v>
       </c>
     </row>
-    <row r="648" hidden="1">
+    <row r="648">
       <c r="A648" t="s">
         <v>3550</v>
       </c>
@@ -29133,7 +29133,7 @@
         <v>3555</v>
       </c>
     </row>
-    <row r="649" hidden="1">
+    <row r="649">
       <c r="A649" t="s">
         <v>3556</v>
       </c>
@@ -29182,7 +29182,7 @@
         <v>3566</v>
       </c>
     </row>
-    <row r="651" hidden="1">
+    <row r="651">
       <c r="A651" t="s">
         <v>3567</v>
       </c>
@@ -29208,7 +29208,7 @@
         <v>3572</v>
       </c>
     </row>
-    <row r="652" hidden="1">
+    <row r="652">
       <c r="A652" t="s">
         <v>3573</v>
       </c>
@@ -29234,7 +29234,7 @@
         <v>3578</v>
       </c>
     </row>
-    <row r="653" hidden="1">
+    <row r="653">
       <c r="A653" t="s">
         <v>3579</v>
       </c>
@@ -29283,7 +29283,7 @@
         <v>3589</v>
       </c>
     </row>
-    <row r="655" hidden="1">
+    <row r="655">
       <c r="A655" t="s">
         <v>3590</v>
       </c>
@@ -29309,7 +29309,7 @@
         <v>3595</v>
       </c>
     </row>
-    <row r="656" hidden="1">
+    <row r="656">
       <c r="A656" t="s">
         <v>3596</v>
       </c>
@@ -29381,7 +29381,7 @@
         <v>3611</v>
       </c>
     </row>
-    <row r="659" hidden="1">
+    <row r="659">
       <c r="A659" t="s">
         <v>3612</v>
       </c>
@@ -29407,7 +29407,7 @@
         <v>3617</v>
       </c>
     </row>
-    <row r="660" hidden="1">
+    <row r="660">
       <c r="A660" t="s">
         <v>3618</v>
       </c>
@@ -29433,7 +29433,7 @@
         <v>3623</v>
       </c>
     </row>
-    <row r="661" hidden="1">
+    <row r="661">
       <c r="A661" t="s">
         <v>3624</v>
       </c>
@@ -29459,7 +29459,7 @@
         <v>3629</v>
       </c>
     </row>
-    <row r="662" hidden="1">
+    <row r="662">
       <c r="A662" t="s">
         <v>3630</v>
       </c>
@@ -29485,7 +29485,7 @@
         <v>3635</v>
       </c>
     </row>
-    <row r="663" hidden="1">
+    <row r="663">
       <c r="A663" t="s">
         <v>3636</v>
       </c>
@@ -29511,7 +29511,7 @@
         <v>3641</v>
       </c>
     </row>
-    <row r="664" hidden="1">
+    <row r="664">
       <c r="A664" t="s">
         <v>3642</v>
       </c>
@@ -29537,7 +29537,7 @@
         <v>3647</v>
       </c>
     </row>
-    <row r="665" hidden="1">
+    <row r="665">
       <c r="A665" t="s">
         <v>3648</v>
       </c>
@@ -29563,7 +29563,7 @@
         <v>3653</v>
       </c>
     </row>
-    <row r="666" hidden="1">
+    <row r="666">
       <c r="A666" t="s">
         <v>3654</v>
       </c>
@@ -29589,7 +29589,7 @@
         <v>3659</v>
       </c>
     </row>
-    <row r="667" hidden="1">
+    <row r="667">
       <c r="A667" t="s">
         <v>3660</v>
       </c>
@@ -29615,7 +29615,7 @@
         <v>3665</v>
       </c>
     </row>
-    <row r="668" hidden="1">
+    <row r="668">
       <c r="A668" t="s">
         <v>3666</v>
       </c>
@@ -29641,7 +29641,7 @@
         <v>3671</v>
       </c>
     </row>
-    <row r="669" hidden="1">
+    <row r="669">
       <c r="A669" t="s">
         <v>3672</v>
       </c>
@@ -29690,7 +29690,7 @@
         <v>3682</v>
       </c>
     </row>
-    <row r="671" hidden="1">
+    <row r="671">
       <c r="A671" t="s">
         <v>3683</v>
       </c>
@@ -29762,7 +29762,7 @@
         <v>3698</v>
       </c>
     </row>
-    <row r="674" hidden="1">
+    <row r="674">
       <c r="A674" t="s">
         <v>3699</v>
       </c>
@@ -29788,7 +29788,7 @@
         <v>3704</v>
       </c>
     </row>
-    <row r="675" hidden="1">
+    <row r="675">
       <c r="A675" t="s">
         <v>3705</v>
       </c>
@@ -29814,7 +29814,7 @@
         <v>3710</v>
       </c>
     </row>
-    <row r="676" hidden="1">
+    <row r="676">
       <c r="A676" t="s">
         <v>3711</v>
       </c>
@@ -29840,7 +29840,7 @@
         <v>3716</v>
       </c>
     </row>
-    <row r="677" hidden="1">
+    <row r="677">
       <c r="A677" t="s">
         <v>3717</v>
       </c>
@@ -29866,7 +29866,7 @@
         <v>3722</v>
       </c>
     </row>
-    <row r="678" hidden="1">
+    <row r="678">
       <c r="A678" t="s">
         <v>3723</v>
       </c>
@@ -29892,7 +29892,7 @@
         <v>3728</v>
       </c>
     </row>
-    <row r="679" hidden="1">
+    <row r="679">
       <c r="A679" t="s">
         <v>3729</v>
       </c>
@@ -29918,7 +29918,7 @@
         <v>3734</v>
       </c>
     </row>
-    <row r="680" hidden="1">
+    <row r="680">
       <c r="A680" t="s">
         <v>3735</v>
       </c>
@@ -29944,7 +29944,7 @@
         <v>3740</v>
       </c>
     </row>
-    <row r="681" hidden="1">
+    <row r="681">
       <c r="A681" t="s">
         <v>3741</v>
       </c>
@@ -29970,7 +29970,7 @@
         <v>3746</v>
       </c>
     </row>
-    <row r="682" hidden="1">
+    <row r="682">
       <c r="A682" t="s">
         <v>3747</v>
       </c>
@@ -29996,7 +29996,7 @@
         <v>3752</v>
       </c>
     </row>
-    <row r="683" hidden="1">
+    <row r="683">
       <c r="A683" t="s">
         <v>3753</v>
       </c>
@@ -30022,7 +30022,7 @@
         <v>3758</v>
       </c>
     </row>
-    <row r="684" hidden="1">
+    <row r="684">
       <c r="A684" t="s">
         <v>3759</v>
       </c>
@@ -30048,7 +30048,7 @@
         <v>3764</v>
       </c>
     </row>
-    <row r="685" hidden="1">
+    <row r="685">
       <c r="A685" t="s">
         <v>3765</v>
       </c>
@@ -30074,7 +30074,7 @@
         <v>3770</v>
       </c>
     </row>
-    <row r="686" hidden="1">
+    <row r="686">
       <c r="A686" t="s">
         <v>3771</v>
       </c>
@@ -30100,7 +30100,7 @@
         <v>3776</v>
       </c>
     </row>
-    <row r="687" hidden="1">
+    <row r="687">
       <c r="A687" t="s">
         <v>3777</v>
       </c>
@@ -30126,7 +30126,7 @@
         <v>3782</v>
       </c>
     </row>
-    <row r="688" hidden="1">
+    <row r="688">
       <c r="A688" t="s">
         <v>3783</v>
       </c>
@@ -30175,7 +30175,7 @@
         <v>3793</v>
       </c>
     </row>
-    <row r="690" hidden="1">
+    <row r="690">
       <c r="A690" t="s">
         <v>3794</v>
       </c>
@@ -30638,7 +30638,7 @@
         <v>3894</v>
       </c>
     </row>
-    <row r="710" hidden="1">
+    <row r="710">
       <c r="A710" t="s">
         <v>3895</v>
       </c>
@@ -30664,7 +30664,7 @@
         <v>3900</v>
       </c>
     </row>
-    <row r="711" hidden="1">
+    <row r="711">
       <c r="A711" t="s">
         <v>3901</v>
       </c>
@@ -30690,7 +30690,7 @@
         <v>3906</v>
       </c>
     </row>
-    <row r="712" hidden="1">
+    <row r="712">
       <c r="A712" t="s">
         <v>3907</v>
       </c>
@@ -30716,7 +30716,7 @@
         <v>3912</v>
       </c>
     </row>
-    <row r="713" hidden="1">
+    <row r="713">
       <c r="A713" t="s">
         <v>3913</v>
       </c>
@@ -30742,7 +30742,7 @@
         <v>3918</v>
       </c>
     </row>
-    <row r="714" hidden="1">
+    <row r="714">
       <c r="A714" t="s">
         <v>3919</v>
       </c>
@@ -30768,7 +30768,7 @@
         <v>3924</v>
       </c>
     </row>
-    <row r="715" hidden="1">
+    <row r="715">
       <c r="A715" t="s">
         <v>3925</v>
       </c>
@@ -30794,7 +30794,7 @@
         <v>3930</v>
       </c>
     </row>
-    <row r="716" hidden="1">
+    <row r="716">
       <c r="A716" t="s">
         <v>3931</v>
       </c>
@@ -30820,7 +30820,7 @@
         <v>3936</v>
       </c>
     </row>
-    <row r="717" hidden="1">
+    <row r="717">
       <c r="A717" t="s">
         <v>3937</v>
       </c>
@@ -30846,7 +30846,7 @@
         <v>3942</v>
       </c>
     </row>
-    <row r="718" hidden="1">
+    <row r="718">
       <c r="A718" t="s">
         <v>3943</v>
       </c>
@@ -30872,7 +30872,7 @@
         <v>3948</v>
       </c>
     </row>
-    <row r="719" hidden="1">
+    <row r="719">
       <c r="A719" t="s">
         <v>3949</v>
       </c>
@@ -30924,7 +30924,7 @@
         <v>3960</v>
       </c>
     </row>
-    <row r="721" hidden="1">
+    <row r="721">
       <c r="A721" t="s">
         <v>3961</v>
       </c>
@@ -30950,7 +30950,7 @@
         <v>3966</v>
       </c>
     </row>
-    <row r="722" hidden="1">
+    <row r="722">
       <c r="A722" t="s">
         <v>3967</v>
       </c>
@@ -30976,7 +30976,7 @@
         <v>3972</v>
       </c>
     </row>
-    <row r="723" hidden="1">
+    <row r="723">
       <c r="A723" t="s">
         <v>3973</v>
       </c>
@@ -31002,7 +31002,7 @@
         <v>3978</v>
       </c>
     </row>
-    <row r="724" hidden="1">
+    <row r="724">
       <c r="A724" t="s">
         <v>3979</v>
       </c>
@@ -31028,7 +31028,7 @@
         <v>3984</v>
       </c>
     </row>
-    <row r="725" hidden="1">
+    <row r="725">
       <c r="A725" t="s">
         <v>3985</v>
       </c>
@@ -31100,7 +31100,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="728" hidden="1">
+    <row r="728">
       <c r="A728" t="s">
         <v>4001</v>
       </c>
@@ -31126,7 +31126,7 @@
         <v>4006</v>
       </c>
     </row>
-    <row r="729" hidden="1">
+    <row r="729">
       <c r="A729" t="s">
         <v>4007</v>
       </c>
@@ -31152,7 +31152,7 @@
         <v>4012</v>
       </c>
     </row>
-    <row r="730" hidden="1">
+    <row r="730">
       <c r="A730" t="s">
         <v>4013</v>
       </c>
@@ -31178,7 +31178,7 @@
         <v>4018</v>
       </c>
     </row>
-    <row r="731" hidden="1">
+    <row r="731">
       <c r="A731" t="s">
         <v>4019</v>
       </c>
@@ -31204,7 +31204,7 @@
         <v>4024</v>
       </c>
     </row>
-    <row r="732" hidden="1">
+    <row r="732">
       <c r="A732" t="s">
         <v>4025</v>
       </c>
@@ -31230,7 +31230,7 @@
         <v>4030</v>
       </c>
     </row>
-    <row r="733" hidden="1">
+    <row r="733">
       <c r="A733" t="s">
         <v>4031</v>
       </c>
@@ -31256,7 +31256,7 @@
         <v>4036</v>
       </c>
     </row>
-    <row r="734" hidden="1">
+    <row r="734">
       <c r="A734" t="s">
         <v>4037</v>
       </c>
@@ -31282,7 +31282,7 @@
         <v>4042</v>
       </c>
     </row>
-    <row r="735" hidden="1">
+    <row r="735">
       <c r="A735" t="s">
         <v>4043</v>
       </c>
@@ -31308,7 +31308,7 @@
         <v>4048</v>
       </c>
     </row>
-    <row r="736" hidden="1">
+    <row r="736">
       <c r="A736" t="s">
         <v>4049</v>
       </c>
@@ -31334,7 +31334,7 @@
         <v>4054</v>
       </c>
     </row>
-    <row r="737" hidden="1">
+    <row r="737">
       <c r="A737" t="s">
         <v>4055</v>
       </c>
@@ -31360,7 +31360,7 @@
         <v>4060</v>
       </c>
     </row>
-    <row r="738" hidden="1">
+    <row r="738">
       <c r="A738" t="s">
         <v>4061</v>
       </c>
@@ -31386,7 +31386,7 @@
         <v>4066</v>
       </c>
     </row>
-    <row r="739" hidden="1">
+    <row r="739">
       <c r="A739" t="s">
         <v>4067</v>
       </c>
@@ -31412,7 +31412,7 @@
         <v>4072</v>
       </c>
     </row>
-    <row r="740" hidden="1">
+    <row r="740">
       <c r="A740" t="s">
         <v>4073</v>
       </c>
@@ -31438,7 +31438,7 @@
         <v>4078</v>
       </c>
     </row>
-    <row r="741" hidden="1">
+    <row r="741">
       <c r="A741" t="s">
         <v>4079</v>
       </c>
@@ -31464,7 +31464,7 @@
         <v>4084</v>
       </c>
     </row>
-    <row r="742" hidden="1">
+    <row r="742">
       <c r="A742" t="s">
         <v>4085</v>
       </c>
@@ -31490,7 +31490,7 @@
         <v>4089</v>
       </c>
     </row>
-    <row r="743" hidden="1">
+    <row r="743">
       <c r="A743" t="s">
         <v>4090</v>
       </c>
@@ -31516,7 +31516,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="744" hidden="1">
+    <row r="744">
       <c r="A744" t="s">
         <v>4095</v>
       </c>
@@ -31542,7 +31542,7 @@
         <v>4099</v>
       </c>
     </row>
-    <row r="745" hidden="1">
+    <row r="745">
       <c r="A745" t="s">
         <v>4100</v>
       </c>
@@ -31568,7 +31568,7 @@
         <v>4105</v>
       </c>
     </row>
-    <row r="746" hidden="1">
+    <row r="746">
       <c r="A746" t="s">
         <v>4106</v>
       </c>
@@ -31599,11 +31599,6 @@
     <filterColumn colId="2">
       <filters>
         <filter val="Maps"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="SlateportCity"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -31615,7 +31610,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{95B020A7-C0FB-4292-B40E-FE5B959A638D}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{4C2E2DEE-4C5B-4D27-892E-80D11AA553ED}">
             <xm:f>"Vertaald"</xm:f>
             <x14:dxf>
               <font>
@@ -31632,7 +31627,7 @@
           <xm:sqref>G:G</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{B3E5C46B-EECF-4E19-A663-21BE19D49B9E}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{A45EB6C7-D7EE-4B22-A937-54FCA28BA216}">
             <xm:f>"Onvertaald"</xm:f>
             <x14:dxf>
               <font>

--- a/translation_dashboard.xlsx
+++ b/translation_dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acvcsc-my.sharepoint.com/personal/ancome_acv-csc_be/Documents/Documenten/Privé/pokemVertaling/pokeemerald/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="11_3C1E32166B49433309C3CAE053D618C3880E743F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68BFB953-3B8C-4379-9C43-F89AB79E2E00}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_3C1E32166B49433309C3CAE053D618C3880E743F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20EA534F-EC52-487C-B18B-CF4F29D6C5C2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4138" uniqueCount="4107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4140" uniqueCount="4108">
   <si>
     <t>Bestand</t>
   </si>
@@ -12358,6 +12358,9 @@
   </si>
   <si>
     <t>Hulp PJ</t>
+  </si>
+  <si>
+    <t>HEEFT TEKST!</t>
   </si>
 </sst>
 </file>
@@ -12979,7 +12982,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:I746"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -13020,7 +13022,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -13046,7 +13048,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -13069,7 +13071,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -13092,7 +13094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -13115,7 +13117,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3945</v>
       </c>
@@ -13141,7 +13143,7 @@
         <v>3949</v>
       </c>
     </row>
-    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -13167,7 +13169,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -13193,7 +13195,7 @@
         <v>4106</v>
       </c>
     </row>
-    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -13216,7 +13218,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -13239,7 +13241,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -13265,7 +13267,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -13291,7 +13293,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -13314,7 +13316,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -13337,7 +13339,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -13360,7 +13362,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>786</v>
       </c>
@@ -13383,7 +13385,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>81</v>
       </c>
@@ -13406,7 +13408,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>2690</v>
       </c>
@@ -13429,7 +13431,7 @@
         <v>2693</v>
       </c>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -13455,7 +13457,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>97</v>
       </c>
@@ -13478,7 +13480,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>102</v>
       </c>
@@ -13501,7 +13503,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>672</v>
       </c>
@@ -13524,7 +13526,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>112</v>
       </c>
@@ -13550,7 +13552,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>118</v>
       </c>
@@ -13576,7 +13578,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -13599,7 +13601,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>129</v>
       </c>
@@ -13622,7 +13624,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>2793</v>
       </c>
@@ -13645,7 +13647,7 @@
         <v>2797</v>
       </c>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>139</v>
       </c>
@@ -13667,8 +13669,11 @@
       <c r="H28" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I28" t="s">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>144</v>
       </c>
@@ -13691,7 +13696,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>149</v>
       </c>
@@ -13714,7 +13719,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>154</v>
       </c>
@@ -13740,7 +13745,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>165</v>
       </c>
@@ -13762,8 +13767,11 @@
       <c r="H32" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="I32" t="s">
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>235</v>
       </c>
@@ -13786,7 +13794,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>180</v>
       </c>
@@ -13835,7 +13843,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>191</v>
       </c>
@@ -13858,7 +13866,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>196</v>
       </c>
@@ -13881,7 +13889,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>201</v>
       </c>
@@ -13907,7 +13915,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>207</v>
       </c>
@@ -13930,7 +13938,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>212</v>
       </c>
@@ -13956,7 +13964,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>218</v>
       </c>
@@ -13979,7 +13987,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>223</v>
       </c>
@@ -14005,7 +14013,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>229</v>
       </c>
@@ -14031,7 +14039,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>575</v>
       </c>
@@ -14054,7 +14062,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>240</v>
       </c>
@@ -14077,7 +14085,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>245</v>
       </c>
@@ -14100,7 +14108,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1095</v>
       </c>
@@ -14123,7 +14131,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>255</v>
       </c>
@@ -14146,7 +14154,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>260</v>
       </c>
@@ -14169,7 +14177,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>265</v>
       </c>
@@ -14192,7 +14200,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>270</v>
       </c>
@@ -14218,7 +14226,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>281</v>
       </c>
@@ -14244,7 +14252,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>287</v>
       </c>
@@ -14270,7 +14278,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>2831</v>
       </c>
@@ -14293,7 +14301,7 @@
         <v>2835</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>3017</v>
       </c>
@@ -14316,7 +14324,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>303</v>
       </c>
@@ -14339,7 +14347,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>802</v>
       </c>
@@ -14362,7 +14370,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>313</v>
       </c>
@@ -14385,7 +14393,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>318</v>
       </c>
@@ -14408,7 +14416,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>463</v>
       </c>
@@ -14431,7 +14439,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>328</v>
       </c>
@@ -14454,7 +14462,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>333</v>
       </c>
@@ -14477,7 +14485,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>338</v>
       </c>
@@ -14500,7 +14508,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>343</v>
       </c>
@@ -14523,7 +14531,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>348</v>
       </c>
@@ -14546,7 +14554,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>353</v>
       </c>
@@ -14572,7 +14580,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>359</v>
       </c>
@@ -14598,7 +14606,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>293</v>
       </c>
@@ -14621,7 +14629,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>107</v>
       </c>
@@ -14644,7 +14652,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>375</v>
       </c>
@@ -14667,7 +14675,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>380</v>
       </c>
@@ -14690,7 +14698,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>385</v>
       </c>
@@ -14713,7 +14721,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>390</v>
       </c>
@@ -14739,7 +14747,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>396</v>
       </c>
@@ -14762,7 +14770,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>401</v>
       </c>
@@ -14785,7 +14793,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>406</v>
       </c>
@@ -14808,7 +14816,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>365</v>
       </c>
@@ -14831,7 +14839,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>543</v>
       </c>
@@ -14854,7 +14862,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>421</v>
       </c>
@@ -14877,7 +14885,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>426</v>
       </c>
@@ -14900,7 +14908,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>431</v>
       </c>
@@ -14923,7 +14931,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>436</v>
       </c>
@@ -14949,7 +14957,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>442</v>
       </c>
@@ -14972,7 +14980,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>617</v>
       </c>
@@ -14995,7 +15003,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>452</v>
       </c>
@@ -15018,7 +15026,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>457</v>
       </c>
@@ -15044,7 +15052,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>323</v>
       </c>
@@ -15067,7 +15075,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>468</v>
       </c>
@@ -15090,7 +15098,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>473</v>
       </c>
@@ -15116,7 +15124,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>175</v>
       </c>
@@ -15139,7 +15147,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>484</v>
       </c>
@@ -15162,7 +15170,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>677</v>
       </c>
@@ -15185,7 +15193,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>494</v>
       </c>
@@ -15211,7 +15219,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>500</v>
       </c>
@@ -15234,7 +15242,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>505</v>
       </c>
@@ -15257,7 +15265,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>510</v>
       </c>
@@ -15280,7 +15288,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>515</v>
       </c>
@@ -15306,7 +15314,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>521</v>
       </c>
@@ -15329,7 +15337,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>526</v>
       </c>
@@ -15352,7 +15360,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>531</v>
       </c>
@@ -15378,7 +15386,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>537</v>
       </c>
@@ -15404,7 +15412,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1000</v>
       </c>
@@ -15427,7 +15435,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>548</v>
       </c>
@@ -15450,7 +15458,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>553</v>
       </c>
@@ -15473,7 +15481,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>558</v>
       </c>
@@ -15499,7 +15507,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>564</v>
       </c>
@@ -15525,7 +15533,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>570</v>
       </c>
@@ -15548,7 +15556,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>1331</v>
       </c>
@@ -15571,7 +15579,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>580</v>
       </c>
@@ -15623,7 +15631,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>591</v>
       </c>
@@ -15649,7 +15657,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>1143</v>
       </c>
@@ -15672,7 +15680,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>602</v>
       </c>
@@ -15695,7 +15703,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>607</v>
       </c>
@@ -15718,7 +15726,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>612</v>
       </c>
@@ -15741,7 +15749,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>861</v>
       </c>
@@ -15764,7 +15772,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>622</v>
       </c>
@@ -15790,7 +15798,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>628</v>
       </c>
@@ -15813,7 +15821,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>633</v>
       </c>
@@ -15839,7 +15847,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>3985</v>
       </c>
@@ -15862,7 +15870,7 @@
         <v>3989</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>644</v>
       </c>
@@ -15888,7 +15896,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>650</v>
       </c>
@@ -15911,7 +15919,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>416</v>
       </c>
@@ -15934,7 +15942,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>660</v>
       </c>
@@ -15960,7 +15968,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>666</v>
       </c>
@@ -15986,7 +15994,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>298</v>
       </c>
@@ -16009,7 +16017,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>2434</v>
       </c>
@@ -16032,7 +16040,7 @@
         <v>2438</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>682</v>
       </c>
@@ -16055,7 +16063,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>687</v>
       </c>
@@ -16078,7 +16086,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>692</v>
       </c>
@@ -16104,7 +16112,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>698</v>
       </c>
@@ -16127,7 +16135,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>703</v>
       </c>
@@ -16153,7 +16161,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>709</v>
       </c>
@@ -16179,7 +16187,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>715</v>
       </c>
@@ -16205,7 +16213,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>721</v>
       </c>
@@ -16228,7 +16236,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>726</v>
       </c>
@@ -16251,7 +16259,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>731</v>
       </c>
@@ -16277,7 +16285,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>737</v>
       </c>
@@ -16303,7 +16311,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>743</v>
       </c>
@@ -16326,7 +16334,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>748</v>
       </c>
@@ -16352,7 +16360,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>754</v>
       </c>
@@ -16378,7 +16386,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>2179</v>
       </c>
@@ -16401,7 +16409,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>765</v>
       </c>
@@ -16450,7 +16458,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>775</v>
       </c>
@@ -16476,7 +16484,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>781</v>
       </c>
@@ -16499,7 +16507,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>1127</v>
       </c>
@@ -16522,7 +16530,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>791</v>
       </c>
@@ -16545,7 +16553,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>796</v>
       </c>
@@ -16571,7 +16579,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>1381</v>
       </c>
@@ -16594,7 +16602,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>851</v>
       </c>
@@ -16617,7 +16625,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>812</v>
       </c>
@@ -16643,7 +16651,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>818</v>
       </c>
@@ -16666,7 +16674,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>823</v>
       </c>
@@ -16692,7 +16700,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>829</v>
       </c>
@@ -16718,7 +16726,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>835</v>
       </c>
@@ -16744,7 +16752,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>841</v>
       </c>
@@ -16767,7 +16775,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>846</v>
       </c>
@@ -16790,7 +16798,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>489</v>
       </c>
@@ -16813,7 +16821,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>856</v>
       </c>
@@ -16836,7 +16844,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>308</v>
       </c>
@@ -16859,7 +16867,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>866</v>
       </c>
@@ -16882,7 +16890,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>871</v>
       </c>
@@ -16931,7 +16939,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>882</v>
       </c>
@@ -16954,7 +16962,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>887</v>
       </c>
@@ -16980,7 +16988,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>893</v>
       </c>
@@ -17006,7 +17014,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>899</v>
       </c>
@@ -17029,7 +17037,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>904</v>
       </c>
@@ -17055,7 +17063,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>910</v>
       </c>
@@ -17078,7 +17086,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>597</v>
       </c>
@@ -17101,7 +17109,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1801</v>
       </c>
@@ -17124,7 +17132,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>925</v>
       </c>
@@ -17147,7 +17155,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>930</v>
       </c>
@@ -17170,7 +17178,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>935</v>
       </c>
@@ -17196,7 +17204,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>941</v>
       </c>
@@ -17219,7 +17227,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>946</v>
       </c>
@@ -17245,7 +17253,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>952</v>
       </c>
@@ -17268,7 +17276,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>957</v>
       </c>
@@ -17294,7 +17302,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>963</v>
       </c>
@@ -17317,7 +17325,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>968</v>
       </c>
@@ -17340,7 +17348,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>973</v>
       </c>
@@ -17363,7 +17371,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>978</v>
       </c>
@@ -17389,7 +17397,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>3980</v>
       </c>
@@ -17412,7 +17420,7 @@
         <v>3984</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>989</v>
       </c>
@@ -17438,7 +17446,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>995</v>
       </c>
@@ -17461,7 +17469,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>2580</v>
       </c>
@@ -17484,7 +17492,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>1005</v>
       </c>
@@ -17510,7 +17518,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>2006</v>
       </c>
@@ -17533,7 +17541,7 @@
         <v>2009</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>1016</v>
       </c>
@@ -17559,7 +17567,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>1022</v>
       </c>
@@ -17582,7 +17590,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>1027</v>
       </c>
@@ -17605,7 +17613,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1032</v>
       </c>
@@ -17634,7 +17642,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1039</v>
       </c>
@@ -17660,7 +17668,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1045</v>
       </c>
@@ -17686,7 +17694,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>1051</v>
       </c>
@@ -17709,7 +17717,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1056</v>
       </c>
@@ -17732,7 +17740,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1061</v>
       </c>
@@ -17755,7 +17763,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1066</v>
       </c>
@@ -17781,7 +17789,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>1072</v>
       </c>
@@ -17807,7 +17815,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1078</v>
       </c>
@@ -17833,7 +17841,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>1084</v>
       </c>
@@ -17859,7 +17867,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>1090</v>
       </c>
@@ -17882,7 +17890,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>1925</v>
       </c>
@@ -17905,7 +17913,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>1100</v>
       </c>
@@ -17931,7 +17939,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>1106</v>
       </c>
@@ -17954,7 +17962,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>1111</v>
       </c>
@@ -17980,7 +17988,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>1117</v>
       </c>
@@ -18003,7 +18011,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>807</v>
       </c>
@@ -18026,7 +18034,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>2265</v>
       </c>
@@ -18049,7 +18057,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>1132</v>
       </c>
@@ -18075,7 +18083,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>1138</v>
       </c>
@@ -18098,7 +18106,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>1429</v>
       </c>
@@ -18121,7 +18129,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>1148</v>
       </c>
@@ -18144,7 +18152,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>1153</v>
       </c>
@@ -18170,7 +18178,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>2412</v>
       </c>
@@ -18193,7 +18201,7 @@
         <v>2416</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>1164</v>
       </c>
@@ -18219,7 +18227,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>1170</v>
       </c>
@@ -18245,7 +18253,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>1176</v>
       </c>
@@ -18268,7 +18276,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>1181</v>
       </c>
@@ -18294,7 +18302,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>1187</v>
       </c>
@@ -18317,7 +18325,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>1192</v>
       </c>
@@ -18343,7 +18351,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>1198</v>
       </c>
@@ -18366,7 +18374,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>1203</v>
       </c>
@@ -18389,7 +18397,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>1208</v>
       </c>
@@ -18412,7 +18420,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>1213</v>
       </c>
@@ -18435,7 +18443,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>1218</v>
       </c>
@@ -18458,7 +18466,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>1223</v>
       </c>
@@ -18484,7 +18492,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>1229</v>
       </c>
@@ -18507,7 +18515,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>1234</v>
       </c>
@@ -18533,7 +18541,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1240</v>
       </c>
@@ -18556,7 +18564,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1245</v>
       </c>
@@ -18579,7 +18587,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1250</v>
       </c>
@@ -18605,7 +18613,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>1256</v>
       </c>
@@ -18628,7 +18636,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1261</v>
       </c>
@@ -18651,7 +18659,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1266</v>
       </c>
@@ -18674,7 +18682,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1271</v>
       </c>
@@ -18697,7 +18705,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1276</v>
       </c>
@@ -18720,7 +18728,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1281</v>
       </c>
@@ -18743,7 +18751,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1286</v>
       </c>
@@ -18769,7 +18777,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1292</v>
       </c>
@@ -18792,7 +18800,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1297</v>
       </c>
@@ -18818,7 +18826,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1303</v>
       </c>
@@ -18841,7 +18849,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1308</v>
       </c>
@@ -18867,7 +18875,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1314</v>
       </c>
@@ -18893,7 +18901,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1320</v>
       </c>
@@ -18916,7 +18924,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1325</v>
       </c>
@@ -18942,7 +18950,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>2021</v>
       </c>
@@ -18965,7 +18973,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1336</v>
       </c>
@@ -18991,7 +18999,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1342</v>
       </c>
@@ -19014,7 +19022,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1347</v>
       </c>
@@ -19040,7 +19048,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1353</v>
       </c>
@@ -19066,7 +19074,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1359</v>
       </c>
@@ -19092,7 +19100,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1365</v>
       </c>
@@ -19115,7 +19123,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1370</v>
       </c>
@@ -19141,7 +19149,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1376</v>
       </c>
@@ -19164,7 +19172,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>920</v>
       </c>
@@ -19187,7 +19195,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1386</v>
       </c>
@@ -19213,7 +19221,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1392</v>
       </c>
@@ -19239,7 +19247,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1398</v>
       </c>
@@ -19265,7 +19273,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1404</v>
       </c>
@@ -19288,7 +19296,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>760</v>
       </c>
@@ -19311,7 +19319,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1414</v>
       </c>
@@ -19334,7 +19342,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1419</v>
       </c>
@@ -19357,7 +19365,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1424</v>
       </c>
@@ -19380,7 +19388,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>26</v>
       </c>
@@ -19403,7 +19411,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1434</v>
       </c>
@@ -19426,7 +19434,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>1439</v>
       </c>
@@ -19452,7 +19460,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>1445</v>
       </c>
@@ -19475,7 +19483,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>1450</v>
       </c>
@@ -19498,7 +19506,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>1455</v>
       </c>
@@ -19524,7 +19532,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>1461</v>
       </c>
@@ -19550,7 +19558,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>1466</v>
       </c>
@@ -19576,7 +19584,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>1472</v>
       </c>
@@ -19602,7 +19610,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>1478</v>
       </c>
@@ -19625,7 +19633,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>1483</v>
       </c>
@@ -19651,7 +19659,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>1489</v>
       </c>
@@ -19674,7 +19682,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>1494</v>
       </c>
@@ -19700,7 +19708,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>1500</v>
       </c>
@@ -19726,7 +19734,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>1506</v>
       </c>
@@ -19752,7 +19760,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>1512</v>
       </c>
@@ -19778,7 +19786,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>1518</v>
       </c>
@@ -19801,7 +19809,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>1523</v>
       </c>
@@ -19827,7 +19835,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>1529</v>
       </c>
@@ -19850,7 +19858,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>1534</v>
       </c>
@@ -19876,7 +19884,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>1540</v>
       </c>
@@ -19902,7 +19910,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>1546</v>
       </c>
@@ -19928,7 +19936,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>160</v>
       </c>
@@ -19951,7 +19959,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>1557</v>
       </c>
@@ -19977,7 +19985,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>170</v>
       </c>
@@ -20000,7 +20008,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>1568</v>
       </c>
@@ -20026,7 +20034,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>1574</v>
       </c>
@@ -20052,7 +20060,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>370</v>
       </c>
@@ -20075,7 +20083,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>1585</v>
       </c>
@@ -20101,7 +20109,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>1591</v>
       </c>
@@ -20127,7 +20135,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>1597</v>
       </c>
@@ -20153,7 +20161,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>1603</v>
       </c>
@@ -20202,7 +20210,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>1613</v>
       </c>
@@ -20228,7 +20236,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>1619</v>
       </c>
@@ -20254,7 +20262,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>1625</v>
       </c>
@@ -20280,7 +20288,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>1631</v>
       </c>
@@ -20306,7 +20314,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>1637</v>
       </c>
@@ -20329,7 +20337,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>1642</v>
       </c>
@@ -20355,7 +20363,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>1648</v>
       </c>
@@ -20378,7 +20386,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>1653</v>
       </c>
@@ -20404,7 +20412,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>1659</v>
       </c>
@@ -20430,7 +20438,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>1665</v>
       </c>
@@ -20456,7 +20464,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>1671</v>
       </c>
@@ -20482,7 +20490,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>1677</v>
       </c>
@@ -20508,7 +20516,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>1683</v>
       </c>
@@ -20534,7 +20542,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>1689</v>
       </c>
@@ -20557,7 +20565,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>1694</v>
       </c>
@@ -20580,7 +20588,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>1699</v>
       </c>
@@ -20606,7 +20614,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>1705</v>
       </c>
@@ -20632,7 +20640,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>1711</v>
       </c>
@@ -20658,7 +20666,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>1717</v>
       </c>
@@ -20681,7 +20689,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>1722</v>
       </c>
@@ -20707,7 +20715,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>1728</v>
       </c>
@@ -20733,7 +20741,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>1734</v>
       </c>
@@ -20756,7 +20764,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>1739</v>
       </c>
@@ -20782,7 +20790,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>1745</v>
       </c>
@@ -20808,7 +20816,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>1751</v>
       </c>
@@ -20831,7 +20839,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>1756</v>
       </c>
@@ -20854,7 +20862,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>1761</v>
       </c>
@@ -20903,7 +20911,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>1771</v>
       </c>
@@ -20929,7 +20937,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>1777</v>
       </c>
@@ -20955,7 +20963,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>1783</v>
       </c>
@@ -20981,7 +20989,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>1789</v>
       </c>
@@ -21007,7 +21015,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>1795</v>
       </c>
@@ -21033,7 +21041,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>1159</v>
       </c>
@@ -21056,7 +21064,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>1806</v>
       </c>
@@ -21082,7 +21090,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>1812</v>
       </c>
@@ -21108,7 +21116,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>1818</v>
       </c>
@@ -21131,7 +21139,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>1823</v>
       </c>
@@ -21157,7 +21165,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>1829</v>
       </c>
@@ -21180,7 +21188,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>1834</v>
       </c>
@@ -21206,7 +21214,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>1840</v>
       </c>
@@ -21235,7 +21243,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>1847</v>
       </c>
@@ -21258,7 +21266,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>1852</v>
       </c>
@@ -21284,7 +21292,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>1858</v>
       </c>
@@ -21310,7 +21318,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>1864</v>
       </c>
@@ -21336,7 +21344,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>1870</v>
       </c>
@@ -21362,7 +21370,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>1876</v>
       </c>
@@ -21388,7 +21396,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>1882</v>
       </c>
@@ -21414,7 +21422,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>1888</v>
       </c>
@@ -21437,7 +21445,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>1893</v>
       </c>
@@ -21463,7 +21471,7 @@
         <v>1898</v>
       </c>
     </row>
-    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>1899</v>
       </c>
@@ -21489,7 +21497,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>1905</v>
       </c>
@@ -21515,7 +21523,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>1911</v>
       </c>
@@ -21538,7 +21546,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>1916</v>
       </c>
@@ -21561,7 +21569,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>1921</v>
       </c>
@@ -21584,7 +21592,7 @@
         <v>1924</v>
       </c>
     </row>
-    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>250</v>
       </c>
@@ -21607,7 +21615,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>1929</v>
       </c>
@@ -21630,7 +21638,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>1934</v>
       </c>
@@ -21656,7 +21664,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>1940</v>
       </c>
@@ -21682,7 +21690,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>1946</v>
       </c>
@@ -21705,7 +21713,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>1951</v>
       </c>
@@ -21734,7 +21742,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>1958</v>
       </c>
@@ -21760,7 +21768,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>1964</v>
       </c>
@@ -21783,7 +21791,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>1969</v>
       </c>
@@ -21806,7 +21814,7 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>1974</v>
       </c>
@@ -21832,7 +21840,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>1980</v>
       </c>
@@ -21858,7 +21866,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>1986</v>
       </c>
@@ -21881,7 +21889,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>1991</v>
       </c>
@@ -21904,7 +21912,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>1996</v>
       </c>
@@ -21927,7 +21935,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>2001</v>
       </c>
@@ -21950,7 +21958,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>2826</v>
       </c>
@@ -21973,7 +21981,7 @@
         <v>2830</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>2010</v>
       </c>
@@ -21999,7 +22007,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>2016</v>
       </c>
@@ -22022,7 +22030,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>1122</v>
       </c>
@@ -22045,7 +22053,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>2026</v>
       </c>
@@ -22071,7 +22079,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>2032</v>
       </c>
@@ -22097,7 +22105,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>2038</v>
       </c>
@@ -22123,7 +22131,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>2044</v>
       </c>
@@ -22149,7 +22157,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>2050</v>
       </c>
@@ -22172,7 +22180,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>655</v>
       </c>
@@ -22195,7 +22203,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>2060</v>
       </c>
@@ -22221,7 +22229,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>2066</v>
       </c>
@@ -22244,7 +22252,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>2071</v>
       </c>
@@ -22267,7 +22275,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>2076</v>
       </c>
@@ -22293,7 +22301,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>2082</v>
       </c>
@@ -22319,7 +22327,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>2088</v>
       </c>
@@ -22342,7 +22350,7 @@
         <v>2092</v>
       </c>
     </row>
-    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>2093</v>
       </c>
@@ -22365,7 +22373,7 @@
         <v>2097</v>
       </c>
     </row>
-    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>2098</v>
       </c>
@@ -22391,7 +22399,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>2104</v>
       </c>
@@ -22417,7 +22425,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>2110</v>
       </c>
@@ -22443,7 +22451,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>2116</v>
       </c>
@@ -22469,7 +22477,7 @@
         <v>2121</v>
       </c>
     </row>
-    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>2122</v>
       </c>
@@ -22495,7 +22503,7 @@
         <v>2127</v>
       </c>
     </row>
-    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>2128</v>
       </c>
@@ -22521,7 +22529,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>2134</v>
       </c>
@@ -22547,7 +22555,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>2140</v>
       </c>
@@ -22573,7 +22581,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>2146</v>
       </c>
@@ -22599,7 +22607,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>2152</v>
       </c>
@@ -22622,7 +22630,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>2157</v>
       </c>
@@ -22645,7 +22653,7 @@
         <v>2161</v>
       </c>
     </row>
-    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>2162</v>
       </c>
@@ -22671,7 +22679,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>2168</v>
       </c>
@@ -22697,7 +22705,7 @@
         <v>2173</v>
       </c>
     </row>
-    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>2174</v>
       </c>
@@ -22720,7 +22728,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>984</v>
       </c>
@@ -22743,7 +22751,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>2184</v>
       </c>
@@ -22766,7 +22774,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>2189</v>
       </c>
@@ -22789,7 +22797,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>2194</v>
       </c>
@@ -22815,7 +22823,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>2200</v>
       </c>
@@ -22841,7 +22849,7 @@
         <v>2205</v>
       </c>
     </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>2206</v>
       </c>
@@ -22864,7 +22872,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>2211</v>
       </c>
@@ -22890,7 +22898,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>2217</v>
       </c>
@@ -22913,7 +22921,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>2222</v>
       </c>
@@ -22936,7 +22944,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>276</v>
       </c>
@@ -22959,7 +22967,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>2232</v>
       </c>
@@ -22985,7 +22993,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>2238</v>
       </c>
@@ -23008,7 +23016,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>2243</v>
       </c>
@@ -23031,7 +23039,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>2248</v>
       </c>
@@ -23054,7 +23062,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>2253</v>
       </c>
@@ -23080,7 +23088,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>2259</v>
       </c>
@@ -23106,7 +23114,7 @@
         <v>2264</v>
       </c>
     </row>
-    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>2055</v>
       </c>
@@ -23129,7 +23137,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>2270</v>
       </c>
@@ -23152,7 +23160,7 @@
         <v>2274</v>
       </c>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>2275</v>
       </c>
@@ -23178,7 +23186,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>2281</v>
       </c>
@@ -23204,7 +23212,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>2287</v>
       </c>
@@ -23227,7 +23235,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>2292</v>
       </c>
@@ -23253,7 +23261,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>2298</v>
       </c>
@@ -23276,7 +23284,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>2303</v>
       </c>
@@ -23302,7 +23310,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>2309</v>
       </c>
@@ -23325,7 +23333,7 @@
         <v>2313</v>
       </c>
     </row>
-    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>2314</v>
       </c>
@@ -23351,7 +23359,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>2320</v>
       </c>
@@ -23374,7 +23382,7 @@
         <v>2324</v>
       </c>
     </row>
-    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>2325</v>
       </c>
@@ -23397,7 +23405,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>2330</v>
       </c>
@@ -23423,7 +23431,7 @@
         <v>2335</v>
       </c>
     </row>
-    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>2336</v>
       </c>
@@ -23449,7 +23457,7 @@
         <v>2341</v>
       </c>
     </row>
-    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>2342</v>
       </c>
@@ -23475,7 +23483,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>2348</v>
       </c>
@@ -23501,7 +23509,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>2354</v>
       </c>
@@ -23527,7 +23535,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>2360</v>
       </c>
@@ -23553,7 +23561,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>2366</v>
       </c>
@@ -23576,7 +23584,7 @@
         <v>2370</v>
       </c>
     </row>
-    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>2371</v>
       </c>
@@ -23602,7 +23610,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>2377</v>
       </c>
@@ -23628,7 +23636,7 @@
         <v>2382</v>
       </c>
     </row>
-    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>2383</v>
       </c>
@@ -23654,7 +23662,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>2389</v>
       </c>
@@ -23680,7 +23688,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>2395</v>
       </c>
@@ -23706,7 +23714,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>2401</v>
       </c>
@@ -23732,7 +23740,7 @@
         <v>2406</v>
       </c>
     </row>
-    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>639</v>
       </c>
@@ -23755,7 +23763,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>134</v>
       </c>
@@ -23778,7 +23786,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>2417</v>
       </c>
@@ -23804,7 +23812,7 @@
         <v>2422</v>
       </c>
     </row>
-    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>2423</v>
       </c>
@@ -23827,7 +23835,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>2428</v>
       </c>
@@ -23853,7 +23861,7 @@
         <v>2433</v>
       </c>
     </row>
-    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1580</v>
       </c>
@@ -23876,7 +23884,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>2439</v>
       </c>
@@ -23902,7 +23910,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>2445</v>
       </c>
@@ -23928,7 +23936,7 @@
         <v>2450</v>
       </c>
     </row>
-    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>2451</v>
       </c>
@@ -23954,7 +23962,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>2456</v>
       </c>
@@ -23980,7 +23988,7 @@
         <v>2461</v>
       </c>
     </row>
-    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>2462</v>
       </c>
@@ -24003,7 +24011,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>2467</v>
       </c>
@@ -24029,7 +24037,7 @@
         <v>2472</v>
       </c>
     </row>
-    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>2473</v>
       </c>
@@ -24055,7 +24063,7 @@
         <v>2478</v>
       </c>
     </row>
-    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>2479</v>
       </c>
@@ -24078,7 +24086,7 @@
         <v>2483</v>
       </c>
     </row>
-    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>2484</v>
       </c>
@@ -24101,7 +24109,7 @@
         <v>2488</v>
       </c>
     </row>
-    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>2489</v>
       </c>
@@ -24127,7 +24135,7 @@
         <v>2494</v>
       </c>
     </row>
-    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>2495</v>
       </c>
@@ -24153,7 +24161,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>2501</v>
       </c>
@@ -24179,7 +24187,7 @@
         <v>2506</v>
       </c>
     </row>
-    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>2507</v>
       </c>
@@ -24205,7 +24213,7 @@
         <v>2512</v>
       </c>
     </row>
-    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>2513</v>
       </c>
@@ -24231,7 +24239,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>2519</v>
       </c>
@@ -24257,7 +24265,7 @@
         <v>2524</v>
       </c>
     </row>
-    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>2525</v>
       </c>
@@ -24280,7 +24288,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>2530</v>
       </c>
@@ -24303,7 +24311,7 @@
         <v>2534</v>
       </c>
     </row>
-    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>2535</v>
       </c>
@@ -24326,7 +24334,7 @@
         <v>2539</v>
       </c>
     </row>
-    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>2540</v>
       </c>
@@ -24352,7 +24360,7 @@
         <v>2545</v>
       </c>
     </row>
-    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>2546</v>
       </c>
@@ -24378,7 +24386,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>2552</v>
       </c>
@@ -24404,7 +24412,7 @@
         <v>2557</v>
       </c>
     </row>
-    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>2558</v>
       </c>
@@ -24430,7 +24438,7 @@
         <v>2563</v>
       </c>
     </row>
-    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>2564</v>
       </c>
@@ -24453,7 +24461,7 @@
         <v>2568</v>
       </c>
     </row>
-    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>2569</v>
       </c>
@@ -24476,7 +24484,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>2574</v>
       </c>
@@ -24502,7 +24510,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>411</v>
       </c>
@@ -24525,7 +24533,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>2585</v>
       </c>
@@ -24551,7 +24559,7 @@
         <v>2590</v>
       </c>
     </row>
-    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>2591</v>
       </c>
@@ -24577,7 +24585,7 @@
         <v>2596</v>
       </c>
     </row>
-    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>2597</v>
       </c>
@@ -24603,7 +24611,7 @@
         <v>2602</v>
       </c>
     </row>
-    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>2603</v>
       </c>
@@ -24629,7 +24637,7 @@
         <v>2608</v>
       </c>
     </row>
-    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>2609</v>
       </c>
@@ -24652,7 +24660,7 @@
         <v>2613</v>
       </c>
     </row>
-    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>2614</v>
       </c>
@@ -24678,7 +24686,7 @@
         <v>2619</v>
       </c>
     </row>
-    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>2620</v>
       </c>
@@ -24704,7 +24712,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>2625</v>
       </c>
@@ -24727,7 +24735,7 @@
         <v>2629</v>
       </c>
     </row>
-    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>2630</v>
       </c>
@@ -24753,7 +24761,7 @@
         <v>2634</v>
       </c>
     </row>
-    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>2635</v>
       </c>
@@ -24776,7 +24784,7 @@
         <v>2639</v>
       </c>
     </row>
-    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>2640</v>
       </c>
@@ -24799,7 +24807,7 @@
         <v>2644</v>
       </c>
     </row>
-    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>2645</v>
       </c>
@@ -24825,7 +24833,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>2651</v>
       </c>
@@ -24848,7 +24856,7 @@
         <v>2655</v>
       </c>
     </row>
-    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>2656</v>
       </c>
@@ -24874,7 +24882,7 @@
         <v>2661</v>
       </c>
     </row>
-    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>2662</v>
       </c>
@@ -24900,7 +24908,7 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>2667</v>
       </c>
@@ -24926,7 +24934,7 @@
         <v>2672</v>
       </c>
     </row>
-    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>2673</v>
       </c>
@@ -24949,7 +24957,7 @@
         <v>2677</v>
       </c>
     </row>
-    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>2678</v>
       </c>
@@ -24975,7 +24983,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>2684</v>
       </c>
@@ -25001,7 +25009,7 @@
         <v>2689</v>
       </c>
     </row>
-    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>479</v>
       </c>
@@ -25024,7 +25032,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>2694</v>
       </c>
@@ -25047,7 +25055,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>2699</v>
       </c>
@@ -25073,7 +25081,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>2705</v>
       </c>
@@ -25096,7 +25104,7 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>2710</v>
       </c>
@@ -25122,7 +25130,7 @@
         <v>2715</v>
       </c>
     </row>
-    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>2716</v>
       </c>
@@ -25148,7 +25156,7 @@
         <v>2721</v>
       </c>
     </row>
-    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>2722</v>
       </c>
@@ -25174,7 +25182,7 @@
         <v>2727</v>
       </c>
     </row>
-    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>2728</v>
       </c>
@@ -25197,7 +25205,7 @@
         <v>2732</v>
       </c>
     </row>
-    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>2733</v>
       </c>
@@ -25220,7 +25228,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>2738</v>
       </c>
@@ -25243,7 +25251,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>2743</v>
       </c>
@@ -25269,7 +25277,7 @@
         <v>2748</v>
       </c>
     </row>
-    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>2749</v>
       </c>
@@ -25295,7 +25303,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>2755</v>
       </c>
@@ -25347,7 +25355,7 @@
         <v>2765</v>
       </c>
     </row>
-    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>2766</v>
       </c>
@@ -25370,7 +25378,7 @@
         <v>2770</v>
       </c>
     </row>
-    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>2771</v>
       </c>
@@ -25393,7 +25401,7 @@
         <v>2775</v>
       </c>
     </row>
-    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>2776</v>
       </c>
@@ -25419,7 +25427,7 @@
         <v>2781</v>
       </c>
     </row>
-    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>2782</v>
       </c>
@@ -25442,7 +25450,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>2787</v>
       </c>
@@ -25468,7 +25476,7 @@
         <v>2792</v>
       </c>
     </row>
-    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>1011</v>
       </c>
@@ -25491,7 +25499,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>2798</v>
       </c>
@@ -25517,7 +25525,7 @@
         <v>2803</v>
       </c>
     </row>
-    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>2804</v>
       </c>
@@ -25540,7 +25548,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>2809</v>
       </c>
@@ -25566,7 +25574,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>2815</v>
       </c>
@@ -25589,7 +25597,7 @@
         <v>2819</v>
       </c>
     </row>
-    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>2820</v>
       </c>
@@ -25615,7 +25623,7 @@
         <v>2825</v>
       </c>
     </row>
-    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>2407</v>
       </c>
@@ -25638,7 +25646,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>447</v>
       </c>
@@ -25661,7 +25669,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>2836</v>
       </c>
@@ -25684,7 +25692,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>2841</v>
       </c>
@@ -25710,7 +25718,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>2847</v>
       </c>
@@ -25736,7 +25744,7 @@
         <v>2852</v>
       </c>
     </row>
-    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>2853</v>
       </c>
@@ -25762,7 +25770,7 @@
         <v>2858</v>
       </c>
     </row>
-    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>1552</v>
       </c>
@@ -25785,7 +25793,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>2864</v>
       </c>
@@ -25811,7 +25819,7 @@
         <v>2869</v>
       </c>
     </row>
-    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>2870</v>
       </c>
@@ -25834,7 +25842,7 @@
         <v>2874</v>
       </c>
     </row>
-    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>2875</v>
       </c>
@@ -25860,7 +25868,7 @@
         <v>2880</v>
       </c>
     </row>
-    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>2881</v>
       </c>
@@ -25886,7 +25894,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>2887</v>
       </c>
@@ -25909,7 +25917,7 @@
         <v>2891</v>
       </c>
     </row>
-    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>2892</v>
       </c>
@@ -25932,7 +25940,7 @@
         <v>2896</v>
       </c>
     </row>
-    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>2897</v>
       </c>
@@ -25958,7 +25966,7 @@
         <v>2902</v>
       </c>
     </row>
-    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>2903</v>
       </c>
@@ -25984,7 +25992,7 @@
         <v>2908</v>
       </c>
     </row>
-    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>2909</v>
       </c>
@@ -26010,7 +26018,7 @@
         <v>2914</v>
       </c>
     </row>
-    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>2915</v>
       </c>
@@ -26036,7 +26044,7 @@
         <v>2920</v>
       </c>
     </row>
-    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>2921</v>
       </c>
@@ -26062,7 +26070,7 @@
         <v>2926</v>
       </c>
     </row>
-    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>2927</v>
       </c>
@@ -26088,7 +26096,7 @@
         <v>2932</v>
       </c>
     </row>
-    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>2933</v>
       </c>
@@ -26111,7 +26119,7 @@
         <v>2937</v>
       </c>
     </row>
-    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>2938</v>
       </c>
@@ -26137,7 +26145,7 @@
         <v>2943</v>
       </c>
     </row>
-    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>2944</v>
       </c>
@@ -26160,7 +26168,7 @@
         <v>2948</v>
       </c>
     </row>
-    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>1563</v>
       </c>
@@ -26183,7 +26191,7 @@
         <v>1567</v>
       </c>
     </row>
-    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>2949</v>
       </c>
@@ -26209,7 +26217,7 @@
         <v>2953</v>
       </c>
     </row>
-    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>2954</v>
       </c>
@@ -26235,7 +26243,7 @@
         <v>2959</v>
       </c>
     </row>
-    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>2960</v>
       </c>
@@ -26261,7 +26269,7 @@
         <v>2965</v>
       </c>
     </row>
-    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>2966</v>
       </c>
@@ -26284,7 +26292,7 @@
         <v>2970</v>
       </c>
     </row>
-    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>2971</v>
       </c>
@@ -26310,7 +26318,7 @@
         <v>2976</v>
       </c>
     </row>
-    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>2977</v>
       </c>
@@ -26336,7 +26344,7 @@
         <v>2982</v>
       </c>
     </row>
-    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>2983</v>
       </c>
@@ -26362,7 +26370,7 @@
         <v>2988</v>
       </c>
     </row>
-    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>2989</v>
       </c>
@@ -26388,7 +26396,7 @@
         <v>2994</v>
       </c>
     </row>
-    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>2995</v>
       </c>
@@ -26411,7 +26419,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>3000</v>
       </c>
@@ -26437,7 +26445,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>3006</v>
       </c>
@@ -26460,7 +26468,7 @@
         <v>3010</v>
       </c>
     </row>
-    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>3011</v>
       </c>
@@ -26486,7 +26494,7 @@
         <v>3016</v>
       </c>
     </row>
-    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>915</v>
       </c>
@@ -26509,7 +26517,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>3022</v>
       </c>
@@ -26532,7 +26540,7 @@
         <v>3026</v>
       </c>
     </row>
-    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>3027</v>
       </c>
@@ -26558,7 +26566,7 @@
         <v>3032</v>
       </c>
     </row>
-    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>3033</v>
       </c>
@@ -26581,7 +26589,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>3038</v>
       </c>
@@ -26607,7 +26615,7 @@
         <v>3043</v>
       </c>
     </row>
-    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>3044</v>
       </c>
@@ -26633,7 +26641,7 @@
         <v>3049</v>
       </c>
     </row>
-    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>3050</v>
       </c>
@@ -26656,7 +26664,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>3055</v>
       </c>
@@ -26682,7 +26690,7 @@
         <v>3060</v>
       </c>
     </row>
-    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>3061</v>
       </c>
@@ -26708,7 +26716,7 @@
         <v>3066</v>
       </c>
     </row>
-    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>3067</v>
       </c>
@@ -26734,7 +26742,7 @@
         <v>3072</v>
       </c>
     </row>
-    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>2227</v>
       </c>
@@ -26757,7 +26765,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>3073</v>
       </c>
@@ -26780,7 +26788,7 @@
         <v>3077</v>
       </c>
     </row>
-    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>3078</v>
       </c>
@@ -26806,7 +26814,7 @@
         <v>3083</v>
       </c>
     </row>
-    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>3084</v>
       </c>
@@ -26858,7 +26866,7 @@
         <v>3094</v>
       </c>
     </row>
-    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>3095</v>
       </c>
@@ -26884,7 +26892,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>3101</v>
       </c>
@@ -26907,7 +26915,7 @@
         <v>3105</v>
       </c>
     </row>
-    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>3106</v>
       </c>
@@ -26933,7 +26941,7 @@
         <v>3111</v>
       </c>
     </row>
-    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>3112</v>
       </c>
@@ -26959,7 +26967,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>3118</v>
       </c>
@@ -27011,7 +27019,7 @@
         <v>3128</v>
       </c>
     </row>
-    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>3129</v>
       </c>
@@ -27037,7 +27045,7 @@
         <v>3134</v>
       </c>
     </row>
-    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>3135</v>
       </c>
@@ -27063,7 +27071,7 @@
         <v>3140</v>
       </c>
     </row>
-    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>3141</v>
       </c>
@@ -27086,7 +27094,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>3146</v>
       </c>
@@ -27112,7 +27120,7 @@
         <v>3151</v>
       </c>
     </row>
-    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>3152</v>
       </c>
@@ -27138,7 +27146,7 @@
         <v>3157</v>
       </c>
     </row>
-    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>3158</v>
       </c>
@@ -27164,7 +27172,7 @@
         <v>3163</v>
       </c>
     </row>
-    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>3164</v>
       </c>
@@ -27190,7 +27198,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>3170</v>
       </c>
@@ -27216,7 +27224,7 @@
         <v>3175</v>
       </c>
     </row>
-    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>3176</v>
       </c>
@@ -27239,7 +27247,7 @@
         <v>3180</v>
       </c>
     </row>
-    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>3181</v>
       </c>
@@ -27262,7 +27270,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>3186</v>
       </c>
@@ -27288,7 +27296,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>3192</v>
       </c>
@@ -27314,7 +27322,7 @@
         <v>3197</v>
       </c>
     </row>
-    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>3198</v>
       </c>
@@ -27337,7 +27345,7 @@
         <v>3202</v>
       </c>
     </row>
-    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>3203</v>
       </c>
@@ -27360,7 +27368,7 @@
         <v>3207</v>
       </c>
     </row>
-    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>3208</v>
       </c>
@@ -27383,7 +27391,7 @@
         <v>3212</v>
       </c>
     </row>
-    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>3213</v>
       </c>
@@ -27406,7 +27414,7 @@
         <v>3217</v>
       </c>
     </row>
-    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>3218</v>
       </c>
@@ -27429,7 +27437,7 @@
         <v>3222</v>
       </c>
     </row>
-    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>3223</v>
       </c>
@@ -27452,7 +27460,7 @@
         <v>3227</v>
       </c>
     </row>
-    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>3228</v>
       </c>
@@ -27475,7 +27483,7 @@
         <v>3232</v>
       </c>
     </row>
-    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>3233</v>
       </c>
@@ -27498,7 +27506,7 @@
         <v>3237</v>
       </c>
     </row>
-    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>3238</v>
       </c>
@@ -27521,7 +27529,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>3243</v>
       </c>
@@ -27544,7 +27552,7 @@
         <v>3247</v>
       </c>
     </row>
-    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>3248</v>
       </c>
@@ -27570,7 +27578,7 @@
         <v>3253</v>
       </c>
     </row>
-    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>3254</v>
       </c>
@@ -27593,7 +27601,7 @@
         <v>3258</v>
       </c>
     </row>
-    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>3259</v>
       </c>
@@ -27616,7 +27624,7 @@
         <v>3263</v>
       </c>
     </row>
-    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>3264</v>
       </c>
@@ -27639,7 +27647,7 @@
         <v>3268</v>
       </c>
     </row>
-    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>3269</v>
       </c>
@@ -27662,7 +27670,7 @@
         <v>3273</v>
       </c>
     </row>
-    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>3274</v>
       </c>
@@ -27685,7 +27693,7 @@
         <v>3278</v>
       </c>
     </row>
-    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>3279</v>
       </c>
@@ -27711,7 +27719,7 @@
         <v>3284</v>
       </c>
     </row>
-    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>3285</v>
       </c>
@@ -27734,7 +27742,7 @@
         <v>3289</v>
       </c>
     </row>
-    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>3290</v>
       </c>
@@ -27757,7 +27765,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>2859</v>
       </c>
@@ -27780,7 +27788,7 @@
         <v>2863</v>
       </c>
     </row>
-    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>3295</v>
       </c>
@@ -27803,7 +27811,7 @@
         <v>3299</v>
       </c>
     </row>
-    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>3300</v>
       </c>
@@ -27826,7 +27834,7 @@
         <v>3304</v>
       </c>
     </row>
-    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>3305</v>
       </c>
@@ -27852,7 +27860,7 @@
         <v>3310</v>
       </c>
     </row>
-    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>3311</v>
       </c>
@@ -27878,7 +27886,7 @@
         <v>3316</v>
       </c>
     </row>
-    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>3317</v>
       </c>
@@ -27904,7 +27912,7 @@
         <v>3322</v>
       </c>
     </row>
-    <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>3323</v>
       </c>
@@ -27930,7 +27938,7 @@
         <v>3328</v>
       </c>
     </row>
-    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>3329</v>
       </c>
@@ -27956,7 +27964,7 @@
         <v>3334</v>
       </c>
     </row>
-    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>3335</v>
       </c>
@@ -27982,7 +27990,7 @@
         <v>3340</v>
       </c>
     </row>
-    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>3341</v>
       </c>
@@ -28008,7 +28016,7 @@
         <v>3346</v>
       </c>
     </row>
-    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>3347</v>
       </c>
@@ -28031,7 +28039,7 @@
         <v>3351</v>
       </c>
     </row>
-    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>3352</v>
       </c>
@@ -28054,7 +28062,7 @@
         <v>3356</v>
       </c>
     </row>
-    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>3357</v>
       </c>
@@ -28080,7 +28088,7 @@
         <v>3362</v>
       </c>
     </row>
-    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>3363</v>
       </c>
@@ -28103,7 +28111,7 @@
         <v>3367</v>
       </c>
     </row>
-    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>3368</v>
       </c>
@@ -28126,7 +28134,7 @@
         <v>3372</v>
       </c>
     </row>
-    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>3373</v>
       </c>
@@ -28152,7 +28160,7 @@
         <v>3378</v>
       </c>
     </row>
-    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>3379</v>
       </c>
@@ -28178,7 +28186,7 @@
         <v>3384</v>
       </c>
     </row>
-    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>3385</v>
       </c>
@@ -28204,7 +28212,7 @@
         <v>3390</v>
       </c>
     </row>
-    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>3391</v>
       </c>
@@ -28230,7 +28238,7 @@
         <v>3396</v>
       </c>
     </row>
-    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>3397</v>
       </c>
@@ -28253,7 +28261,7 @@
         <v>3401</v>
       </c>
     </row>
-    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>3402</v>
       </c>
@@ -28279,7 +28287,7 @@
         <v>3407</v>
       </c>
     </row>
-    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>3408</v>
       </c>
@@ -28302,7 +28310,7 @@
         <v>3412</v>
       </c>
     </row>
-    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>3413</v>
       </c>
@@ -28325,7 +28333,7 @@
         <v>3417</v>
       </c>
     </row>
-    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>3418</v>
       </c>
@@ -28351,7 +28359,7 @@
         <v>3423</v>
       </c>
     </row>
-    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>3424</v>
       </c>
@@ -28377,7 +28385,7 @@
         <v>3429</v>
       </c>
     </row>
-    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>3430</v>
       </c>
@@ -28403,7 +28411,7 @@
         <v>3435</v>
       </c>
     </row>
-    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>3436</v>
       </c>
@@ -28426,7 +28434,7 @@
         <v>3440</v>
       </c>
     </row>
-    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>3441</v>
       </c>
@@ -28452,7 +28460,7 @@
         <v>3446</v>
       </c>
     </row>
-    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>3447</v>
       </c>
@@ -28478,7 +28486,7 @@
         <v>3452</v>
       </c>
     </row>
-    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>3453</v>
       </c>
@@ -28504,7 +28512,7 @@
         <v>3458</v>
       </c>
     </row>
-    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>3459</v>
       </c>
@@ -28530,7 +28538,7 @@
         <v>3464</v>
       </c>
     </row>
-    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>3465</v>
       </c>
@@ -28556,7 +28564,7 @@
         <v>3470</v>
       </c>
     </row>
-    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>3471</v>
       </c>
@@ -28582,7 +28590,7 @@
         <v>3476</v>
       </c>
     </row>
-    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>3477</v>
       </c>
@@ -28608,7 +28616,7 @@
         <v>3482</v>
       </c>
     </row>
-    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>3483</v>
       </c>
@@ -28634,7 +28642,7 @@
         <v>3488</v>
       </c>
     </row>
-    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>3489</v>
       </c>
@@ -28660,7 +28668,7 @@
         <v>3494</v>
       </c>
     </row>
-    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>3495</v>
       </c>
@@ -28686,7 +28694,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>3501</v>
       </c>
@@ -28712,7 +28720,7 @@
         <v>3506</v>
       </c>
     </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>3507</v>
       </c>
@@ -28738,7 +28746,7 @@
         <v>3512</v>
       </c>
     </row>
-    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>3513</v>
       </c>
@@ -28761,7 +28769,7 @@
         <v>3517</v>
       </c>
     </row>
-    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>3518</v>
       </c>
@@ -28784,7 +28792,7 @@
         <v>3522</v>
       </c>
     </row>
-    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>3523</v>
       </c>
@@ -28810,7 +28818,7 @@
         <v>3528</v>
       </c>
     </row>
-    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>3529</v>
       </c>
@@ -28836,7 +28844,7 @@
         <v>3534</v>
       </c>
     </row>
-    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>3535</v>
       </c>
@@ -28859,7 +28867,7 @@
         <v>3539</v>
       </c>
     </row>
-    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>3540</v>
       </c>
@@ -28885,7 +28893,7 @@
         <v>3545</v>
       </c>
     </row>
-    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>3546</v>
       </c>
@@ -28911,7 +28919,7 @@
         <v>3551</v>
       </c>
     </row>
-    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>3552</v>
       </c>
@@ -28934,7 +28942,7 @@
         <v>3556</v>
       </c>
     </row>
-    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>3557</v>
       </c>
@@ -28960,7 +28968,7 @@
         <v>3562</v>
       </c>
     </row>
-    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>3563</v>
       </c>
@@ -28986,7 +28994,7 @@
         <v>3568</v>
       </c>
     </row>
-    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>3569</v>
       </c>
@@ -29012,7 +29020,7 @@
         <v>3574</v>
       </c>
     </row>
-    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>3575</v>
       </c>
@@ -29035,7 +29043,7 @@
         <v>3579</v>
       </c>
     </row>
-    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>3580</v>
       </c>
@@ -29061,7 +29069,7 @@
         <v>3585</v>
       </c>
     </row>
-    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>3586</v>
       </c>
@@ -29087,7 +29095,7 @@
         <v>3591</v>
       </c>
     </row>
-    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>3592</v>
       </c>
@@ -29110,7 +29118,7 @@
         <v>3596</v>
       </c>
     </row>
-    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>3597</v>
       </c>
@@ -29133,7 +29141,7 @@
         <v>3601</v>
       </c>
     </row>
-    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>3602</v>
       </c>
@@ -29159,7 +29167,7 @@
         <v>3607</v>
       </c>
     </row>
-    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>3608</v>
       </c>
@@ -29185,7 +29193,7 @@
         <v>3613</v>
       </c>
     </row>
-    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>3614</v>
       </c>
@@ -29211,7 +29219,7 @@
         <v>3619</v>
       </c>
     </row>
-    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>3620</v>
       </c>
@@ -29237,7 +29245,7 @@
         <v>3625</v>
       </c>
     </row>
-    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>3626</v>
       </c>
@@ -29263,7 +29271,7 @@
         <v>3631</v>
       </c>
     </row>
-    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>3632</v>
       </c>
@@ -29289,7 +29297,7 @@
         <v>3637</v>
       </c>
     </row>
-    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>3638</v>
       </c>
@@ -29315,7 +29323,7 @@
         <v>3643</v>
       </c>
     </row>
-    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>3644</v>
       </c>
@@ -29341,7 +29349,7 @@
         <v>3649</v>
       </c>
     </row>
-    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>3650</v>
       </c>
@@ -29367,7 +29375,7 @@
         <v>3655</v>
       </c>
     </row>
-    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>3656</v>
       </c>
@@ -29393,7 +29401,7 @@
         <v>3661</v>
       </c>
     </row>
-    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>3662</v>
       </c>
@@ -29419,7 +29427,7 @@
         <v>3667</v>
       </c>
     </row>
-    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>3668</v>
       </c>
@@ -29442,7 +29450,7 @@
         <v>3672</v>
       </c>
     </row>
-    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>3673</v>
       </c>
@@ -29468,7 +29476,7 @@
         <v>3678</v>
       </c>
     </row>
-    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>3679</v>
       </c>
@@ -29491,7 +29499,7 @@
         <v>3683</v>
       </c>
     </row>
-    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>3684</v>
       </c>
@@ -29514,7 +29522,7 @@
         <v>3688</v>
       </c>
     </row>
-    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>3689</v>
       </c>
@@ -29540,7 +29548,7 @@
         <v>3694</v>
       </c>
     </row>
-    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>3695</v>
       </c>
@@ -29566,7 +29574,7 @@
         <v>3700</v>
       </c>
     </row>
-    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>3701</v>
       </c>
@@ -29592,7 +29600,7 @@
         <v>3706</v>
       </c>
     </row>
-    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>3707</v>
       </c>
@@ -29618,7 +29626,7 @@
         <v>3712</v>
       </c>
     </row>
-    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>3713</v>
       </c>
@@ -29644,7 +29652,7 @@
         <v>3718</v>
       </c>
     </row>
-    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>3719</v>
       </c>
@@ -29670,7 +29678,7 @@
         <v>3724</v>
       </c>
     </row>
-    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>3725</v>
       </c>
@@ -29696,7 +29704,7 @@
         <v>3730</v>
       </c>
     </row>
-    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>3731</v>
       </c>
@@ -29722,7 +29730,7 @@
         <v>3736</v>
       </c>
     </row>
-    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>3737</v>
       </c>
@@ -29748,7 +29756,7 @@
         <v>3742</v>
       </c>
     </row>
-    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>3743</v>
       </c>
@@ -29774,7 +29782,7 @@
         <v>3748</v>
       </c>
     </row>
-    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>3749</v>
       </c>
@@ -29800,7 +29808,7 @@
         <v>3754</v>
       </c>
     </row>
-    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>3755</v>
       </c>
@@ -29826,7 +29834,7 @@
         <v>3760</v>
       </c>
     </row>
-    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>3761</v>
       </c>
@@ -29852,7 +29860,7 @@
         <v>3766</v>
       </c>
     </row>
-    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>3767</v>
       </c>
@@ -29878,7 +29886,7 @@
         <v>3772</v>
       </c>
     </row>
-    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>3773</v>
       </c>
@@ -29904,7 +29912,7 @@
         <v>3778</v>
       </c>
     </row>
-    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>3779</v>
       </c>
@@ -29927,7 +29935,7 @@
         <v>3783</v>
       </c>
     </row>
-    <row r="690" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>3784</v>
       </c>
@@ -29953,7 +29961,7 @@
         <v>3789</v>
       </c>
     </row>
-    <row r="691" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>3790</v>
       </c>
@@ -29976,7 +29984,7 @@
         <v>3794</v>
       </c>
     </row>
-    <row r="692" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>3795</v>
       </c>
@@ -29999,7 +30007,7 @@
         <v>3799</v>
       </c>
     </row>
-    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>3800</v>
       </c>
@@ -30022,7 +30030,7 @@
         <v>3804</v>
       </c>
     </row>
-    <row r="694" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>3805</v>
       </c>
@@ -30045,7 +30053,7 @@
         <v>3809</v>
       </c>
     </row>
-    <row r="695" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>3810</v>
       </c>
@@ -30068,7 +30076,7 @@
         <v>3814</v>
       </c>
     </row>
-    <row r="696" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>3815</v>
       </c>
@@ -30091,7 +30099,7 @@
         <v>3819</v>
       </c>
     </row>
-    <row r="697" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>3820</v>
       </c>
@@ -30114,7 +30122,7 @@
         <v>3824</v>
       </c>
     </row>
-    <row r="698" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>3825</v>
       </c>
@@ -30137,7 +30145,7 @@
         <v>3829</v>
       </c>
     </row>
-    <row r="699" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>3830</v>
       </c>
@@ -30160,7 +30168,7 @@
         <v>3834</v>
       </c>
     </row>
-    <row r="700" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>3835</v>
       </c>
@@ -30183,7 +30191,7 @@
         <v>3839</v>
       </c>
     </row>
-    <row r="701" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>3840</v>
       </c>
@@ -30206,7 +30214,7 @@
         <v>3844</v>
       </c>
     </row>
-    <row r="702" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>3845</v>
       </c>
@@ -30229,7 +30237,7 @@
         <v>3849</v>
       </c>
     </row>
-    <row r="703" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>3850</v>
       </c>
@@ -30252,7 +30260,7 @@
         <v>3854</v>
       </c>
     </row>
-    <row r="704" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>3855</v>
       </c>
@@ -30275,7 +30283,7 @@
         <v>3859</v>
       </c>
     </row>
-    <row r="705" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>3860</v>
       </c>
@@ -30298,7 +30306,7 @@
         <v>3864</v>
       </c>
     </row>
-    <row r="706" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>3865</v>
       </c>
@@ -30321,7 +30329,7 @@
         <v>3869</v>
       </c>
     </row>
-    <row r="707" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>3870</v>
       </c>
@@ -30344,7 +30352,7 @@
         <v>3874</v>
       </c>
     </row>
-    <row r="708" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>3875</v>
       </c>
@@ -30367,7 +30375,7 @@
         <v>3879</v>
       </c>
     </row>
-    <row r="709" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>3880</v>
       </c>
@@ -30390,7 +30398,7 @@
         <v>3884</v>
       </c>
     </row>
-    <row r="710" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>3885</v>
       </c>
@@ -30416,7 +30424,7 @@
         <v>3890</v>
       </c>
     </row>
-    <row r="711" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>3891</v>
       </c>
@@ -30442,7 +30450,7 @@
         <v>3896</v>
       </c>
     </row>
-    <row r="712" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>3897</v>
       </c>
@@ -30468,7 +30476,7 @@
         <v>3902</v>
       </c>
     </row>
-    <row r="713" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>3903</v>
       </c>
@@ -30494,7 +30502,7 @@
         <v>3908</v>
       </c>
     </row>
-    <row r="714" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>3909</v>
       </c>
@@ -30520,7 +30528,7 @@
         <v>3914</v>
       </c>
     </row>
-    <row r="715" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>3915</v>
       </c>
@@ -30546,7 +30554,7 @@
         <v>3920</v>
       </c>
     </row>
-    <row r="716" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>3921</v>
       </c>
@@ -30572,7 +30580,7 @@
         <v>3926</v>
       </c>
     </row>
-    <row r="717" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>3927</v>
       </c>
@@ -30598,7 +30606,7 @@
         <v>3932</v>
       </c>
     </row>
-    <row r="718" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>3933</v>
       </c>
@@ -30624,7 +30632,7 @@
         <v>3938</v>
       </c>
     </row>
-    <row r="719" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>3939</v>
       </c>
@@ -30650,7 +30658,7 @@
         <v>3944</v>
       </c>
     </row>
-    <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>1409</v>
       </c>
@@ -30673,7 +30681,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="721" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>3950</v>
       </c>
@@ -30699,7 +30707,7 @@
         <v>3955</v>
       </c>
     </row>
-    <row r="722" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>3956</v>
       </c>
@@ -30725,7 +30733,7 @@
         <v>3961</v>
       </c>
     </row>
-    <row r="723" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>3962</v>
       </c>
@@ -30751,7 +30759,7 @@
         <v>3967</v>
       </c>
     </row>
-    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>3968</v>
       </c>
@@ -30777,7 +30785,7 @@
         <v>3973</v>
       </c>
     </row>
-    <row r="725" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>76</v>
       </c>
@@ -30800,7 +30808,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="726" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>86</v>
       </c>
@@ -30823,7 +30831,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>3974</v>
       </c>
@@ -30849,7 +30857,7 @@
         <v>3979</v>
       </c>
     </row>
-    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>3990</v>
       </c>
@@ -30875,7 +30883,7 @@
         <v>3995</v>
       </c>
     </row>
-    <row r="729" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>3996</v>
       </c>
@@ -30901,7 +30909,7 @@
         <v>4001</v>
       </c>
     </row>
-    <row r="730" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>4002</v>
       </c>
@@ -30927,7 +30935,7 @@
         <v>4007</v>
       </c>
     </row>
-    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>4008</v>
       </c>
@@ -30953,7 +30961,7 @@
         <v>4013</v>
       </c>
     </row>
-    <row r="732" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>4014</v>
       </c>
@@ -30979,7 +30987,7 @@
         <v>4019</v>
       </c>
     </row>
-    <row r="733" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>4020</v>
       </c>
@@ -31005,7 +31013,7 @@
         <v>4025</v>
       </c>
     </row>
-    <row r="734" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>4026</v>
       </c>
@@ -31031,7 +31039,7 @@
         <v>4031</v>
       </c>
     </row>
-    <row r="735" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>4032</v>
       </c>
@@ -31057,7 +31065,7 @@
         <v>4037</v>
       </c>
     </row>
-    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>4038</v>
       </c>
@@ -31083,7 +31091,7 @@
         <v>4043</v>
       </c>
     </row>
-    <row r="737" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>4044</v>
       </c>
@@ -31109,7 +31117,7 @@
         <v>4049</v>
       </c>
     </row>
-    <row r="738" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>4050</v>
       </c>
@@ -31135,7 +31143,7 @@
         <v>4055</v>
       </c>
     </row>
-    <row r="739" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>4056</v>
       </c>
@@ -31161,7 +31169,7 @@
         <v>4061</v>
       </c>
     </row>
-    <row r="740" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>4062</v>
       </c>
@@ -31187,7 +31195,7 @@
         <v>4067</v>
       </c>
     </row>
-    <row r="741" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>4068</v>
       </c>
@@ -31213,7 +31221,7 @@
         <v>4073</v>
       </c>
     </row>
-    <row r="742" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>4074</v>
       </c>
@@ -31239,7 +31247,7 @@
         <v>4078</v>
       </c>
     </row>
-    <row r="743" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>4079</v>
       </c>
@@ -31265,7 +31273,7 @@
         <v>4083</v>
       </c>
     </row>
-    <row r="744" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>4084</v>
       </c>
@@ -31291,7 +31299,7 @@
         <v>4088</v>
       </c>
     </row>
-    <row r="745" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>4089</v>
       </c>
@@ -31317,7 +31325,7 @@
         <v>4094</v>
       </c>
     </row>
-    <row r="746" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>4095</v>
       </c>
@@ -31345,17 +31353,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I746" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Maps"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="SlateportCity"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I746">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:I746">
       <sortCondition descending="1" ref="E1:E746"/>
     </sortState>
   </autoFilter>

--- a/translation_dashboard.xlsx
+++ b/translation_dashboard.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -2225,7 +2225,7 @@
     <t>SlateportCity</t>
   </si>
   <si>
-    <t>Onvertaald</t>
+    <t>Vertaald</t>
   </si>
   <si>
     <t>Hoog</t>
@@ -12242,9 +12242,6 @@
     <t>NavelRock</t>
   </si>
   <si>
-    <t>Vertaald</t>
-  </si>
-  <si>
     <t>Laag</t>
   </si>
   <si>
@@ -12330,6 +12327,9 @@
   </si>
   <si>
     <t>Tekens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tekens van Maps</t>
   </si>
   <si>
     <t xml:space="preserve">Onvertaalde tekens</t>
@@ -12348,7 +12348,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.000000"/>
       <name val="Calibri"/>
@@ -12365,6 +12365,11 @@
       <sz val="11.000000"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.000000"/>
+      <color indexed="64"/>
+      <name val="Courier New"/>
     </font>
     <font>
       <sz val="12.000000"/>
@@ -12401,14 +12406,21 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="10" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="10" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="9" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Procent" xfId="1" builtinId="5"/>
@@ -12676,8 +12688,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0">
-      <a:off x="0" y="0"/>
-      <a:ext cx="0" cy="0"/>
+      <a:off x="152398" y="1247775"/>
+      <a:ext cx="3689349" cy="2006598"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -12720,20 +12732,837 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent>
+    <mc:Choice Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" spc="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout/>
+      </c:layout>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Tekens van Maps</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr bwMode="auto">
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$G$2:$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Vertaald</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Onvertaald</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$H$2:$H$3</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>670891</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1428345</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="75"/>
+      </c:doughnutChart>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr bwMode="auto">
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr bwMode="auto">
+    <a:xfrm rot="0" flipH="0" flipV="0">
+      <a:off x="3962399" y="1162050"/>
+      <a:ext cx="5114925" cy="2501899"/>
+    </a:xfrm>
+    <a:prstGeom prst="rect">
+      <a:avLst/>
+    </a:prstGeom>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="900">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" spc="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr bwMode="auto">
+      <a:prstGeom prst="rect">
+        <a:avLst/>
+      </a:prstGeom>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>530224</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>152398</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>136525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>530224</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>6349</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>44448</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -12743,12 +13572,44 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0">
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="152398" y="1247775"/>
+        <a:ext cx="3689349" cy="2006598"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>165099</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>422274</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>63499</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="366890496" name=""/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm rot="0" flipH="0" flipV="0">
+        <a:off x="3962399" y="1162050"/>
+        <a:ext cx="5114925" cy="2501899"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -13312,7 +14173,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="1">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -13413,7 +14274,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="1">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -13485,7 +14346,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="1">
       <c r="A12" t="s">
         <v>59</v>
       </c>
@@ -13557,7 +14418,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="1">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -13649,7 +14510,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="19" hidden="1">
+    <row r="19">
       <c r="A19" t="s">
         <v>93</v>
       </c>
@@ -13770,7 +14631,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" hidden="1">
+    <row r="24">
       <c r="A24" t="s">
         <v>119</v>
       </c>
@@ -13796,7 +14657,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="1">
       <c r="A25" t="s">
         <v>125</v>
       </c>
@@ -13937,7 +14798,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="31" hidden="1">
+    <row r="31">
       <c r="A31" t="s">
         <v>156</v>
       </c>
@@ -14035,7 +14896,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="35" hidden="1">
+    <row r="35">
       <c r="A35" t="s">
         <v>177</v>
       </c>
@@ -14061,7 +14922,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="1">
       <c r="A36" t="s">
         <v>183</v>
       </c>
@@ -14084,7 +14945,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="1">
       <c r="A37" t="s">
         <v>188</v>
       </c>
@@ -14107,7 +14968,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" hidden="1">
+    <row r="38">
       <c r="A38" t="s">
         <v>193</v>
       </c>
@@ -14156,7 +15017,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" hidden="1">
+    <row r="40">
       <c r="A40" t="s">
         <v>204</v>
       </c>
@@ -14205,7 +15066,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" hidden="1">
+    <row r="42">
       <c r="A42" t="s">
         <v>215</v>
       </c>
@@ -14231,7 +15092,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="43" hidden="1">
+    <row r="43">
       <c r="A43" t="s">
         <v>221</v>
       </c>
@@ -14349,7 +15210,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="1">
       <c r="A48" t="s">
         <v>247</v>
       </c>
@@ -14421,7 +15282,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="51" hidden="1">
+    <row r="51">
       <c r="A51" t="s">
         <v>263</v>
       </c>
@@ -14447,7 +15308,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="52" hidden="1">
+    <row r="52">
       <c r="A52" t="s">
         <v>269</v>
       </c>
@@ -14473,7 +15334,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="53" hidden="1">
+    <row r="53">
       <c r="A53" t="s">
         <v>275</v>
       </c>
@@ -14545,7 +15406,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="1">
       <c r="A56" t="s">
         <v>291</v>
       </c>
@@ -14591,7 +15452,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="1">
       <c r="A58" t="s">
         <v>301</v>
       </c>
@@ -14775,7 +15636,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="66" hidden="1">
+    <row r="66">
       <c r="A66" t="s">
         <v>341</v>
       </c>
@@ -14801,7 +15662,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="67" hidden="1">
+    <row r="67">
       <c r="A67" t="s">
         <v>347</v>
       </c>
@@ -14919,7 +15780,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="1">
       <c r="A72" t="s">
         <v>373</v>
       </c>
@@ -14942,7 +15803,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="73" hidden="1">
+    <row r="73">
       <c r="A73" t="s">
         <v>378</v>
       </c>
@@ -14991,7 +15852,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="1">
       <c r="A75" t="s">
         <v>389</v>
       </c>
@@ -15106,7 +15967,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="1">
       <c r="A80" t="s">
         <v>414</v>
       </c>
@@ -15152,7 +16013,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="82" hidden="1">
+    <row r="82">
       <c r="A82" t="s">
         <v>424</v>
       </c>
@@ -15224,7 +16085,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="1">
       <c r="A85" t="s">
         <v>440</v>
       </c>
@@ -15247,7 +16108,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="86" hidden="1">
+    <row r="86">
       <c r="A86" t="s">
         <v>445</v>
       </c>
@@ -15296,7 +16157,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="1">
       <c r="A88" t="s">
         <v>456</v>
       </c>
@@ -15319,7 +16180,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="89" hidden="1">
+    <row r="89">
       <c r="A89" t="s">
         <v>461</v>
       </c>
@@ -15414,7 +16275,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="93" hidden="1">
+    <row r="93">
       <c r="A93" t="s">
         <v>482</v>
       </c>
@@ -15509,7 +16370,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="97" hidden="1">
+    <row r="97">
       <c r="A97" t="s">
         <v>503</v>
       </c>
@@ -15581,7 +16442,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="100" hidden="1">
+    <row r="100">
       <c r="A100" t="s">
         <v>519</v>
       </c>
@@ -15607,7 +16468,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="101" hidden="1">
+    <row r="101">
       <c r="A101" t="s">
         <v>525</v>
       </c>
@@ -15702,7 +16563,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="105" hidden="1">
+    <row r="105">
       <c r="A105" t="s">
         <v>546</v>
       </c>
@@ -15728,7 +16589,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="106" hidden="1">
+    <row r="106">
       <c r="A106" t="s">
         <v>552</v>
       </c>
@@ -15800,7 +16661,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="109" hidden="1">
+    <row r="109">
       <c r="A109" t="s">
         <v>568</v>
       </c>
@@ -15826,7 +16687,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="110" hidden="1">
+    <row r="110">
       <c r="A110" t="s">
         <v>574</v>
       </c>
@@ -15852,7 +16713,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="111" hidden="1">
+    <row r="111">
       <c r="A111" t="s">
         <v>579</v>
       </c>
@@ -15901,7 +16762,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="1">
       <c r="A113" t="s">
         <v>590</v>
       </c>
@@ -15947,7 +16808,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="1">
       <c r="A115" t="s">
         <v>600</v>
       </c>
@@ -15993,7 +16854,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="117" hidden="1">
+    <row r="117">
       <c r="A117" t="s">
         <v>610</v>
       </c>
@@ -16042,7 +16903,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="119" hidden="1">
+    <row r="119">
       <c r="A119" t="s">
         <v>621</v>
       </c>
@@ -16091,7 +16952,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="121" hidden="1">
+    <row r="121">
       <c r="A121" t="s">
         <v>632</v>
       </c>
@@ -16163,7 +17024,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="124" hidden="1">
+    <row r="124">
       <c r="A124" t="s">
         <v>648</v>
       </c>
@@ -16189,7 +17050,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="125" hidden="1">
+    <row r="125">
       <c r="A125" t="s">
         <v>654</v>
       </c>
@@ -16307,7 +17168,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="130" hidden="1">
+    <row r="130">
       <c r="A130" t="s">
         <v>680</v>
       </c>
@@ -16356,7 +17217,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="132" hidden="1">
+    <row r="132">
       <c r="A132" t="s">
         <v>691</v>
       </c>
@@ -16382,7 +17243,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="133" hidden="1">
+    <row r="133">
       <c r="A133" t="s">
         <v>697</v>
       </c>
@@ -16408,7 +17269,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="134" hidden="1">
+    <row r="134">
       <c r="A134" t="s">
         <v>703</v>
       </c>
@@ -16457,7 +17318,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="1">
       <c r="A136" t="s">
         <v>714</v>
       </c>
@@ -16480,7 +17341,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="137" hidden="1">
+    <row r="137">
       <c r="A137" t="s">
         <v>719</v>
       </c>
@@ -16506,7 +17367,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="138" hidden="1">
+    <row r="138">
       <c r="A138" t="s">
         <v>725</v>
       </c>
@@ -16558,7 +17419,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="140" hidden="1">
+    <row r="140">
       <c r="A140" t="s">
         <v>736</v>
       </c>
@@ -16584,7 +17445,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="141" hidden="1">
+    <row r="141">
       <c r="A141" t="s">
         <v>742</v>
       </c>
@@ -16633,7 +17494,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="1">
       <c r="A143" t="s">
         <v>753</v>
       </c>
@@ -16656,7 +17517,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="144" hidden="1">
+    <row r="144">
       <c r="A144" t="s">
         <v>758</v>
       </c>
@@ -16682,7 +17543,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="145" hidden="1">
+    <row r="145">
       <c r="A145" t="s">
         <v>763</v>
       </c>
@@ -16777,7 +17638,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="149" hidden="1">
+    <row r="149">
       <c r="A149" t="s">
         <v>784</v>
       </c>
@@ -16849,7 +17710,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="152" hidden="1">
+    <row r="152">
       <c r="A152" t="s">
         <v>800</v>
       </c>
@@ -16898,7 +17759,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="154" hidden="1">
+    <row r="154">
       <c r="A154" t="s">
         <v>811</v>
       </c>
@@ -16924,7 +17785,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="155" hidden="1">
+    <row r="155">
       <c r="A155" t="s">
         <v>817</v>
       </c>
@@ -16950,7 +17811,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="156" hidden="1">
+    <row r="156">
       <c r="A156" t="s">
         <v>823</v>
       </c>
@@ -17137,7 +17998,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="164" hidden="1">
+    <row r="164">
       <c r="A164" t="s">
         <v>864</v>
       </c>
@@ -17186,7 +18047,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="166" hidden="1">
+    <row r="166">
       <c r="A166" t="s">
         <v>875</v>
       </c>
@@ -17212,7 +18073,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="167" hidden="1">
+    <row r="167">
       <c r="A167" t="s">
         <v>881</v>
       </c>
@@ -17261,7 +18122,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="169" hidden="1">
+    <row r="169">
       <c r="A169" t="s">
         <v>892</v>
       </c>
@@ -17402,7 +18263,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="175" hidden="1">
+    <row r="175">
       <c r="A175" t="s">
         <v>923</v>
       </c>
@@ -17451,7 +18312,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="177" hidden="1">
+    <row r="177">
       <c r="A177" t="s">
         <v>934</v>
       </c>
@@ -17500,7 +18361,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="179" hidden="1">
+    <row r="179">
       <c r="A179" t="s">
         <v>945</v>
       </c>
@@ -17549,7 +18410,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="1">
       <c r="A181" t="s">
         <v>956</v>
       </c>
@@ -17595,7 +18456,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="183" hidden="1">
+    <row r="183">
       <c r="A183" t="s">
         <v>966</v>
       </c>
@@ -17644,7 +18505,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="185" hidden="1">
+    <row r="185">
       <c r="A185" t="s">
         <v>977</v>
       </c>
@@ -17716,7 +18577,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="188" hidden="1">
+    <row r="188">
       <c r="A188" t="s">
         <v>993</v>
       </c>
@@ -17765,7 +18626,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="190" hidden="1">
+    <row r="190">
       <c r="A190" t="s">
         <v>1003</v>
       </c>
@@ -17814,7 +18675,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" hidden="1">
       <c r="A192" t="s">
         <v>1014</v>
       </c>
@@ -17837,7 +18698,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="193" hidden="1">
+    <row r="193">
       <c r="A193" t="s">
         <v>1019</v>
       </c>
@@ -17866,7 +18727,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="194" hidden="1">
+    <row r="194">
       <c r="A194" t="s">
         <v>1026</v>
       </c>
@@ -17892,7 +18753,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="195" hidden="1">
+    <row r="195">
       <c r="A195" t="s">
         <v>1032</v>
       </c>
@@ -17941,7 +18802,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" hidden="1">
       <c r="A197" t="s">
         <v>1043</v>
       </c>
@@ -17987,7 +18848,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="199" hidden="1">
+    <row r="199">
       <c r="A199" t="s">
         <v>1053</v>
       </c>
@@ -18013,7 +18874,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="200" hidden="1">
+    <row r="200">
       <c r="A200" t="s">
         <v>1059</v>
       </c>
@@ -18039,7 +18900,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="201" hidden="1">
+    <row r="201">
       <c r="A201" t="s">
         <v>1065</v>
       </c>
@@ -18065,7 +18926,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="202" hidden="1">
+    <row r="202">
       <c r="A202" t="s">
         <v>1071</v>
       </c>
@@ -18137,7 +18998,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="205" hidden="1">
+    <row r="205">
       <c r="A205" t="s">
         <v>1086</v>
       </c>
@@ -18186,7 +19047,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="207" hidden="1">
+    <row r="207">
       <c r="A207" t="s">
         <v>1097</v>
       </c>
@@ -18281,7 +19142,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="211" hidden="1">
+    <row r="211">
       <c r="A211" t="s">
         <v>1118</v>
       </c>
@@ -18376,7 +19237,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="215" hidden="1">
+    <row r="215">
       <c r="A215" t="s">
         <v>1139</v>
       </c>
@@ -18425,7 +19286,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="217" hidden="1">
+    <row r="217">
       <c r="A217" t="s">
         <v>1150</v>
       </c>
@@ -18451,7 +19312,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="218" hidden="1">
+    <row r="218">
       <c r="A218" t="s">
         <v>1156</v>
       </c>
@@ -18477,7 +19338,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" hidden="1">
       <c r="A219" t="s">
         <v>1162</v>
       </c>
@@ -18500,7 +19361,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="220" hidden="1">
+    <row r="220">
       <c r="A220" t="s">
         <v>1167</v>
       </c>
@@ -18549,7 +19410,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="222" hidden="1">
+    <row r="222">
       <c r="A222" t="s">
         <v>1178</v>
       </c>
@@ -18690,7 +19551,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="228" hidden="1">
+    <row r="228">
       <c r="A228" t="s">
         <v>1209</v>
       </c>
@@ -18739,7 +19600,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="230" hidden="1">
+    <row r="230">
       <c r="A230" t="s">
         <v>1220</v>
       </c>
@@ -18811,7 +19672,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="233" hidden="1">
+    <row r="233">
       <c r="A233" t="s">
         <v>1236</v>
       </c>
@@ -18929,7 +19790,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" hidden="1">
       <c r="A238" t="s">
         <v>1262</v>
       </c>
@@ -18975,7 +19836,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="240" hidden="1">
+    <row r="240">
       <c r="A240" t="s">
         <v>1272</v>
       </c>
@@ -19024,7 +19885,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="242" hidden="1">
+    <row r="242">
       <c r="A242" t="s">
         <v>1283</v>
       </c>
@@ -19073,7 +19934,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="244" hidden="1">
+    <row r="244">
       <c r="A244" t="s">
         <v>1294</v>
       </c>
@@ -19099,7 +19960,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="245" hidden="1">
+    <row r="245">
       <c r="A245" t="s">
         <v>1300</v>
       </c>
@@ -19148,7 +20009,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="247" hidden="1">
+    <row r="247">
       <c r="A247" t="s">
         <v>1311</v>
       </c>
@@ -19197,7 +20058,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="249" hidden="1">
+    <row r="249">
       <c r="A249" t="s">
         <v>1322</v>
       </c>
@@ -19246,7 +20107,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="251" hidden="1">
+    <row r="251">
       <c r="A251" t="s">
         <v>1333</v>
       </c>
@@ -19272,7 +20133,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="252" hidden="1">
+    <row r="252">
       <c r="A252" t="s">
         <v>1339</v>
       </c>
@@ -19298,7 +20159,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="253" hidden="1">
+    <row r="253">
       <c r="A253" t="s">
         <v>1345</v>
       </c>
@@ -19347,7 +20208,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="255" hidden="1">
+    <row r="255">
       <c r="A255" t="s">
         <v>1356</v>
       </c>
@@ -19419,7 +20280,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="258" hidden="1">
+    <row r="258">
       <c r="A258" t="s">
         <v>1372</v>
       </c>
@@ -19445,7 +20306,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="259" hidden="1">
+    <row r="259">
       <c r="A259" t="s">
         <v>1378</v>
       </c>
@@ -19471,7 +20332,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="260" hidden="1">
+    <row r="260">
       <c r="A260" t="s">
         <v>1384</v>
       </c>
@@ -19497,7 +20358,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" hidden="1">
       <c r="A261" t="s">
         <v>1390</v>
       </c>
@@ -19658,7 +20519,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="268" hidden="1">
+    <row r="268">
       <c r="A268" t="s">
         <v>1424</v>
       </c>
@@ -19707,7 +20568,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" hidden="1">
       <c r="A270" t="s">
         <v>1435</v>
       </c>
@@ -19730,7 +20591,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="271" hidden="1">
+    <row r="271">
       <c r="A271" t="s">
         <v>1440</v>
       </c>
@@ -19756,7 +20617,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="272" hidden="1">
+    <row r="272">
       <c r="A272" t="s">
         <v>1446</v>
       </c>
@@ -19782,7 +20643,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="273" hidden="1">
+    <row r="273">
       <c r="A273" t="s">
         <v>1451</v>
       </c>
@@ -19808,7 +20669,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="274" hidden="1">
+    <row r="274">
       <c r="A274" t="s">
         <v>1457</v>
       </c>
@@ -19834,7 +20695,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" hidden="1">
       <c r="A275" t="s">
         <v>1463</v>
       </c>
@@ -19857,7 +20718,7 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="276" hidden="1">
+    <row r="276">
       <c r="A276" t="s">
         <v>1468</v>
       </c>
@@ -19906,7 +20767,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="278" hidden="1">
+    <row r="278">
       <c r="A278" t="s">
         <v>1479</v>
       </c>
@@ -19932,7 +20793,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="279" hidden="1">
+    <row r="279">
       <c r="A279" t="s">
         <v>1485</v>
       </c>
@@ -19958,7 +20819,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="280" hidden="1">
+    <row r="280">
       <c r="A280" t="s">
         <v>1491</v>
       </c>
@@ -19984,7 +20845,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="281" hidden="1">
+    <row r="281">
       <c r="A281" t="s">
         <v>1497</v>
       </c>
@@ -20033,7 +20894,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="283" hidden="1">
+    <row r="283">
       <c r="A283" t="s">
         <v>1508</v>
       </c>
@@ -20082,7 +20943,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="285" hidden="1">
+    <row r="285">
       <c r="A285" t="s">
         <v>1519</v>
       </c>
@@ -20108,7 +20969,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="286" hidden="1">
+    <row r="286">
       <c r="A286" t="s">
         <v>1525</v>
       </c>
@@ -20134,7 +20995,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="287" hidden="1">
+    <row r="287">
       <c r="A287" t="s">
         <v>1531</v>
       </c>
@@ -20183,7 +21044,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="289" hidden="1">
+    <row r="289">
       <c r="A289" t="s">
         <v>1542</v>
       </c>
@@ -20232,7 +21093,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="291" hidden="1">
+    <row r="291">
       <c r="A291" t="s">
         <v>1553</v>
       </c>
@@ -20258,7 +21119,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="292" hidden="1">
+    <row r="292">
       <c r="A292" t="s">
         <v>1559</v>
       </c>
@@ -20307,7 +21168,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="294" hidden="1">
+    <row r="294">
       <c r="A294" t="s">
         <v>1570</v>
       </c>
@@ -20333,7 +21194,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="295" hidden="1">
+    <row r="295">
       <c r="A295" t="s">
         <v>1576</v>
       </c>
@@ -20359,7 +21220,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="296" hidden="1">
+    <row r="296">
       <c r="A296" t="s">
         <v>1582</v>
       </c>
@@ -20408,7 +21269,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="298" hidden="1">
+    <row r="298">
       <c r="A298" t="s">
         <v>1593</v>
       </c>
@@ -20434,7 +21295,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="299" hidden="1">
+    <row r="299">
       <c r="A299" t="s">
         <v>1598</v>
       </c>
@@ -20460,7 +21321,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="300" hidden="1">
+    <row r="300">
       <c r="A300" t="s">
         <v>1604</v>
       </c>
@@ -20486,7 +21347,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="301" hidden="1">
+    <row r="301">
       <c r="A301" t="s">
         <v>1610</v>
       </c>
@@ -20512,7 +21373,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="302" hidden="1">
+    <row r="302">
       <c r="A302" t="s">
         <v>1616</v>
       </c>
@@ -20561,7 +21422,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="304" hidden="1">
+    <row r="304">
       <c r="A304" t="s">
         <v>1627</v>
       </c>
@@ -20610,7 +21471,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="306" hidden="1">
+    <row r="306">
       <c r="A306" t="s">
         <v>1638</v>
       </c>
@@ -20636,7 +21497,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="307" hidden="1">
+    <row r="307">
       <c r="A307" t="s">
         <v>1644</v>
       </c>
@@ -20662,7 +21523,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="308" hidden="1">
+    <row r="308">
       <c r="A308" t="s">
         <v>1650</v>
       </c>
@@ -20688,7 +21549,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="309" hidden="1">
+    <row r="309">
       <c r="A309" t="s">
         <v>1656</v>
       </c>
@@ -20714,7 +21575,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="310" hidden="1">
+    <row r="310">
       <c r="A310" t="s">
         <v>1662</v>
       </c>
@@ -20740,7 +21601,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="311" hidden="1">
+    <row r="311">
       <c r="A311" t="s">
         <v>1668</v>
       </c>
@@ -20766,7 +21627,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" hidden="1">
       <c r="A312" t="s">
         <v>1674</v>
       </c>
@@ -20812,7 +21673,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="314" hidden="1">
+    <row r="314">
       <c r="A314" t="s">
         <v>1684</v>
       </c>
@@ -20838,7 +21699,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="315" hidden="1">
+    <row r="315">
       <c r="A315" t="s">
         <v>1690</v>
       </c>
@@ -20864,7 +21725,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="316" hidden="1">
+    <row r="316">
       <c r="A316" t="s">
         <v>1696</v>
       </c>
@@ -20890,7 +21751,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" hidden="1">
       <c r="A317" t="s">
         <v>1702</v>
       </c>
@@ -20913,7 +21774,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="318" hidden="1">
+    <row r="318">
       <c r="A318" t="s">
         <v>1707</v>
       </c>
@@ -20939,7 +21800,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="319" hidden="1">
+    <row r="319">
       <c r="A319" t="s">
         <v>1713</v>
       </c>
@@ -20988,7 +21849,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="321" hidden="1">
+    <row r="321">
       <c r="A321" t="s">
         <v>1724</v>
       </c>
@@ -21014,7 +21875,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="322" hidden="1">
+    <row r="322">
       <c r="A322" t="s">
         <v>1730</v>
       </c>
@@ -21109,7 +21970,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="326" hidden="1">
+    <row r="326">
       <c r="A326" t="s">
         <v>1751</v>
       </c>
@@ -21135,7 +21996,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="327" hidden="1">
+    <row r="327">
       <c r="A327" t="s">
         <v>1756</v>
       </c>
@@ -21161,7 +22022,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="328" hidden="1">
+    <row r="328">
       <c r="A328" t="s">
         <v>1762</v>
       </c>
@@ -21187,7 +22048,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="329" hidden="1">
+    <row r="329">
       <c r="A329" t="s">
         <v>1768</v>
       </c>
@@ -21213,7 +22074,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="330" hidden="1">
+    <row r="330">
       <c r="A330" t="s">
         <v>1774</v>
       </c>
@@ -21239,7 +22100,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="331" hidden="1">
+    <row r="331">
       <c r="A331" t="s">
         <v>1780</v>
       </c>
@@ -21288,7 +22149,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="333" hidden="1">
+    <row r="333">
       <c r="A333" t="s">
         <v>1791</v>
       </c>
@@ -21314,7 +22175,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="334" hidden="1">
+    <row r="334">
       <c r="A334" t="s">
         <v>1797</v>
       </c>
@@ -21363,7 +22224,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="336" hidden="1">
+    <row r="336">
       <c r="A336" t="s">
         <v>1808</v>
       </c>
@@ -21412,7 +22273,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="338" hidden="1">
+    <row r="338">
       <c r="A338" t="s">
         <v>1819</v>
       </c>
@@ -21438,7 +22299,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="339" hidden="1">
+    <row r="339">
       <c r="A339" t="s">
         <v>1825</v>
       </c>
@@ -21490,7 +22351,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="341" hidden="1">
+    <row r="341">
       <c r="A341" t="s">
         <v>1837</v>
       </c>
@@ -21516,7 +22377,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="342" hidden="1">
+    <row r="342">
       <c r="A342" t="s">
         <v>1843</v>
       </c>
@@ -21542,7 +22403,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="343" hidden="1">
+    <row r="343">
       <c r="A343" t="s">
         <v>1849</v>
       </c>
@@ -21568,7 +22429,7 @@
         <v>1854</v>
       </c>
     </row>
-    <row r="344" hidden="1">
+    <row r="344">
       <c r="A344" t="s">
         <v>1855</v>
       </c>
@@ -21594,7 +22455,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="345" hidden="1">
+    <row r="345">
       <c r="A345" t="s">
         <v>1861</v>
       </c>
@@ -21620,7 +22481,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="346" hidden="1">
+    <row r="346">
       <c r="A346" t="s">
         <v>1867</v>
       </c>
@@ -21669,7 +22530,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="348" hidden="1">
+    <row r="348">
       <c r="A348" t="s">
         <v>1878</v>
       </c>
@@ -21695,7 +22556,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="349" hidden="1">
+    <row r="349">
       <c r="A349" t="s">
         <v>1884</v>
       </c>
@@ -21721,7 +22582,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="350" hidden="1">
+    <row r="350">
       <c r="A350" t="s">
         <v>1890</v>
       </c>
@@ -21862,7 +22723,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="356" hidden="1">
+    <row r="356">
       <c r="A356" t="s">
         <v>1920</v>
       </c>
@@ -21888,7 +22749,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="357" hidden="1">
+    <row r="357">
       <c r="A357" t="s">
         <v>1926</v>
       </c>
@@ -21937,7 +22798,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="359" hidden="1">
+    <row r="359">
       <c r="A359" t="s">
         <v>1937</v>
       </c>
@@ -21966,7 +22827,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="360" hidden="1">
+    <row r="360">
       <c r="A360" t="s">
         <v>1944</v>
       </c>
@@ -22038,7 +22899,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="363" hidden="1">
+    <row r="363">
       <c r="A363" t="s">
         <v>1960</v>
       </c>
@@ -22064,7 +22925,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="364" hidden="1">
+    <row r="364">
       <c r="A364" t="s">
         <v>1966</v>
       </c>
@@ -22090,7 +22951,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" hidden="1">
       <c r="A365" t="s">
         <v>1972</v>
       </c>
@@ -22159,7 +23020,7 @@
         <v>1986</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" hidden="1">
       <c r="A368" t="s">
         <v>1987</v>
       </c>
@@ -22205,7 +23066,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="370" hidden="1">
+    <row r="370">
       <c r="A370" t="s">
         <v>1997</v>
       </c>
@@ -22231,7 +23092,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" hidden="1">
       <c r="A371" t="s">
         <v>2003</v>
       </c>
@@ -22277,7 +23138,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="373" hidden="1">
+    <row r="373">
       <c r="A373" t="s">
         <v>2013</v>
       </c>
@@ -22303,7 +23164,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="374" hidden="1">
+    <row r="374">
       <c r="A374" t="s">
         <v>2019</v>
       </c>
@@ -22329,7 +23190,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="375" hidden="1">
+    <row r="375">
       <c r="A375" t="s">
         <v>2025</v>
       </c>
@@ -22355,7 +23216,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="376" hidden="1">
+    <row r="376">
       <c r="A376" t="s">
         <v>2031</v>
       </c>
@@ -22427,7 +23288,7 @@
         <v>2046</v>
       </c>
     </row>
-    <row r="379" hidden="1">
+    <row r="379">
       <c r="A379" t="s">
         <v>2047</v>
       </c>
@@ -22499,7 +23360,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="382" hidden="1">
+    <row r="382">
       <c r="A382" t="s">
         <v>2063</v>
       </c>
@@ -22525,7 +23386,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="383" hidden="1">
+    <row r="383">
       <c r="A383" t="s">
         <v>2069</v>
       </c>
@@ -22597,7 +23458,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="386" hidden="1">
+    <row r="386">
       <c r="A386" t="s">
         <v>2085</v>
       </c>
@@ -22623,7 +23484,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="387" hidden="1">
+    <row r="387">
       <c r="A387" t="s">
         <v>2091</v>
       </c>
@@ -22649,7 +23510,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="388" hidden="1">
+    <row r="388">
       <c r="A388" t="s">
         <v>2097</v>
       </c>
@@ -22675,7 +23536,7 @@
         <v>2102</v>
       </c>
     </row>
-    <row r="389" hidden="1">
+    <row r="389">
       <c r="A389" t="s">
         <v>2103</v>
       </c>
@@ -22701,7 +23562,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="390" hidden="1">
+    <row r="390">
       <c r="A390" t="s">
         <v>2109</v>
       </c>
@@ -22727,7 +23588,7 @@
         <v>2114</v>
       </c>
     </row>
-    <row r="391" hidden="1">
+    <row r="391">
       <c r="A391" t="s">
         <v>2115</v>
       </c>
@@ -22753,7 +23614,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="392" hidden="1">
+    <row r="392">
       <c r="A392" t="s">
         <v>2121</v>
       </c>
@@ -22779,7 +23640,7 @@
         <v>2126</v>
       </c>
     </row>
-    <row r="393" hidden="1">
+    <row r="393">
       <c r="A393" t="s">
         <v>2127</v>
       </c>
@@ -22805,7 +23666,7 @@
         <v>2132</v>
       </c>
     </row>
-    <row r="394" hidden="1">
+    <row r="394">
       <c r="A394" t="s">
         <v>2133</v>
       </c>
@@ -22877,7 +23738,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="397" hidden="1">
+    <row r="397">
       <c r="A397" t="s">
         <v>2149</v>
       </c>
@@ -22903,7 +23764,7 @@
         <v>2154</v>
       </c>
     </row>
-    <row r="398" hidden="1">
+    <row r="398">
       <c r="A398" t="s">
         <v>2155</v>
       </c>
@@ -22975,7 +23836,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="401">
+    <row r="401" hidden="1">
       <c r="A401" t="s">
         <v>2171</v>
       </c>
@@ -23021,7 +23882,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="403" hidden="1">
+    <row r="403">
       <c r="A403" t="s">
         <v>2181</v>
       </c>
@@ -23047,7 +23908,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="404" hidden="1">
+    <row r="404">
       <c r="A404" t="s">
         <v>2187</v>
       </c>
@@ -23096,7 +23957,7 @@
         <v>2197</v>
       </c>
     </row>
-    <row r="406" hidden="1">
+    <row r="406">
       <c r="A406" t="s">
         <v>2198</v>
       </c>
@@ -23191,7 +24052,7 @@
         <v>2218</v>
       </c>
     </row>
-    <row r="410" hidden="1">
+    <row r="410">
       <c r="A410" t="s">
         <v>2219</v>
       </c>
@@ -23263,7 +24124,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" hidden="1">
       <c r="A413" t="s">
         <v>2235</v>
       </c>
@@ -23286,7 +24147,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="414" hidden="1">
+    <row r="414">
       <c r="A414" t="s">
         <v>2240</v>
       </c>
@@ -23312,7 +24173,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="415" hidden="1">
+    <row r="415">
       <c r="A415" t="s">
         <v>2246</v>
       </c>
@@ -23384,7 +24245,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="418" hidden="1">
+    <row r="418">
       <c r="A418" t="s">
         <v>2262</v>
       </c>
@@ -23410,7 +24271,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="419" hidden="1">
+    <row r="419">
       <c r="A419" t="s">
         <v>2268</v>
       </c>
@@ -23459,7 +24320,7 @@
         <v>2278</v>
       </c>
     </row>
-    <row r="421" hidden="1">
+    <row r="421">
       <c r="A421" t="s">
         <v>2279</v>
       </c>
@@ -23485,7 +24346,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" hidden="1">
       <c r="A422" t="s">
         <v>2285</v>
       </c>
@@ -23508,7 +24369,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="423" hidden="1">
+    <row r="423">
       <c r="A423" t="s">
         <v>2290</v>
       </c>
@@ -23557,7 +24418,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="425" hidden="1">
+    <row r="425">
       <c r="A425" t="s">
         <v>2301</v>
       </c>
@@ -23583,7 +24444,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" hidden="1">
       <c r="A426" t="s">
         <v>2307</v>
       </c>
@@ -23629,7 +24490,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="428" hidden="1">
+    <row r="428">
       <c r="A428" t="s">
         <v>2317</v>
       </c>
@@ -23655,7 +24516,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="429" hidden="1">
+    <row r="429">
       <c r="A429" t="s">
         <v>2323</v>
       </c>
@@ -23681,7 +24542,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="430" hidden="1">
+    <row r="430">
       <c r="A430" t="s">
         <v>2329</v>
       </c>
@@ -23707,7 +24568,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="431" hidden="1">
+    <row r="431">
       <c r="A431" t="s">
         <v>2335</v>
       </c>
@@ -23733,7 +24594,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="432" hidden="1">
+    <row r="432">
       <c r="A432" t="s">
         <v>2341</v>
       </c>
@@ -23759,7 +24620,7 @@
         <v>2346</v>
       </c>
     </row>
-    <row r="433" hidden="1">
+    <row r="433">
       <c r="A433" t="s">
         <v>2347</v>
       </c>
@@ -23785,7 +24646,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" hidden="1">
       <c r="A434" t="s">
         <v>2353</v>
       </c>
@@ -23808,7 +24669,7 @@
         <v>2357</v>
       </c>
     </row>
-    <row r="435" hidden="1">
+    <row r="435">
       <c r="A435" t="s">
         <v>2358</v>
       </c>
@@ -23834,7 +24695,7 @@
         <v>2363</v>
       </c>
     </row>
-    <row r="436" hidden="1">
+    <row r="436">
       <c r="A436" t="s">
         <v>2364</v>
       </c>
@@ -23860,7 +24721,7 @@
         <v>2369</v>
       </c>
     </row>
-    <row r="437" hidden="1">
+    <row r="437">
       <c r="A437" t="s">
         <v>2370</v>
       </c>
@@ -23886,7 +24747,7 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="438" hidden="1">
+    <row r="438">
       <c r="A438" t="s">
         <v>2376</v>
       </c>
@@ -23912,7 +24773,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="439" hidden="1">
+    <row r="439">
       <c r="A439" t="s">
         <v>2382</v>
       </c>
@@ -23938,7 +24799,7 @@
         <v>2387</v>
       </c>
     </row>
-    <row r="440" hidden="1">
+    <row r="440">
       <c r="A440" t="s">
         <v>2388</v>
       </c>
@@ -24010,7 +24871,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="443" hidden="1">
+    <row r="443">
       <c r="A443" t="s">
         <v>2404</v>
       </c>
@@ -24059,7 +24920,7 @@
         <v>2414</v>
       </c>
     </row>
-    <row r="445" hidden="1">
+    <row r="445">
       <c r="A445" t="s">
         <v>2415</v>
       </c>
@@ -24108,7 +24969,7 @@
         <v>2425</v>
       </c>
     </row>
-    <row r="447" hidden="1">
+    <row r="447">
       <c r="A447" t="s">
         <v>2426</v>
       </c>
@@ -24134,7 +24995,7 @@
         <v>2431</v>
       </c>
     </row>
-    <row r="448" hidden="1">
+    <row r="448">
       <c r="A448" t="s">
         <v>2432</v>
       </c>
@@ -24160,7 +25021,7 @@
         <v>2437</v>
       </c>
     </row>
-    <row r="449" hidden="1">
+    <row r="449">
       <c r="A449" t="s">
         <v>2438</v>
       </c>
@@ -24186,7 +25047,7 @@
         <v>2442</v>
       </c>
     </row>
-    <row r="450" hidden="1">
+    <row r="450">
       <c r="A450" t="s">
         <v>2443</v>
       </c>
@@ -24235,7 +25096,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="452" hidden="1">
+    <row r="452">
       <c r="A452" t="s">
         <v>2454</v>
       </c>
@@ -24261,7 +25122,7 @@
         <v>2459</v>
       </c>
     </row>
-    <row r="453" hidden="1">
+    <row r="453">
       <c r="A453" t="s">
         <v>2460</v>
       </c>
@@ -24287,7 +25148,7 @@
         <v>2465</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" hidden="1">
       <c r="A454" t="s">
         <v>2466</v>
       </c>
@@ -24333,7 +25194,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="456" hidden="1">
+    <row r="456">
       <c r="A456" t="s">
         <v>2476</v>
       </c>
@@ -24359,7 +25220,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="457" hidden="1">
+    <row r="457">
       <c r="A457" t="s">
         <v>2482</v>
       </c>
@@ -24385,7 +25246,7 @@
         <v>2487</v>
       </c>
     </row>
-    <row r="458" hidden="1">
+    <row r="458">
       <c r="A458" t="s">
         <v>2488</v>
       </c>
@@ -24411,7 +25272,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="459" hidden="1">
+    <row r="459">
       <c r="A459" t="s">
         <v>2494</v>
       </c>
@@ -24437,7 +25298,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="460" hidden="1">
+    <row r="460">
       <c r="A460" t="s">
         <v>2500</v>
       </c>
@@ -24463,7 +25324,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="461" hidden="1">
+    <row r="461">
       <c r="A461" t="s">
         <v>2506</v>
       </c>
@@ -24558,7 +25419,7 @@
         <v>2526</v>
       </c>
     </row>
-    <row r="465" hidden="1">
+    <row r="465">
       <c r="A465" t="s">
         <v>2527</v>
       </c>
@@ -24584,7 +25445,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="466" hidden="1">
+    <row r="466">
       <c r="A466" t="s">
         <v>2533</v>
       </c>
@@ -24610,7 +25471,7 @@
         <v>2538</v>
       </c>
     </row>
-    <row r="467" hidden="1">
+    <row r="467">
       <c r="A467" t="s">
         <v>2539</v>
       </c>
@@ -24636,7 +25497,7 @@
         <v>2544</v>
       </c>
     </row>
-    <row r="468" hidden="1">
+    <row r="468">
       <c r="A468" t="s">
         <v>2545</v>
       </c>
@@ -24708,7 +25569,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="471" hidden="1">
+    <row r="471">
       <c r="A471" t="s">
         <v>2561</v>
       </c>
@@ -24757,7 +25618,7 @@
         <v>2571</v>
       </c>
     </row>
-    <row r="473" hidden="1">
+    <row r="473">
       <c r="A473" t="s">
         <v>2572</v>
       </c>
@@ -24783,7 +25644,7 @@
         <v>2577</v>
       </c>
     </row>
-    <row r="474" hidden="1">
+    <row r="474">
       <c r="A474" t="s">
         <v>2578</v>
       </c>
@@ -24809,7 +25670,7 @@
         <v>2583</v>
       </c>
     </row>
-    <row r="475" hidden="1">
+    <row r="475">
       <c r="A475" t="s">
         <v>2584</v>
       </c>
@@ -24835,7 +25696,7 @@
         <v>2589</v>
       </c>
     </row>
-    <row r="476" hidden="1">
+    <row r="476">
       <c r="A476" t="s">
         <v>2590</v>
       </c>
@@ -24884,7 +25745,7 @@
         <v>2600</v>
       </c>
     </row>
-    <row r="478" hidden="1">
+    <row r="478">
       <c r="A478" t="s">
         <v>2601</v>
       </c>
@@ -24910,7 +25771,7 @@
         <v>2606</v>
       </c>
     </row>
-    <row r="479" hidden="1">
+    <row r="479">
       <c r="A479" t="s">
         <v>2607</v>
       </c>
@@ -24936,7 +25797,7 @@
         <v>2611</v>
       </c>
     </row>
-    <row r="480">
+    <row r="480" hidden="1">
       <c r="A480" t="s">
         <v>2612</v>
       </c>
@@ -24959,7 +25820,7 @@
         <v>2616</v>
       </c>
     </row>
-    <row r="481" hidden="1">
+    <row r="481">
       <c r="A481" t="s">
         <v>2617</v>
       </c>
@@ -25031,7 +25892,7 @@
         <v>2631</v>
       </c>
     </row>
-    <row r="484" hidden="1">
+    <row r="484">
       <c r="A484" t="s">
         <v>2632</v>
       </c>
@@ -25080,7 +25941,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="486" hidden="1">
+    <row r="486">
       <c r="A486" t="s">
         <v>2643</v>
       </c>
@@ -25106,7 +25967,7 @@
         <v>2648</v>
       </c>
     </row>
-    <row r="487" hidden="1">
+    <row r="487">
       <c r="A487" t="s">
         <v>2649</v>
       </c>
@@ -25132,7 +25993,7 @@
         <v>2653</v>
       </c>
     </row>
-    <row r="488" hidden="1">
+    <row r="488">
       <c r="A488" t="s">
         <v>2654</v>
       </c>
@@ -25158,7 +26019,7 @@
         <v>2659</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" hidden="1">
       <c r="A489" t="s">
         <v>2660</v>
       </c>
@@ -25181,7 +26042,7 @@
         <v>2664</v>
       </c>
     </row>
-    <row r="490" hidden="1">
+    <row r="490">
       <c r="A490" t="s">
         <v>2665</v>
       </c>
@@ -25207,7 +26068,7 @@
         <v>2670</v>
       </c>
     </row>
-    <row r="491" hidden="1">
+    <row r="491">
       <c r="A491" t="s">
         <v>2671</v>
       </c>
@@ -25279,7 +26140,7 @@
         <v>2686</v>
       </c>
     </row>
-    <row r="494" hidden="1">
+    <row r="494">
       <c r="A494" t="s">
         <v>2687</v>
       </c>
@@ -25328,7 +26189,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="496" hidden="1">
+    <row r="496">
       <c r="A496" t="s">
         <v>2698</v>
       </c>
@@ -25354,7 +26215,7 @@
         <v>2703</v>
       </c>
     </row>
-    <row r="497" hidden="1">
+    <row r="497">
       <c r="A497" t="s">
         <v>2704</v>
       </c>
@@ -25380,7 +26241,7 @@
         <v>2709</v>
       </c>
     </row>
-    <row r="498" hidden="1">
+    <row r="498">
       <c r="A498" t="s">
         <v>2710</v>
       </c>
@@ -25429,7 +26290,7 @@
         <v>2720</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" hidden="1">
       <c r="A500" t="s">
         <v>2721</v>
       </c>
@@ -25475,7 +26336,7 @@
         <v>2730</v>
       </c>
     </row>
-    <row r="502" hidden="1">
+    <row r="502">
       <c r="A502" t="s">
         <v>2731</v>
       </c>
@@ -25501,7 +26362,7 @@
         <v>2736</v>
       </c>
     </row>
-    <row r="503" hidden="1">
+    <row r="503">
       <c r="A503" t="s">
         <v>2737</v>
       </c>
@@ -25527,7 +26388,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="504" hidden="1">
+    <row r="504">
       <c r="A504" t="s">
         <v>2743</v>
       </c>
@@ -25553,7 +26414,7 @@
         <v>2748</v>
       </c>
     </row>
-    <row r="505" hidden="1">
+    <row r="505">
       <c r="A505" t="s">
         <v>2749</v>
       </c>
@@ -25625,7 +26486,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="508" hidden="1">
+    <row r="508">
       <c r="A508" t="s">
         <v>2764</v>
       </c>
@@ -25674,7 +26535,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="510" hidden="1">
+    <row r="510">
       <c r="A510" t="s">
         <v>2775</v>
       </c>
@@ -25723,7 +26584,7 @@
         <v>2785</v>
       </c>
     </row>
-    <row r="512" hidden="1">
+    <row r="512">
       <c r="A512" t="s">
         <v>2786</v>
       </c>
@@ -25749,7 +26610,7 @@
         <v>2791</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" hidden="1">
       <c r="A513" t="s">
         <v>2792</v>
       </c>
@@ -25772,7 +26633,7 @@
         <v>2796</v>
       </c>
     </row>
-    <row r="514" hidden="1">
+    <row r="514">
       <c r="A514" t="s">
         <v>2797</v>
       </c>
@@ -25821,7 +26682,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="516" hidden="1">
+    <row r="516">
       <c r="A516" t="s">
         <v>2808</v>
       </c>
@@ -25893,7 +26754,7 @@
         <v>2823</v>
       </c>
     </row>
-    <row r="519">
+    <row r="519" hidden="1">
       <c r="A519" t="s">
         <v>2824</v>
       </c>
@@ -25916,7 +26777,7 @@
         <v>2828</v>
       </c>
     </row>
-    <row r="520" hidden="1">
+    <row r="520">
       <c r="A520" t="s">
         <v>2829</v>
       </c>
@@ -25942,7 +26803,7 @@
         <v>2834</v>
       </c>
     </row>
-    <row r="521" hidden="1">
+    <row r="521">
       <c r="A521" t="s">
         <v>2835</v>
       </c>
@@ -25968,7 +26829,7 @@
         <v>2840</v>
       </c>
     </row>
-    <row r="522" hidden="1">
+    <row r="522">
       <c r="A522" t="s">
         <v>2841</v>
       </c>
@@ -26017,7 +26878,7 @@
         <v>2851</v>
       </c>
     </row>
-    <row r="524" hidden="1">
+    <row r="524">
       <c r="A524" t="s">
         <v>2852</v>
       </c>
@@ -26043,7 +26904,7 @@
         <v>2857</v>
       </c>
     </row>
-    <row r="525">
+    <row r="525" hidden="1">
       <c r="A525" t="s">
         <v>2858</v>
       </c>
@@ -26066,7 +26927,7 @@
         <v>2862</v>
       </c>
     </row>
-    <row r="526" hidden="1">
+    <row r="526">
       <c r="A526" t="s">
         <v>2863</v>
       </c>
@@ -26092,7 +26953,7 @@
         <v>2868</v>
       </c>
     </row>
-    <row r="527" hidden="1">
+    <row r="527">
       <c r="A527" t="s">
         <v>2869</v>
       </c>
@@ -26164,7 +27025,7 @@
         <v>2884</v>
       </c>
     </row>
-    <row r="530" hidden="1">
+    <row r="530">
       <c r="A530" t="s">
         <v>2885</v>
       </c>
@@ -26190,7 +27051,7 @@
         <v>2890</v>
       </c>
     </row>
-    <row r="531" hidden="1">
+    <row r="531">
       <c r="A531" t="s">
         <v>2891</v>
       </c>
@@ -26216,7 +27077,7 @@
         <v>2896</v>
       </c>
     </row>
-    <row r="532" hidden="1">
+    <row r="532">
       <c r="A532" t="s">
         <v>2897</v>
       </c>
@@ -26242,7 +27103,7 @@
         <v>2902</v>
       </c>
     </row>
-    <row r="533" hidden="1">
+    <row r="533">
       <c r="A533" t="s">
         <v>2903</v>
       </c>
@@ -26268,7 +27129,7 @@
         <v>2908</v>
       </c>
     </row>
-    <row r="534" hidden="1">
+    <row r="534">
       <c r="A534" t="s">
         <v>2909</v>
       </c>
@@ -26294,7 +27155,7 @@
         <v>2914</v>
       </c>
     </row>
-    <row r="535" hidden="1">
+    <row r="535">
       <c r="A535" t="s">
         <v>2915</v>
       </c>
@@ -26320,7 +27181,7 @@
         <v>2920</v>
       </c>
     </row>
-    <row r="536">
+    <row r="536" hidden="1">
       <c r="A536" t="s">
         <v>2921</v>
       </c>
@@ -26343,7 +27204,7 @@
         <v>2925</v>
       </c>
     </row>
-    <row r="537" hidden="1">
+    <row r="537">
       <c r="A537" t="s">
         <v>2926</v>
       </c>
@@ -26415,7 +27276,7 @@
         <v>2941</v>
       </c>
     </row>
-    <row r="540" hidden="1">
+    <row r="540">
       <c r="A540" t="s">
         <v>2942</v>
       </c>
@@ -26441,7 +27302,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="541" hidden="1">
+    <row r="541">
       <c r="A541" t="s">
         <v>2947</v>
       </c>
@@ -26467,7 +27328,7 @@
         <v>2952</v>
       </c>
     </row>
-    <row r="542" hidden="1">
+    <row r="542">
       <c r="A542" t="s">
         <v>2953</v>
       </c>
@@ -26493,7 +27354,7 @@
         <v>2958</v>
       </c>
     </row>
-    <row r="543">
+    <row r="543" hidden="1">
       <c r="A543" t="s">
         <v>2959</v>
       </c>
@@ -26516,7 +27377,7 @@
         <v>2963</v>
       </c>
     </row>
-    <row r="544" hidden="1">
+    <row r="544">
       <c r="A544" t="s">
         <v>2964</v>
       </c>
@@ -26542,7 +27403,7 @@
         <v>2969</v>
       </c>
     </row>
-    <row r="545" hidden="1">
+    <row r="545">
       <c r="A545" t="s">
         <v>2970</v>
       </c>
@@ -26568,7 +27429,7 @@
         <v>2975</v>
       </c>
     </row>
-    <row r="546" hidden="1">
+    <row r="546">
       <c r="A546" t="s">
         <v>2976</v>
       </c>
@@ -26594,7 +27455,7 @@
         <v>2981</v>
       </c>
     </row>
-    <row r="547" hidden="1">
+    <row r="547">
       <c r="A547" t="s">
         <v>2982</v>
       </c>
@@ -26643,7 +27504,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="549" hidden="1">
+    <row r="549">
       <c r="A549" t="s">
         <v>2993</v>
       </c>
@@ -26692,7 +27553,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="551" hidden="1">
+    <row r="551">
       <c r="A551" t="s">
         <v>3004</v>
       </c>
@@ -26764,7 +27625,7 @@
         <v>3019</v>
       </c>
     </row>
-    <row r="554" hidden="1">
+    <row r="554">
       <c r="A554" t="s">
         <v>3020</v>
       </c>
@@ -26790,7 +27651,7 @@
         <v>3025</v>
       </c>
     </row>
-    <row r="555">
+    <row r="555" hidden="1">
       <c r="A555" t="s">
         <v>3026</v>
       </c>
@@ -26813,7 +27674,7 @@
         <v>3030</v>
       </c>
     </row>
-    <row r="556" hidden="1">
+    <row r="556">
       <c r="A556" t="s">
         <v>3031</v>
       </c>
@@ -26839,7 +27700,7 @@
         <v>3036</v>
       </c>
     </row>
-    <row r="557" hidden="1">
+    <row r="557">
       <c r="A557" t="s">
         <v>3037</v>
       </c>
@@ -26888,7 +27749,7 @@
         <v>3047</v>
       </c>
     </row>
-    <row r="559" hidden="1">
+    <row r="559">
       <c r="A559" t="s">
         <v>3048</v>
       </c>
@@ -26914,7 +27775,7 @@
         <v>3053</v>
       </c>
     </row>
-    <row r="560" hidden="1">
+    <row r="560">
       <c r="A560" t="s">
         <v>3054</v>
       </c>
@@ -26940,7 +27801,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="561" hidden="1">
+    <row r="561">
       <c r="A561" t="s">
         <v>3060</v>
       </c>
@@ -27012,7 +27873,7 @@
         <v>3075</v>
       </c>
     </row>
-    <row r="564" hidden="1">
+    <row r="564">
       <c r="A564" t="s">
         <v>3076</v>
       </c>
@@ -27038,7 +27899,7 @@
         <v>3081</v>
       </c>
     </row>
-    <row r="565" hidden="1">
+    <row r="565">
       <c r="A565" t="s">
         <v>3082</v>
       </c>
@@ -27064,7 +27925,7 @@
         <v>3087</v>
       </c>
     </row>
-    <row r="566" hidden="1">
+    <row r="566">
       <c r="A566" t="s">
         <v>3088</v>
       </c>
@@ -27090,7 +27951,7 @@
         <v>3092</v>
       </c>
     </row>
-    <row r="567" hidden="1">
+    <row r="567">
       <c r="A567" t="s">
         <v>3093</v>
       </c>
@@ -27139,7 +28000,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="569" hidden="1">
+    <row r="569">
       <c r="A569" t="s">
         <v>3104</v>
       </c>
@@ -27165,7 +28026,7 @@
         <v>3109</v>
       </c>
     </row>
-    <row r="570" hidden="1">
+    <row r="570">
       <c r="A570" t="s">
         <v>3110</v>
       </c>
@@ -27191,7 +28052,7 @@
         <v>3115</v>
       </c>
     </row>
-    <row r="571" hidden="1">
+    <row r="571">
       <c r="A571" t="s">
         <v>3116</v>
       </c>
@@ -27217,7 +28078,7 @@
         <v>3121</v>
       </c>
     </row>
-    <row r="572" hidden="1">
+    <row r="572">
       <c r="A572" t="s">
         <v>3122</v>
       </c>
@@ -27243,7 +28104,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="573" hidden="1">
+    <row r="573">
       <c r="A573" t="s">
         <v>3126</v>
       </c>
@@ -27269,7 +28130,7 @@
         <v>3131</v>
       </c>
     </row>
-    <row r="574" hidden="1">
+    <row r="574">
       <c r="A574" t="s">
         <v>3132</v>
       </c>
@@ -27318,7 +28179,7 @@
         <v>3142</v>
       </c>
     </row>
-    <row r="576" hidden="1">
+    <row r="576">
       <c r="A576" t="s">
         <v>3143</v>
       </c>
@@ -27344,7 +28205,7 @@
         <v>3148</v>
       </c>
     </row>
-    <row r="577" hidden="1">
+    <row r="577">
       <c r="A577" t="s">
         <v>3149</v>
       </c>
@@ -27370,7 +28231,7 @@
         <v>3154</v>
       </c>
     </row>
-    <row r="578" hidden="1">
+    <row r="578">
       <c r="A578" t="s">
         <v>3155</v>
       </c>
@@ -27396,7 +28257,7 @@
         <v>3160</v>
       </c>
     </row>
-    <row r="579" hidden="1">
+    <row r="579">
       <c r="A579" t="s">
         <v>3161</v>
       </c>
@@ -27422,7 +28283,7 @@
         <v>3166</v>
       </c>
     </row>
-    <row r="580" hidden="1">
+    <row r="580">
       <c r="A580" t="s">
         <v>3167</v>
       </c>
@@ -27494,7 +28355,7 @@
         <v>3182</v>
       </c>
     </row>
-    <row r="583" hidden="1">
+    <row r="583">
       <c r="A583" t="s">
         <v>3183</v>
       </c>
@@ -27520,7 +28381,7 @@
         <v>3188</v>
       </c>
     </row>
-    <row r="584" hidden="1">
+    <row r="584">
       <c r="A584" t="s">
         <v>3189</v>
       </c>
@@ -27546,7 +28407,7 @@
         <v>3194</v>
       </c>
     </row>
-    <row r="585">
+    <row r="585" hidden="1">
       <c r="A585" t="s">
         <v>3195</v>
       </c>
@@ -27569,7 +28430,7 @@
         <v>3199</v>
       </c>
     </row>
-    <row r="586">
+    <row r="586" hidden="1">
       <c r="A586" t="s">
         <v>3200</v>
       </c>
@@ -27592,7 +28453,7 @@
         <v>3204</v>
       </c>
     </row>
-    <row r="587">
+    <row r="587" hidden="1">
       <c r="A587" t="s">
         <v>3205</v>
       </c>
@@ -27615,7 +28476,7 @@
         <v>3209</v>
       </c>
     </row>
-    <row r="588">
+    <row r="588" hidden="1">
       <c r="A588" t="s">
         <v>3210</v>
       </c>
@@ -27638,7 +28499,7 @@
         <v>3214</v>
       </c>
     </row>
-    <row r="589">
+    <row r="589" hidden="1">
       <c r="A589" t="s">
         <v>3215</v>
       </c>
@@ -27661,7 +28522,7 @@
         <v>3219</v>
       </c>
     </row>
-    <row r="590">
+    <row r="590" hidden="1">
       <c r="A590" t="s">
         <v>3220</v>
       </c>
@@ -27684,7 +28545,7 @@
         <v>3224</v>
       </c>
     </row>
-    <row r="591">
+    <row r="591" hidden="1">
       <c r="A591" t="s">
         <v>3225</v>
       </c>
@@ -27707,7 +28568,7 @@
         <v>3229</v>
       </c>
     </row>
-    <row r="592">
+    <row r="592" hidden="1">
       <c r="A592" t="s">
         <v>3230</v>
       </c>
@@ -27730,7 +28591,7 @@
         <v>3234</v>
       </c>
     </row>
-    <row r="593">
+    <row r="593" hidden="1">
       <c r="A593" t="s">
         <v>3235</v>
       </c>
@@ -27753,7 +28614,7 @@
         <v>3239</v>
       </c>
     </row>
-    <row r="594">
+    <row r="594" hidden="1">
       <c r="A594" t="s">
         <v>3240</v>
       </c>
@@ -27776,7 +28637,7 @@
         <v>3244</v>
       </c>
     </row>
-    <row r="595" hidden="1">
+    <row r="595">
       <c r="A595" t="s">
         <v>3245</v>
       </c>
@@ -27802,7 +28663,7 @@
         <v>3250</v>
       </c>
     </row>
-    <row r="596">
+    <row r="596" hidden="1">
       <c r="A596" t="s">
         <v>3251</v>
       </c>
@@ -27825,7 +28686,7 @@
         <v>3255</v>
       </c>
     </row>
-    <row r="597">
+    <row r="597" hidden="1">
       <c r="A597" t="s">
         <v>3256</v>
       </c>
@@ -27848,7 +28709,7 @@
         <v>3260</v>
       </c>
     </row>
-    <row r="598">
+    <row r="598" hidden="1">
       <c r="A598" t="s">
         <v>3261</v>
       </c>
@@ -27871,7 +28732,7 @@
         <v>3265</v>
       </c>
     </row>
-    <row r="599">
+    <row r="599" hidden="1">
       <c r="A599" t="s">
         <v>3266</v>
       </c>
@@ -27894,7 +28755,7 @@
         <v>3270</v>
       </c>
     </row>
-    <row r="600">
+    <row r="600" hidden="1">
       <c r="A600" t="s">
         <v>3271</v>
       </c>
@@ -27917,7 +28778,7 @@
         <v>3275</v>
       </c>
     </row>
-    <row r="601" hidden="1">
+    <row r="601">
       <c r="A601" t="s">
         <v>3276</v>
       </c>
@@ -27966,7 +28827,7 @@
         <v>3286</v>
       </c>
     </row>
-    <row r="603">
+    <row r="603" hidden="1">
       <c r="A603" t="s">
         <v>3287</v>
       </c>
@@ -28058,7 +28919,7 @@
         <v>3306</v>
       </c>
     </row>
-    <row r="607" hidden="1">
+    <row r="607">
       <c r="A607" t="s">
         <v>3307</v>
       </c>
@@ -28084,7 +28945,7 @@
         <v>3312</v>
       </c>
     </row>
-    <row r="608" hidden="1">
+    <row r="608">
       <c r="A608" t="s">
         <v>3313</v>
       </c>
@@ -28110,7 +28971,7 @@
         <v>3318</v>
       </c>
     </row>
-    <row r="609" hidden="1">
+    <row r="609">
       <c r="A609" t="s">
         <v>3319</v>
       </c>
@@ -28136,7 +28997,7 @@
         <v>3324</v>
       </c>
     </row>
-    <row r="610" hidden="1">
+    <row r="610">
       <c r="A610" t="s">
         <v>3325</v>
       </c>
@@ -28162,7 +29023,7 @@
         <v>3330</v>
       </c>
     </row>
-    <row r="611" hidden="1">
+    <row r="611">
       <c r="A611" t="s">
         <v>3331</v>
       </c>
@@ -28188,7 +29049,7 @@
         <v>3336</v>
       </c>
     </row>
-    <row r="612" hidden="1">
+    <row r="612">
       <c r="A612" t="s">
         <v>3337</v>
       </c>
@@ -28214,7 +29075,7 @@
         <v>3342</v>
       </c>
     </row>
-    <row r="613" hidden="1">
+    <row r="613">
       <c r="A613" t="s">
         <v>3343</v>
       </c>
@@ -28286,7 +29147,7 @@
         <v>3358</v>
       </c>
     </row>
-    <row r="616" hidden="1">
+    <row r="616">
       <c r="A616" t="s">
         <v>3359</v>
       </c>
@@ -28358,7 +29219,7 @@
         <v>3374</v>
       </c>
     </row>
-    <row r="619" hidden="1">
+    <row r="619">
       <c r="A619" t="s">
         <v>3375</v>
       </c>
@@ -28384,7 +29245,7 @@
         <v>3380</v>
       </c>
     </row>
-    <row r="620" hidden="1">
+    <row r="620">
       <c r="A620" t="s">
         <v>3381</v>
       </c>
@@ -28410,7 +29271,7 @@
         <v>3386</v>
       </c>
     </row>
-    <row r="621" hidden="1">
+    <row r="621">
       <c r="A621" t="s">
         <v>3387</v>
       </c>
@@ -28436,7 +29297,7 @@
         <v>3392</v>
       </c>
     </row>
-    <row r="622" hidden="1">
+    <row r="622">
       <c r="A622" t="s">
         <v>3393</v>
       </c>
@@ -28485,7 +29346,7 @@
         <v>3403</v>
       </c>
     </row>
-    <row r="624" hidden="1">
+    <row r="624">
       <c r="A624" t="s">
         <v>3404</v>
       </c>
@@ -28557,7 +29418,7 @@
         <v>3419</v>
       </c>
     </row>
-    <row r="627" hidden="1">
+    <row r="627">
       <c r="A627" t="s">
         <v>3420</v>
       </c>
@@ -28583,7 +29444,7 @@
         <v>3425</v>
       </c>
     </row>
-    <row r="628" hidden="1">
+    <row r="628">
       <c r="A628" t="s">
         <v>3426</v>
       </c>
@@ -28609,7 +29470,7 @@
         <v>3431</v>
       </c>
     </row>
-    <row r="629" hidden="1">
+    <row r="629">
       <c r="A629" t="s">
         <v>3432</v>
       </c>
@@ -28658,7 +29519,7 @@
         <v>3442</v>
       </c>
     </row>
-    <row r="631" hidden="1">
+    <row r="631">
       <c r="A631" t="s">
         <v>3443</v>
       </c>
@@ -28684,7 +29545,7 @@
         <v>3448</v>
       </c>
     </row>
-    <row r="632" hidden="1">
+    <row r="632">
       <c r="A632" t="s">
         <v>3449</v>
       </c>
@@ -28710,7 +29571,7 @@
         <v>3454</v>
       </c>
     </row>
-    <row r="633" hidden="1">
+    <row r="633">
       <c r="A633" t="s">
         <v>3455</v>
       </c>
@@ -28736,7 +29597,7 @@
         <v>3460</v>
       </c>
     </row>
-    <row r="634" hidden="1">
+    <row r="634">
       <c r="A634" t="s">
         <v>3461</v>
       </c>
@@ -28762,7 +29623,7 @@
         <v>3466</v>
       </c>
     </row>
-    <row r="635" hidden="1">
+    <row r="635">
       <c r="A635" t="s">
         <v>3467</v>
       </c>
@@ -28788,7 +29649,7 @@
         <v>3472</v>
       </c>
     </row>
-    <row r="636" hidden="1">
+    <row r="636">
       <c r="A636" t="s">
         <v>3473</v>
       </c>
@@ -28814,7 +29675,7 @@
         <v>3478</v>
       </c>
     </row>
-    <row r="637" hidden="1">
+    <row r="637">
       <c r="A637" t="s">
         <v>3479</v>
       </c>
@@ -28840,7 +29701,7 @@
         <v>3484</v>
       </c>
     </row>
-    <row r="638" hidden="1">
+    <row r="638">
       <c r="A638" t="s">
         <v>3485</v>
       </c>
@@ -28866,7 +29727,7 @@
         <v>3490</v>
       </c>
     </row>
-    <row r="639" hidden="1">
+    <row r="639">
       <c r="A639" t="s">
         <v>3491</v>
       </c>
@@ -28892,7 +29753,7 @@
         <v>3496</v>
       </c>
     </row>
-    <row r="640" hidden="1">
+    <row r="640">
       <c r="A640" t="s">
         <v>3497</v>
       </c>
@@ -28918,7 +29779,7 @@
         <v>3502</v>
       </c>
     </row>
-    <row r="641" hidden="1">
+    <row r="641">
       <c r="A641" t="s">
         <v>3503</v>
       </c>
@@ -28944,7 +29805,7 @@
         <v>3508</v>
       </c>
     </row>
-    <row r="642" hidden="1">
+    <row r="642">
       <c r="A642" t="s">
         <v>3509</v>
       </c>
@@ -29016,7 +29877,7 @@
         <v>3524</v>
       </c>
     </row>
-    <row r="645" hidden="1">
+    <row r="645">
       <c r="A645" t="s">
         <v>3525</v>
       </c>
@@ -29042,7 +29903,7 @@
         <v>3530</v>
       </c>
     </row>
-    <row r="646" hidden="1">
+    <row r="646">
       <c r="A646" t="s">
         <v>3531</v>
       </c>
@@ -29091,7 +29952,7 @@
         <v>3541</v>
       </c>
     </row>
-    <row r="648" hidden="1">
+    <row r="648">
       <c r="A648" t="s">
         <v>3542</v>
       </c>
@@ -29117,7 +29978,7 @@
         <v>3547</v>
       </c>
     </row>
-    <row r="649" hidden="1">
+    <row r="649">
       <c r="A649" t="s">
         <v>3548</v>
       </c>
@@ -29166,7 +30027,7 @@
         <v>3558</v>
       </c>
     </row>
-    <row r="651" hidden="1">
+    <row r="651">
       <c r="A651" t="s">
         <v>3559</v>
       </c>
@@ -29192,7 +30053,7 @@
         <v>3564</v>
       </c>
     </row>
-    <row r="652" hidden="1">
+    <row r="652">
       <c r="A652" t="s">
         <v>3565</v>
       </c>
@@ -29218,7 +30079,7 @@
         <v>3570</v>
       </c>
     </row>
-    <row r="653" hidden="1">
+    <row r="653">
       <c r="A653" t="s">
         <v>3571</v>
       </c>
@@ -29267,7 +30128,7 @@
         <v>3581</v>
       </c>
     </row>
-    <row r="655" hidden="1">
+    <row r="655">
       <c r="A655" t="s">
         <v>3582</v>
       </c>
@@ -29293,7 +30154,7 @@
         <v>3587</v>
       </c>
     </row>
-    <row r="656" hidden="1">
+    <row r="656">
       <c r="A656" t="s">
         <v>3588</v>
       </c>
@@ -29365,7 +30226,7 @@
         <v>3603</v>
       </c>
     </row>
-    <row r="659" hidden="1">
+    <row r="659">
       <c r="A659" t="s">
         <v>3604</v>
       </c>
@@ -29391,7 +30252,7 @@
         <v>3609</v>
       </c>
     </row>
-    <row r="660" hidden="1">
+    <row r="660">
       <c r="A660" t="s">
         <v>3610</v>
       </c>
@@ -29417,7 +30278,7 @@
         <v>3615</v>
       </c>
     </row>
-    <row r="661" hidden="1">
+    <row r="661">
       <c r="A661" t="s">
         <v>3616</v>
       </c>
@@ -29443,7 +30304,7 @@
         <v>3621</v>
       </c>
     </row>
-    <row r="662" hidden="1">
+    <row r="662">
       <c r="A662" t="s">
         <v>3622</v>
       </c>
@@ -29469,7 +30330,7 @@
         <v>3627</v>
       </c>
     </row>
-    <row r="663" hidden="1">
+    <row r="663">
       <c r="A663" t="s">
         <v>3628</v>
       </c>
@@ -29495,7 +30356,7 @@
         <v>3633</v>
       </c>
     </row>
-    <row r="664" hidden="1">
+    <row r="664">
       <c r="A664" t="s">
         <v>3634</v>
       </c>
@@ -29521,7 +30382,7 @@
         <v>3639</v>
       </c>
     </row>
-    <row r="665" hidden="1">
+    <row r="665">
       <c r="A665" t="s">
         <v>3640</v>
       </c>
@@ -29547,7 +30408,7 @@
         <v>3645</v>
       </c>
     </row>
-    <row r="666" hidden="1">
+    <row r="666">
       <c r="A666" t="s">
         <v>3646</v>
       </c>
@@ -29573,7 +30434,7 @@
         <v>3651</v>
       </c>
     </row>
-    <row r="667" hidden="1">
+    <row r="667">
       <c r="A667" t="s">
         <v>3652</v>
       </c>
@@ -29599,7 +30460,7 @@
         <v>3657</v>
       </c>
     </row>
-    <row r="668" hidden="1">
+    <row r="668">
       <c r="A668" t="s">
         <v>3658</v>
       </c>
@@ -29625,7 +30486,7 @@
         <v>3663</v>
       </c>
     </row>
-    <row r="669" hidden="1">
+    <row r="669">
       <c r="A669" t="s">
         <v>3664</v>
       </c>
@@ -29674,7 +30535,7 @@
         <v>3674</v>
       </c>
     </row>
-    <row r="671" hidden="1">
+    <row r="671">
       <c r="A671" t="s">
         <v>3675</v>
       </c>
@@ -29746,7 +30607,7 @@
         <v>3690</v>
       </c>
     </row>
-    <row r="674" hidden="1">
+    <row r="674">
       <c r="A674" t="s">
         <v>3691</v>
       </c>
@@ -29772,7 +30633,7 @@
         <v>3696</v>
       </c>
     </row>
-    <row r="675" hidden="1">
+    <row r="675">
       <c r="A675" t="s">
         <v>3697</v>
       </c>
@@ -29798,7 +30659,7 @@
         <v>3702</v>
       </c>
     </row>
-    <row r="676" hidden="1">
+    <row r="676">
       <c r="A676" t="s">
         <v>3703</v>
       </c>
@@ -29824,7 +30685,7 @@
         <v>3708</v>
       </c>
     </row>
-    <row r="677" hidden="1">
+    <row r="677">
       <c r="A677" t="s">
         <v>3709</v>
       </c>
@@ -29850,7 +30711,7 @@
         <v>3714</v>
       </c>
     </row>
-    <row r="678" hidden="1">
+    <row r="678">
       <c r="A678" t="s">
         <v>3715</v>
       </c>
@@ -29876,7 +30737,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="679" hidden="1">
+    <row r="679">
       <c r="A679" t="s">
         <v>3721</v>
       </c>
@@ -29902,7 +30763,7 @@
         <v>3726</v>
       </c>
     </row>
-    <row r="680" hidden="1">
+    <row r="680">
       <c r="A680" t="s">
         <v>3727</v>
       </c>
@@ -29928,7 +30789,7 @@
         <v>3732</v>
       </c>
     </row>
-    <row r="681" hidden="1">
+    <row r="681">
       <c r="A681" t="s">
         <v>3733</v>
       </c>
@@ -29954,7 +30815,7 @@
         <v>3738</v>
       </c>
     </row>
-    <row r="682" hidden="1">
+    <row r="682">
       <c r="A682" t="s">
         <v>3739</v>
       </c>
@@ -29980,7 +30841,7 @@
         <v>3744</v>
       </c>
     </row>
-    <row r="683" hidden="1">
+    <row r="683">
       <c r="A683" t="s">
         <v>3745</v>
       </c>
@@ -30006,7 +30867,7 @@
         <v>3750</v>
       </c>
     </row>
-    <row r="684" hidden="1">
+    <row r="684">
       <c r="A684" t="s">
         <v>3751</v>
       </c>
@@ -30032,7 +30893,7 @@
         <v>3756</v>
       </c>
     </row>
-    <row r="685" hidden="1">
+    <row r="685">
       <c r="A685" t="s">
         <v>3757</v>
       </c>
@@ -30058,7 +30919,7 @@
         <v>3762</v>
       </c>
     </row>
-    <row r="686" hidden="1">
+    <row r="686">
       <c r="A686" t="s">
         <v>3763</v>
       </c>
@@ -30084,7 +30945,7 @@
         <v>3768</v>
       </c>
     </row>
-    <row r="687" hidden="1">
+    <row r="687">
       <c r="A687" t="s">
         <v>3769</v>
       </c>
@@ -30110,7 +30971,7 @@
         <v>3774</v>
       </c>
     </row>
-    <row r="688" hidden="1">
+    <row r="688">
       <c r="A688" t="s">
         <v>3775</v>
       </c>
@@ -30136,7 +30997,7 @@
         <v>3780</v>
       </c>
     </row>
-    <row r="689">
+    <row r="689" hidden="1">
       <c r="A689" t="s">
         <v>3781</v>
       </c>
@@ -30159,7 +31020,7 @@
         <v>3785</v>
       </c>
     </row>
-    <row r="690" hidden="1">
+    <row r="690">
       <c r="A690" t="s">
         <v>3786</v>
       </c>
@@ -30231,7 +31092,7 @@
         <v>3801</v>
       </c>
     </row>
-    <row r="693">
+    <row r="693" hidden="1">
       <c r="A693" t="s">
         <v>3802</v>
       </c>
@@ -30254,7 +31115,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="694">
+    <row r="694" hidden="1">
       <c r="A694" t="s">
         <v>3807</v>
       </c>
@@ -30277,7 +31138,7 @@
         <v>3811</v>
       </c>
     </row>
-    <row r="695">
+    <row r="695" hidden="1">
       <c r="A695" t="s">
         <v>3812</v>
       </c>
@@ -30300,7 +31161,7 @@
         <v>3816</v>
       </c>
     </row>
-    <row r="696">
+    <row r="696" hidden="1">
       <c r="A696" t="s">
         <v>3817</v>
       </c>
@@ -30323,7 +31184,7 @@
         <v>3821</v>
       </c>
     </row>
-    <row r="697">
+    <row r="697" hidden="1">
       <c r="A697" t="s">
         <v>3822</v>
       </c>
@@ -30346,7 +31207,7 @@
         <v>3826</v>
       </c>
     </row>
-    <row r="698">
+    <row r="698" hidden="1">
       <c r="A698" t="s">
         <v>3827</v>
       </c>
@@ -30369,7 +31230,7 @@
         <v>3831</v>
       </c>
     </row>
-    <row r="699">
+    <row r="699" hidden="1">
       <c r="A699" t="s">
         <v>3832</v>
       </c>
@@ -30392,7 +31253,7 @@
         <v>3836</v>
       </c>
     </row>
-    <row r="700">
+    <row r="700" hidden="1">
       <c r="A700" t="s">
         <v>3837</v>
       </c>
@@ -30415,7 +31276,7 @@
         <v>3841</v>
       </c>
     </row>
-    <row r="701">
+    <row r="701" hidden="1">
       <c r="A701" t="s">
         <v>3842</v>
       </c>
@@ -30438,7 +31299,7 @@
         <v>3846</v>
       </c>
     </row>
-    <row r="702">
+    <row r="702" hidden="1">
       <c r="A702" t="s">
         <v>3847</v>
       </c>
@@ -30461,7 +31322,7 @@
         <v>3851</v>
       </c>
     </row>
-    <row r="703">
+    <row r="703" hidden="1">
       <c r="A703" t="s">
         <v>3852</v>
       </c>
@@ -30484,7 +31345,7 @@
         <v>3856</v>
       </c>
     </row>
-    <row r="704">
+    <row r="704" hidden="1">
       <c r="A704" t="s">
         <v>3857</v>
       </c>
@@ -30507,7 +31368,7 @@
         <v>3861</v>
       </c>
     </row>
-    <row r="705">
+    <row r="705" hidden="1">
       <c r="A705" t="s">
         <v>3862</v>
       </c>
@@ -30530,7 +31391,7 @@
         <v>3866</v>
       </c>
     </row>
-    <row r="706">
+    <row r="706" hidden="1">
       <c r="A706" t="s">
         <v>3867</v>
       </c>
@@ -30553,7 +31414,7 @@
         <v>3871</v>
       </c>
     </row>
-    <row r="707">
+    <row r="707" hidden="1">
       <c r="A707" t="s">
         <v>3872</v>
       </c>
@@ -30576,7 +31437,7 @@
         <v>3876</v>
       </c>
     </row>
-    <row r="708">
+    <row r="708" hidden="1">
       <c r="A708" t="s">
         <v>3877</v>
       </c>
@@ -30622,7 +31483,7 @@
         <v>3886</v>
       </c>
     </row>
-    <row r="710" hidden="1">
+    <row r="710">
       <c r="A710" t="s">
         <v>3887</v>
       </c>
@@ -30648,7 +31509,7 @@
         <v>3892</v>
       </c>
     </row>
-    <row r="711" hidden="1">
+    <row r="711">
       <c r="A711" t="s">
         <v>3893</v>
       </c>
@@ -30674,7 +31535,7 @@
         <v>3898</v>
       </c>
     </row>
-    <row r="712" hidden="1">
+    <row r="712">
       <c r="A712" t="s">
         <v>3899</v>
       </c>
@@ -30700,7 +31561,7 @@
         <v>3904</v>
       </c>
     </row>
-    <row r="713" hidden="1">
+    <row r="713">
       <c r="A713" t="s">
         <v>3905</v>
       </c>
@@ -30726,7 +31587,7 @@
         <v>3910</v>
       </c>
     </row>
-    <row r="714" hidden="1">
+    <row r="714">
       <c r="A714" t="s">
         <v>3911</v>
       </c>
@@ -30752,7 +31613,7 @@
         <v>3916</v>
       </c>
     </row>
-    <row r="715" hidden="1">
+    <row r="715">
       <c r="A715" t="s">
         <v>3917</v>
       </c>
@@ -30778,7 +31639,7 @@
         <v>3922</v>
       </c>
     </row>
-    <row r="716" hidden="1">
+    <row r="716">
       <c r="A716" t="s">
         <v>3923</v>
       </c>
@@ -30804,7 +31665,7 @@
         <v>3928</v>
       </c>
     </row>
-    <row r="717" hidden="1">
+    <row r="717">
       <c r="A717" t="s">
         <v>3929</v>
       </c>
@@ -30830,7 +31691,7 @@
         <v>3933</v>
       </c>
     </row>
-    <row r="718" hidden="1">
+    <row r="718">
       <c r="A718" t="s">
         <v>3934</v>
       </c>
@@ -30856,7 +31717,7 @@
         <v>3939</v>
       </c>
     </row>
-    <row r="719" hidden="1">
+    <row r="719">
       <c r="A719" t="s">
         <v>3940</v>
       </c>
@@ -30905,7 +31766,7 @@
         <v>3950</v>
       </c>
     </row>
-    <row r="721" hidden="1">
+    <row r="721">
       <c r="A721" t="s">
         <v>3951</v>
       </c>
@@ -30931,7 +31792,7 @@
         <v>3956</v>
       </c>
     </row>
-    <row r="722" hidden="1">
+    <row r="722">
       <c r="A722" t="s">
         <v>3957</v>
       </c>
@@ -30957,7 +31818,7 @@
         <v>3962</v>
       </c>
     </row>
-    <row r="723" hidden="1">
+    <row r="723">
       <c r="A723" t="s">
         <v>3963</v>
       </c>
@@ -30983,7 +31844,7 @@
         <v>3968</v>
       </c>
     </row>
-    <row r="724" hidden="1">
+    <row r="724">
       <c r="A724" t="s">
         <v>3969</v>
       </c>
@@ -31055,7 +31916,7 @@
         <v>3984</v>
       </c>
     </row>
-    <row r="727" hidden="1">
+    <row r="727">
       <c r="A727" t="s">
         <v>3985</v>
       </c>
@@ -31081,7 +31942,7 @@
         <v>3990</v>
       </c>
     </row>
-    <row r="728" hidden="1">
+    <row r="728">
       <c r="A728" t="s">
         <v>3991</v>
       </c>
@@ -31107,7 +31968,7 @@
         <v>3996</v>
       </c>
     </row>
-    <row r="729" hidden="1">
+    <row r="729">
       <c r="A729" t="s">
         <v>3997</v>
       </c>
@@ -31133,7 +31994,7 @@
         <v>4002</v>
       </c>
     </row>
-    <row r="730" hidden="1">
+    <row r="730">
       <c r="A730" t="s">
         <v>4003</v>
       </c>
@@ -31159,7 +32020,7 @@
         <v>4008</v>
       </c>
     </row>
-    <row r="731" hidden="1">
+    <row r="731">
       <c r="A731" t="s">
         <v>4009</v>
       </c>
@@ -31185,7 +32046,7 @@
         <v>4014</v>
       </c>
     </row>
-    <row r="732" hidden="1">
+    <row r="732">
       <c r="A732" t="s">
         <v>4015</v>
       </c>
@@ -31211,7 +32072,7 @@
         <v>4020</v>
       </c>
     </row>
-    <row r="733" hidden="1">
+    <row r="733">
       <c r="A733" t="s">
         <v>4021</v>
       </c>
@@ -31237,7 +32098,7 @@
         <v>4026</v>
       </c>
     </row>
-    <row r="734" hidden="1">
+    <row r="734">
       <c r="A734" t="s">
         <v>4027</v>
       </c>
@@ -31263,7 +32124,7 @@
         <v>4032</v>
       </c>
     </row>
-    <row r="735" hidden="1">
+    <row r="735">
       <c r="A735" t="s">
         <v>4033</v>
       </c>
@@ -31289,7 +32150,7 @@
         <v>4038</v>
       </c>
     </row>
-    <row r="736" hidden="1">
+    <row r="736">
       <c r="A736" t="s">
         <v>4039</v>
       </c>
@@ -31315,7 +32176,7 @@
         <v>4044</v>
       </c>
     </row>
-    <row r="737" hidden="1">
+    <row r="737">
       <c r="A737" t="s">
         <v>4045</v>
       </c>
@@ -31341,7 +32202,7 @@
         <v>4050</v>
       </c>
     </row>
-    <row r="738" hidden="1">
+    <row r="738">
       <c r="A738" t="s">
         <v>4051</v>
       </c>
@@ -31367,7 +32228,7 @@
         <v>4056</v>
       </c>
     </row>
-    <row r="739" hidden="1">
+    <row r="739">
       <c r="A739" t="s">
         <v>4057</v>
       </c>
@@ -31393,7 +32254,7 @@
         <v>4062</v>
       </c>
     </row>
-    <row r="740" hidden="1">
+    <row r="740">
       <c r="A740" t="s">
         <v>4063</v>
       </c>
@@ -31419,7 +32280,7 @@
         <v>4068</v>
       </c>
     </row>
-    <row r="741" hidden="1">
+    <row r="741">
       <c r="A741" t="s">
         <v>4069</v>
       </c>
@@ -31439,24 +32300,24 @@
         <v>3</v>
       </c>
       <c r="G741" t="s">
+        <v>734</v>
+      </c>
+      <c r="H741" t="s">
         <v>4073</v>
       </c>
-      <c r="H741" t="s">
+    </row>
+    <row r="742">
+      <c r="A742" t="s">
         <v>4074</v>
       </c>
-    </row>
-    <row r="742" hidden="1">
-      <c r="A742" t="s">
+      <c r="B742" t="s">
         <v>4075</v>
       </c>
-      <c r="B742" t="s">
+      <c r="C742" t="s">
         <v>4076</v>
       </c>
-      <c r="C742" t="s">
+      <c r="D742" t="s">
         <v>4077</v>
-      </c>
-      <c r="D742" t="s">
-        <v>4078</v>
       </c>
       <c r="E742">
         <v>36</v>
@@ -31468,21 +32329,21 @@
         <v>868</v>
       </c>
       <c r="H742" t="s">
+        <v>4078</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="s">
         <v>4079</v>
       </c>
-    </row>
-    <row r="743" hidden="1">
-      <c r="A743" t="s">
+      <c r="B743" t="s">
         <v>4080</v>
       </c>
-      <c r="B743" t="s">
+      <c r="C743" t="s">
         <v>4081</v>
       </c>
-      <c r="C743" t="s">
+      <c r="D743" t="s">
         <v>4082</v>
-      </c>
-      <c r="D743" t="s">
-        <v>4083</v>
       </c>
       <c r="E743">
         <v>36</v>
@@ -31494,21 +32355,21 @@
         <v>684</v>
       </c>
       <c r="H743" t="s">
+        <v>4083</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="s">
         <v>4084</v>
       </c>
-    </row>
-    <row r="744" hidden="1">
-      <c r="A744" t="s">
+      <c r="B744" t="s">
         <v>4085</v>
       </c>
-      <c r="B744" t="s">
+      <c r="C744" t="s">
         <v>4086</v>
       </c>
-      <c r="C744" t="s">
+      <c r="D744" t="s">
         <v>4087</v>
-      </c>
-      <c r="D744" t="s">
-        <v>4088</v>
       </c>
       <c r="E744">
         <v>36</v>
@@ -31520,21 +32381,21 @@
         <v>181</v>
       </c>
       <c r="H744" t="s">
+        <v>4088</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="s">
         <v>4089</v>
       </c>
-    </row>
-    <row r="745" hidden="1">
-      <c r="A745" t="s">
+      <c r="B745" t="s">
         <v>4090</v>
       </c>
-      <c r="B745" t="s">
+      <c r="C745" t="s">
         <v>4091</v>
       </c>
-      <c r="C745" t="s">
+      <c r="D745" t="s">
         <v>4092</v>
-      </c>
-      <c r="D745" t="s">
-        <v>4093</v>
       </c>
       <c r="E745">
         <v>35</v>
@@ -31543,24 +32404,24 @@
         <v>3</v>
       </c>
       <c r="G745" t="s">
+        <v>4093</v>
+      </c>
+      <c r="H745" t="s">
         <v>4094</v>
       </c>
-      <c r="H745" t="s">
+    </row>
+    <row r="746">
+      <c r="A746" t="s">
         <v>4095</v>
       </c>
-    </row>
-    <row r="746" hidden="1">
-      <c r="A746" t="s">
+      <c r="B746" t="s">
         <v>4096</v>
-      </c>
-      <c r="B746" t="s">
-        <v>4097</v>
       </c>
       <c r="C746" t="s">
         <v>259</v>
       </c>
       <c r="D746" t="s">
-        <v>4098</v>
+        <v>4097</v>
       </c>
       <c r="E746">
         <v>34</v>
@@ -31569,17 +32430,17 @@
         <v>3</v>
       </c>
       <c r="G746" t="s">
+        <v>4098</v>
+      </c>
+      <c r="H746" t="s">
         <v>4099</v>
-      </c>
-      <c r="H746" t="s">
-        <v>4100</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I746">
     <filterColumn colId="2">
       <filters>
-        <filter val="Pokemon"/>
+        <filter val="Maps"/>
       </filters>
     </filterColumn>
     <sortState ref="A19:I746">
@@ -31594,7 +32455,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{F89FE493-E8EA-4DD7-B63E-FC3C22F1A3B7}">
+          <x14:cfRule type="cellIs" priority="1" operator="equal" id="{1A0DCCEA-9F41-455B-802A-8938CA789C45}">
             <xm:f>"Vertaald"</xm:f>
             <x14:dxf>
               <font>
@@ -31611,7 +32472,7 @@
           <xm:sqref>G:G</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{FFB2F9FD-4594-46B9-A507-1FAD2653B5E2}">
+          <x14:cfRule type="cellIs" priority="2" operator="equal" id="{76C695CC-F392-4105-8B06-BEBD7E0106BE}">
             <xm:f>"Onvertaald"</xm:f>
             <x14:dxf>
               <font>
@@ -31635,25 +32496,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="22"/>
     <col customWidth="1" min="2" max="2" width="25.33203125"/>
     <col bestFit="1" min="3" max="3" width="9.5546875"/>
+    <col customWidth="1" min="8" max="8" width="18.00390625"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4101</v>
+        <v>4100</v>
       </c>
       <c r="B1" s="2">
         <f>SUMIF(Sheet1!G2:G997,"Vertaald",Sheet1!E2:E997)</f>
-        <v>2054087</v>
+        <v>2069197</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
       <c r="E1" t="s">
+        <v>4101</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>4102</v>
       </c>
     </row>
@@ -31663,39 +32531,57 @@
       </c>
       <c r="B2" s="2">
         <f>SUMIF(Sheet1!G2:G997,"Onvertaald",Sheet1!E2:E997)</f>
-        <v>6030823</v>
+        <v>6015713</v>
       </c>
       <c r="D2" t="s">
         <v>181</v>
       </c>
       <c r="E2">
         <f>SUMIF(Sheet1!G2:G997,"Vertaald",Sheet1!E2:E997)</f>
-        <v>2054087</v>
-      </c>
-    </row>
-    <row r="3" ht="15.6">
+        <v>2069197</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2" s="4">
+        <f>SUMIFS(Sheet1!E2:E1000,Sheet1!C2:C1000,"Maps",Sheet1!G2:G1000,"Vertaald")</f>
+        <v>670891</v>
+      </c>
+    </row>
+    <row r="3" ht="15">
       <c r="A3" s="1" t="s">
         <v>4104</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="5">
         <f>SUM(Sheet1!E2:E997)</f>
         <v>8084910</v>
       </c>
       <c r="D3" t="s">
-        <v>4099</v>
+        <v>4098</v>
       </c>
       <c r="E3">
         <f>SUMIF(Sheet1!G2:G997,"Onvertaald",Sheet1!E2:E997)</f>
-        <v>6030823</v>
-      </c>
-    </row>
-    <row r="4" ht="46.200000000000003">
+        <v>6015713</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>4098</v>
+      </c>
+      <c r="H3" s="4">
+        <f>SUMIFS(Sheet1!E2:E1000,Sheet1!C2:C1000,"Maps",Sheet1!G2:G1000,"Onvertaald")</f>
+        <v>1428345</v>
+      </c>
+    </row>
+    <row r="4" ht="45">
       <c r="A4" s="1" t="s">
         <v>4105</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="6">
         <f>B1/B3</f>
-        <v>0.25406430003549824</v>
+        <v>0.25593321385148382</v>
+      </c>
+      <c r="H4" s="7">
+        <f>H2/SUM(H2:H3)</f>
+        <v>0.31958817398329675</v>
       </c>
     </row>
   </sheetData>
